--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B8FC795-B1B5-4A4F-AFB9-6AC7355799E1}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C61EE5C6-F26D-4FF2-A94B-2F09B6B1F642}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Portada" sheetId="1" r:id="rId1"/>
-    <sheet name="Calculos" sheetId="2" r:id="rId2"/>
+    <sheet name="Portada" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Calculos" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Dashboard Ejecutivo" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="Triángulo Accidentabilidad" sheetId="4" r:id="rId4"/>
-    <sheet name="Parametros" sheetId="5" r:id="rId5"/>
+    <sheet name="Parametros" sheetId="5" state="hidden" r:id="rId5"/>
     <sheet name="Captura Enero" sheetId="6" state="hidden" r:id="rId6"/>
     <sheet name="Captura Febrero" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet name="Captura Marzo" sheetId="8" state="hidden" r:id="rId8"/>
@@ -38,7 +38,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'ACUMULADO - 2026'!$A$3:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Dashboard Ejecutivo'!$A$1:$Y$75</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1883,7 +1883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="56" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2131,6 +2131,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2152,24 +2173,6 @@
     <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2178,15 +2181,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2202,23 +2196,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2244,6 +2229,24 @@
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2253,8 +2256,11 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3273,43 +3279,43 @@
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>Alrededores</c:v>
+                  <c:v>Calidad</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Calidad</c:v>
+                  <c:v>Materias Primas</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Centro de Distribucion</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>ETEI</c:v>
+                  <c:v>Linea 2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Equipos Auxiliares</c:v>
+                  <c:v>Jarabes</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jarabes</c:v>
+                  <c:v>Equipos Auxiliares</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Linea 1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Linea 2</c:v>
+                  <c:v>Linea 4</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Linea 3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Linea 4</c:v>
+                  <c:v>ETEI</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>Mantenimiento</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>Linea 5</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>Mantenimiento</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>Materias Primas</c:v>
+                  <c:v>Alrededores</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Almacen de Repuestos</c:v>
@@ -3690,16 +3696,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.42372574846206423</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.71533333333333315</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.71533333333333315</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -4377,7 +4383,7 @@
                   <c:v>0.86230933333333326</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.47197181635907953</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4835,8 +4841,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1682750" y="4267200"/>
-          <a:ext cx="7632700" cy="3435350"/>
+          <a:off x="1680882" y="4295588"/>
+          <a:ext cx="7603939" cy="3481294"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5113,38 +5119,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
+      <c r="B3" s="122" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
     </row>
     <row r="4" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="121"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
     </row>
     <row r="5" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
     </row>
     <row r="6" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
     </row>
     <row r="7" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="122" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
+      <c r="B7" s="123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
     </row>
     <row r="10" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -5177,7 +5183,7 @@
       </c>
       <c r="C13" s="4">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5198,72 +5204,72 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="123" t="s">
+      <c r="B18" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="123"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="123"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
     </row>
     <row r="19" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="121"/>
     </row>
     <row r="21" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="121" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
     </row>
     <row r="22" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="120" t="s">
+      <c r="C22" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="120"/>
-      <c r="E22" s="120"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="121"/>
     </row>
     <row r="23" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="120" t="s">
+      <c r="C23" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="120"/>
-      <c r="E23" s="120"/>
+      <c r="D23" s="121"/>
+      <c r="E23" s="121"/>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="120" t="s">
+      <c r="C24" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="120"/>
-      <c r="E24" s="120"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5304,62 +5310,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5368,20 +5374,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5429,66 +5435,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5700,10 +5706,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8270,16 +8276,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.8793333333333333</v>
@@ -8446,9 +8452,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8475,11 +8481,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8537,12 +8543,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8557,6 +8557,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8638,62 +8644,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8702,20 +8708,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8763,66 +8769,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -9034,10 +9040,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11604,16 +11610,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11780,9 +11786,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11809,11 +11815,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11871,12 +11877,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11891,6 +11891,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11974,62 +11980,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -12038,20 +12044,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -12099,66 +12105,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12370,10 +12376,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14940,16 +14946,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -15116,9 +15122,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -15145,11 +15151,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -15207,12 +15213,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -15227,6 +15227,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15312,62 +15318,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15376,20 +15382,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15437,66 +15443,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15708,10 +15714,10 @@
         <f>'Captura Agosto'!AQ7</f>
         <v>0.64449999999999996</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -18278,16 +18284,16 @@
         <v>0.97124999999999995</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.86230933333333326</v>
@@ -18454,9 +18460,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18483,11 +18489,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18545,12 +18551,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18565,6 +18565,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18637,7 +18643,9 @@
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="48" width="9.54296875" customWidth="1"/>
+    <col min="4" max="44" width="9.54296875" customWidth="1"/>
+    <col min="45" max="45" width="19" customWidth="1"/>
+    <col min="46" max="48" width="9.54296875" customWidth="1"/>
     <col min="49" max="50" width="11" customWidth="1"/>
     <col min="51" max="51" width="13" customWidth="1"/>
     <col min="52" max="52" width="11" customWidth="1"/>
@@ -18647,90 +18655,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="149" t="s">
+      <c r="G2" s="113" t="s">
         <v>166</v>
       </c>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
-      <c r="M2" s="149"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18738,7 +18746,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:55" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AR3" s="58"/>
       <c r="AS3" s="63" t="s">
         <v>171</v>
@@ -18771,81 +18779,81 @@
         <v>180</v>
       </c>
       <c r="BC3" s="69">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:55" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
-      <c r="AS4" s="71" t="str">
+      <c r="AS4" s="150" t="str">
         <f>'Captura Septiembre'!B6</f>
         <v>Almacen de Repuestos</v>
       </c>
       <c r="AT4" s="72">
         <f>'Captura Septiembre'!K6+'Captura Septiembre'!N6+'Captura Septiembre'!Q6</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU4" s="72">
         <f>'Captura Septiembre'!T6</f>
@@ -18857,7 +18865,7 @@
       </c>
       <c r="AW4" s="72">
         <f>'Captura Septiembre'!G6</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AX4" s="72">
         <f>'Captura Septiembre'!X6</f>
@@ -18873,13 +18881,13 @@
       </c>
       <c r="BA4" s="74">
         <f>'Captura Septiembre'!AQ6</f>
-        <v>0.33</v>
+        <v>0.47000000000000003</v>
       </c>
       <c r="BB4" s="68" t="s">
         <v>191</v>
       </c>
       <c r="BC4" s="75">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:55" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -19049,10 +19057,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.33</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -19066,18 +19074,18 @@
         <v>Fredy Fuentes</v>
       </c>
       <c r="D6" s="85">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E6" s="85">
         <v>0</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ref="F6:F20" si="0">AVERAGE(D6,E6)</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="86">
         <f>F6*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="H6" s="87">
         <v>38</v>
@@ -19093,14 +19101,14 @@
         <v>0.08</v>
       </c>
       <c r="L6" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N6" s="86">
         <f>IF(M6="NO",0,L6*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O6" s="85">
         <v>0</v>
@@ -19194,11 +19202,11 @@
       </c>
       <c r="AP6" s="11">
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
-        <v>0.33</v>
+        <v>0.47000000000000003</v>
       </c>
       <c r="AQ6" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6-AN6-IF(AO6="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.47000000000000003</v>
       </c>
       <c r="AR6" s="58"/>
       <c r="AS6" s="71" t="str">
@@ -19207,7 +19215,7 @@
       </c>
       <c r="AT6" s="72">
         <f>'Captura Septiembre'!K8+'Captura Septiembre'!N8+'Captura Septiembre'!Q8</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU6" s="72">
         <f>'Captura Septiembre'!T8</f>
@@ -19219,7 +19227,7 @@
       </c>
       <c r="AW6" s="72">
         <f>'Captura Septiembre'!G8</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX6" s="72">
         <f>'Captura Septiembre'!X8</f>
@@ -19235,12 +19243,12 @@
       </c>
       <c r="BA6" s="74">
         <f>'Captura Septiembre'!AQ8</f>
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="BB6" s="58"/>
       <c r="BC6" s="58"/>
     </row>
-    <row r="7" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:55" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>2</v>
       </c>
@@ -19387,13 +19395,13 @@
         <v>0.33</v>
       </c>
       <c r="AR7" s="58"/>
-      <c r="AS7" s="79" t="str">
+      <c r="AS7" s="151" t="str">
         <f>'Captura Septiembre'!B9</f>
         <v>Centro de Distribucion</v>
       </c>
       <c r="AT7" s="80">
         <f>'Captura Septiembre'!K9+'Captura Septiembre'!N9+'Captura Septiembre'!Q9</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU7" s="80">
         <f>'Captura Septiembre'!T9</f>
@@ -19405,7 +19413,7 @@
       </c>
       <c r="AW7" s="80">
         <f>'Captura Septiembre'!G9</f>
-        <v>0</v>
+        <v>9.7370000000000012E-2</v>
       </c>
       <c r="AX7" s="80">
         <f>'Captura Septiembre'!X9</f>
@@ -19421,7 +19429,7 @@
       </c>
       <c r="BA7" s="82">
         <f>'Captura Septiembre'!AQ9</f>
-        <v>0.33</v>
+        <v>0.5073700000000001</v>
       </c>
       <c r="BB7" s="58"/>
       <c r="BC7" s="58"/>
@@ -19438,18 +19446,18 @@
         <v>Alejandro Martinez</v>
       </c>
       <c r="D8" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="85">
         <v>0</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="86">
         <f>F8*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H8" s="87">
         <v>38</v>
@@ -19465,14 +19473,14 @@
         <v>0.08</v>
       </c>
       <c r="L8" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N8" s="86">
         <f>IF(M8="NO",0,L8*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O8" s="85">
         <v>0</v>
@@ -19566,11 +19574,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="AQ8" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8-AN8-IF(AO8="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="AR8" s="58"/>
       <c r="AS8" s="71" t="str">
@@ -19591,7 +19599,7 @@
       </c>
       <c r="AW8" s="72">
         <f>'Captura Septiembre'!G10</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX8" s="72">
         <f>'Captura Septiembre'!X10</f>
@@ -19607,7 +19615,7 @@
       </c>
       <c r="BA8" s="74">
         <f>'Captura Septiembre'!AQ10</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BB8" s="58"/>
       <c r="BC8" s="58"/>
@@ -19624,18 +19632,18 @@
         <v>Jimmy Velasquez</v>
       </c>
       <c r="D9" s="85">
-        <v>0</v>
+        <v>0.97370000000000001</v>
       </c>
       <c r="E9" s="85">
         <v>0</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.48685</v>
       </c>
       <c r="G9" s="86">
         <f>F9*Parametros!$E$6</f>
-        <v>0</v>
+        <v>9.7370000000000012E-2</v>
       </c>
       <c r="H9" s="87">
         <v>38</v>
@@ -19651,14 +19659,14 @@
         <v>0.08</v>
       </c>
       <c r="L9" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N9" s="86">
         <f>IF(M9="NO",0,L9*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O9" s="85">
         <v>0</v>
@@ -19752,11 +19760,11 @@
       </c>
       <c r="AP9" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.5073700000000001</v>
       </c>
       <c r="AQ9" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9-AN9-IF(AO9="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.5073700000000001</v>
       </c>
       <c r="AR9" s="58"/>
       <c r="AS9" s="79" t="str">
@@ -19765,7 +19773,7 @@
       </c>
       <c r="AT9" s="80">
         <f>'Captura Septiembre'!K11+'Captura Septiembre'!N11+'Captura Septiembre'!Q11</f>
-        <v>0.08</v>
+        <v>0.1552</v>
       </c>
       <c r="AU9" s="80">
         <f>'Captura Septiembre'!T11</f>
@@ -19777,7 +19785,7 @@
       </c>
       <c r="AW9" s="80">
         <f>'Captura Septiembre'!G11</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX9" s="80">
         <f>'Captura Septiembre'!X11</f>
@@ -19793,7 +19801,7 @@
       </c>
       <c r="BA9" s="82">
         <f>'Captura Septiembre'!AQ11</f>
-        <v>0.33</v>
+        <v>0.50519999999999998</v>
       </c>
       <c r="BB9" s="58"/>
       <c r="BC9" s="58"/>
@@ -19810,18 +19818,18 @@
         <v>Jessica Loarca</v>
       </c>
       <c r="D10" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="85">
         <v>0</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="86">
         <f>F10*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H10" s="87">
         <v>38</v>
@@ -19938,11 +19946,11 @@
       </c>
       <c r="AP10" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ10" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10-AN10-IF(AO10="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR10" s="58"/>
       <c r="AS10" s="71" t="str">
@@ -19951,7 +19959,7 @@
       </c>
       <c r="AT10" s="72">
         <f>'Captura Septiembre'!K12+'Captura Septiembre'!N12+'Captura Septiembre'!Q12</f>
-        <v>0.08</v>
+        <v>0.156</v>
       </c>
       <c r="AU10" s="72">
         <f>'Captura Septiembre'!T12</f>
@@ -19963,7 +19971,7 @@
       </c>
       <c r="AW10" s="72">
         <f>'Captura Septiembre'!G12</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX10" s="72">
         <f>'Captura Septiembre'!X12</f>
@@ -19979,7 +19987,7 @@
       </c>
       <c r="BA10" s="74">
         <f>'Captura Septiembre'!AQ12</f>
-        <v>0.33</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="BB10" s="58"/>
       <c r="BC10" s="58"/>
@@ -19996,18 +20004,18 @@
         <v>Edson Bonifacio</v>
       </c>
       <c r="D11" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="85">
         <v>0</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="86">
         <f>F11*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H11" s="87">
         <v>38</v>
@@ -20023,14 +20031,14 @@
         <v>0.08</v>
       </c>
       <c r="L11" s="85">
-        <v>0</v>
+        <v>0.94</v>
       </c>
       <c r="M11" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N11" s="86">
         <f>IF(M11="NO",0,L11*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="O11" s="85">
         <v>0</v>
@@ -20124,11 +20132,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.50519999999999998</v>
       </c>
       <c r="AQ11" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11-AN11-IF(AO11="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.50519999999999998</v>
       </c>
       <c r="AR11" s="58"/>
       <c r="AS11" s="79" t="str">
@@ -20137,7 +20145,7 @@
       </c>
       <c r="AT11" s="80">
         <f>'Captura Septiembre'!K13+'Captura Septiembre'!N13+'Captura Septiembre'!Q13</f>
-        <v>0.08</v>
+        <v>0.15679999999999999</v>
       </c>
       <c r="AU11" s="80">
         <f>'Captura Septiembre'!T13</f>
@@ -20149,7 +20157,7 @@
       </c>
       <c r="AW11" s="80">
         <f>'Captura Septiembre'!G13</f>
-        <v>0</v>
+        <v>8.6363636363636365E-2</v>
       </c>
       <c r="AX11" s="80">
         <f>'Captura Septiembre'!X13</f>
@@ -20165,7 +20173,7 @@
       </c>
       <c r="BA11" s="82">
         <f>'Captura Septiembre'!AQ13</f>
-        <v>0.33</v>
+        <v>0.49316363636363636</v>
       </c>
       <c r="BB11" s="58"/>
       <c r="BC11" s="58"/>
@@ -20182,18 +20190,18 @@
         <v>Adrian Santisteban</v>
       </c>
       <c r="D12" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="85">
         <v>0</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="86">
         <f>F12*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="87">
         <v>38</v>
@@ -20209,14 +20217,14 @@
         <v>0.08</v>
       </c>
       <c r="L12" s="85">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="M12" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N12" s="86">
         <f>IF(M12="NO",0,L12*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="O12" s="85">
         <v>0</v>
@@ -20310,11 +20318,11 @@
       </c>
       <c r="AP12" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="AQ12" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12-AN12-IF(AO12="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.50600000000000001</v>
       </c>
       <c r="AR12" s="58"/>
       <c r="AS12" s="71" t="str">
@@ -20323,7 +20331,7 @@
       </c>
       <c r="AT12" s="72">
         <f>'Captura Septiembre'!K14+'Captura Septiembre'!N14+'Captura Septiembre'!Q14</f>
-        <v>0.08</v>
+        <v>0.15679999999999999</v>
       </c>
       <c r="AU12" s="72">
         <f>'Captura Septiembre'!T14</f>
@@ -20335,7 +20343,7 @@
       </c>
       <c r="AW12" s="72">
         <f>'Captura Septiembre'!G14</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" s="72">
         <f>'Captura Septiembre'!X14</f>
@@ -20351,7 +20359,7 @@
       </c>
       <c r="BA12" s="74">
         <f>'Captura Septiembre'!AQ14</f>
-        <v>0.33</v>
+        <v>0.50679999999999992</v>
       </c>
       <c r="BB12" s="58"/>
       <c r="BC12" s="58"/>
@@ -20368,18 +20376,18 @@
         <v>Amilcar Ralda</v>
       </c>
       <c r="D13" s="85">
-        <v>0</v>
+        <v>0.86363636363636365</v>
       </c>
       <c r="E13" s="85">
         <v>0</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.43181818181818182</v>
       </c>
       <c r="G13" s="86">
         <f>F13*Parametros!$E$6</f>
-        <v>0</v>
+        <v>8.6363636363636365E-2</v>
       </c>
       <c r="H13" s="87">
         <v>38</v>
@@ -20395,14 +20403,14 @@
         <v>0.08</v>
       </c>
       <c r="L13" s="85">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M13" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N13" s="86">
         <f>IF(M13="NO",0,L13*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="O13" s="85">
         <v>0</v>
@@ -20496,11 +20504,11 @@
       </c>
       <c r="AP13" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.49316363636363636</v>
       </c>
       <c r="AQ13" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13-AN13-IF(AO13="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.49316363636363636</v>
       </c>
       <c r="AR13" s="58"/>
       <c r="AS13" s="79" t="str">
@@ -20509,7 +20517,7 @@
       </c>
       <c r="AT13" s="80">
         <f>'Captura Septiembre'!K15+'Captura Septiembre'!N15+'Captura Septiembre'!Q15</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU13" s="80">
         <f>'Captura Septiembre'!T15</f>
@@ -20521,7 +20529,7 @@
       </c>
       <c r="AW13" s="80">
         <f>'Captura Septiembre'!G15</f>
-        <v>0</v>
+        <v>6.3157894736842107E-2</v>
       </c>
       <c r="AX13" s="80">
         <f>'Captura Septiembre'!X15</f>
@@ -20537,7 +20545,7 @@
       </c>
       <c r="BA13" s="82">
         <f>'Captura Septiembre'!AQ15</f>
-        <v>0.33</v>
+        <v>0.47315789473684211</v>
       </c>
       <c r="BB13" s="58"/>
       <c r="BC13" s="58"/>
@@ -20554,18 +20562,18 @@
         <v>Amilcar Ralda</v>
       </c>
       <c r="D14" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="85">
         <v>0</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="86">
         <f>F14*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H14" s="87">
         <v>38</v>
@@ -20581,14 +20589,14 @@
         <v>0.08</v>
       </c>
       <c r="L14" s="85">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M14" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N14" s="86">
         <f>IF(M14="NO",0,L14*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="O14" s="85">
         <v>0</v>
@@ -20682,11 +20690,11 @@
       </c>
       <c r="AP14" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.50679999999999992</v>
       </c>
       <c r="AQ14" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14-AN14-IF(AO14="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.50679999999999992</v>
       </c>
       <c r="AR14" s="58"/>
       <c r="AS14" s="71" t="str">
@@ -20695,7 +20703,7 @@
       </c>
       <c r="AT14" s="72">
         <f>'Captura Septiembre'!K16+'Captura Septiembre'!N16+'Captura Septiembre'!Q16</f>
-        <v>0.08</v>
+        <v>0.15679999999999999</v>
       </c>
       <c r="AU14" s="72">
         <f>'Captura Septiembre'!T16</f>
@@ -20707,7 +20715,7 @@
       </c>
       <c r="AW14" s="72">
         <f>'Captura Septiembre'!G16</f>
-        <v>0</v>
+        <v>8.5714285714285715E-2</v>
       </c>
       <c r="AX14" s="72">
         <f>'Captura Septiembre'!X16</f>
@@ -20723,7 +20731,7 @@
       </c>
       <c r="BA14" s="74">
         <f>'Captura Septiembre'!AQ16</f>
-        <v>0.33</v>
+        <v>0.49251428571428568</v>
       </c>
       <c r="BB14" s="58"/>
       <c r="BC14" s="58"/>
@@ -20740,18 +20748,18 @@
         <v>Mario Ramos</v>
       </c>
       <c r="D15" s="85">
-        <v>0</v>
+        <v>0.63157894736842102</v>
       </c>
       <c r="E15" s="85">
         <v>0</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.31578947368421051</v>
       </c>
       <c r="G15" s="86">
         <f>F15*Parametros!$E$6</f>
-        <v>0</v>
+        <v>6.3157894736842107E-2</v>
       </c>
       <c r="H15" s="87">
         <v>38</v>
@@ -20767,14 +20775,14 @@
         <v>0.08</v>
       </c>
       <c r="L15" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N15" s="86">
         <f>IF(M15="NO",0,L15*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O15" s="85">
         <v>0</v>
@@ -20868,11 +20876,11 @@
       </c>
       <c r="AP15" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.47315789473684211</v>
       </c>
       <c r="AQ15" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15-AN15-IF(AO15="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.47315789473684211</v>
       </c>
       <c r="AR15" s="58"/>
       <c r="AS15" s="79" t="str">
@@ -20893,7 +20901,7 @@
       </c>
       <c r="AW15" s="80">
         <f>'Captura Septiembre'!G17</f>
-        <v>0</v>
+        <v>7.857142857142857E-2</v>
       </c>
       <c r="AX15" s="80">
         <f>'Captura Septiembre'!X17</f>
@@ -20909,7 +20917,7 @@
       </c>
       <c r="BA15" s="82">
         <f>'Captura Septiembre'!AQ17</f>
-        <v>0.33</v>
+        <v>0.40857142857142859</v>
       </c>
       <c r="BB15" s="58"/>
       <c r="BC15" s="58"/>
@@ -20926,18 +20934,18 @@
         <v>Mario Ramos</v>
       </c>
       <c r="D16" s="85">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E16" s="85">
         <v>0</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="G16" s="86">
         <f>F16*Parametros!$E$6</f>
-        <v>0</v>
+        <v>8.5714285714285715E-2</v>
       </c>
       <c r="H16" s="87">
         <v>38</v>
@@ -20953,14 +20961,14 @@
         <v>0.08</v>
       </c>
       <c r="L16" s="85">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M16" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N16" s="86">
         <f>IF(M16="NO",0,L16*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="O16" s="85">
         <v>0</v>
@@ -21054,11 +21062,11 @@
       </c>
       <c r="AP16" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.49251428571428568</v>
       </c>
       <c r="AQ16" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16-AN16-IF(AO16="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.49251428571428568</v>
       </c>
       <c r="AR16" s="58"/>
       <c r="AS16" s="71" t="str">
@@ -21079,7 +21087,7 @@
       </c>
       <c r="AW16" s="72">
         <f>'Captura Septiembre'!G18</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX16" s="72">
         <f>'Captura Septiembre'!X18</f>
@@ -21095,7 +21103,7 @@
       </c>
       <c r="BA16" s="74">
         <f>'Captura Septiembre'!AQ18</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BB16" s="58"/>
       <c r="BC16" s="58"/>
@@ -21112,18 +21120,18 @@
         <v>Roy Luarca</v>
       </c>
       <c r="D17" s="85">
-        <v>0</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E17" s="85">
         <v>0</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.39285714285714285</v>
       </c>
       <c r="G17" s="86">
         <f>F17*Parametros!$E$6</f>
-        <v>0</v>
+        <v>7.857142857142857E-2</v>
       </c>
       <c r="H17" s="87">
         <v>38</v>
@@ -21240,11 +21248,11 @@
       </c>
       <c r="AP17" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.40857142857142859</v>
       </c>
       <c r="AQ17" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17-AN17-IF(AO17="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.40857142857142859</v>
       </c>
       <c r="AR17" s="58"/>
       <c r="AS17" s="79" t="str">
@@ -21253,7 +21261,7 @@
       </c>
       <c r="AT17" s="80">
         <f>'Captura Septiembre'!K19+'Captura Septiembre'!N19+'Captura Septiembre'!Q19</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU17" s="80">
         <f>'Captura Septiembre'!T19</f>
@@ -21265,7 +21273,7 @@
       </c>
       <c r="AW17" s="80">
         <f>'Captura Septiembre'!G19</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX17" s="80">
         <f>'Captura Septiembre'!X19</f>
@@ -21281,7 +21289,7 @@
       </c>
       <c r="BA17" s="82">
         <f>'Captura Septiembre'!AQ19</f>
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="BB17" s="58"/>
       <c r="BC17" s="58"/>
@@ -21298,18 +21306,18 @@
         <v>Eliu Tello</v>
       </c>
       <c r="D18" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="85">
         <v>0</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="86">
         <f>F18*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="87">
         <v>38</v>
@@ -21426,11 +21434,11 @@
       </c>
       <c r="AP18" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ18" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18-AN18-IF(AO18="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR18" s="58"/>
       <c r="AS18" s="71" t="str">
@@ -21439,7 +21447,7 @@
       </c>
       <c r="AT18" s="72">
         <f>'Captura Septiembre'!K20+'Captura Septiembre'!N20+'Captura Septiembre'!Q20</f>
-        <v>0.08</v>
+        <v>0.15679999999999999</v>
       </c>
       <c r="AU18" s="72">
         <f>'Captura Septiembre'!T20</f>
@@ -21451,7 +21459,7 @@
       </c>
       <c r="AW18" s="72">
         <f>'Captura Septiembre'!G20</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX18" s="72">
         <f>'Captura Septiembre'!X20</f>
@@ -21467,7 +21475,7 @@
       </c>
       <c r="BA18" s="74">
         <f>'Captura Septiembre'!AQ20</f>
-        <v>0.33</v>
+        <v>0.50679999999999992</v>
       </c>
       <c r="BB18" s="58"/>
       <c r="BC18" s="58"/>
@@ -21484,18 +21492,18 @@
         <v>Miguel Godinez</v>
       </c>
       <c r="D19" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="85">
         <v>0</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="86">
         <f>F19*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H19" s="87">
         <v>38</v>
@@ -21511,14 +21519,14 @@
         <v>0.08</v>
       </c>
       <c r="L19" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N19" s="86">
         <f>IF(M19="NO",0,L19*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O19" s="85">
         <v>0</v>
@@ -21612,26 +21620,26 @@
       </c>
       <c r="AP19" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="AQ19" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19-AN19-IF(AO19="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.51</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.33</v>
+        <v>0.47197181635907953</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -21648,18 +21656,18 @@
         <v>Adrian Santisteban</v>
       </c>
       <c r="D20" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="85">
         <v>0</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="86">
         <f>F20*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H20" s="87">
         <v>38</v>
@@ -21675,14 +21683,14 @@
         <v>0.08</v>
       </c>
       <c r="L20" s="85">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M20" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N20" s="86">
         <f>IF(M20="NO",0,L20*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="O20" s="85">
         <v>0</v>
@@ -21776,11 +21784,11 @@
       </c>
       <c r="AP20" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.50679999999999992</v>
       </c>
       <c r="AQ20" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20-AN20-IF(AO20="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.50679999999999992</v>
       </c>
       <c r="AR20" s="58"/>
       <c r="AS20" s="58"/>
@@ -21795,9 +21803,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21824,11 +21832,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21870,7 +21878,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="94">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.33</v>
+        <v>0.47197181635907953</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -21886,13 +21894,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
-    <mergeCell ref="G2:M2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21907,6 +21908,13 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
+    <mergeCell ref="G2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21988,62 +21996,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -22052,20 +22060,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -22113,66 +22121,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22384,10 +22392,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24954,16 +24962,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -25130,9 +25138,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -25159,11 +25167,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -25221,12 +25229,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -25241,6 +25243,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25322,62 +25330,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25386,20 +25394,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25447,66 +25455,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25718,10 +25726,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28288,16 +28296,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28464,9 +28472,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28493,11 +28501,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28555,12 +28563,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28575,6 +28577,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28656,62 +28664,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28720,20 +28728,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28781,66 +28789,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -29052,10 +29060,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31622,16 +31630,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31798,9 +31806,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31827,11 +31835,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31889,12 +31897,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31909,6 +31911,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31982,21 +31990,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="147" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="147"/>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -32117,13 +32125,13 @@
       <c r="A14" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="B14" s="97" t="str">
+      <c r="B14" s="97">
         <f>IF(AVERAGE('Captura Septiembre'!D6:D20)=0,"",'Captura Septiembre'!AQ23)</f>
-        <v/>
+        <v>0.47197181635907953</v>
       </c>
       <c r="C14" s="12" t="str">
         <f>IF(B14="","",IF(B14&gt;=Parametros!$C$37,"Verde",IF(B14&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
-        <v/>
+        <v>Rojo</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32204,22 +32212,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="148" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="99" t="s">
@@ -32301,9 +32309,9 @@
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
         <v>0.97525000000000006</v>
       </c>
-      <c r="J4" s="10" t="str">
+      <c r="J4" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
-        <v/>
+        <v>0.51</v>
       </c>
       <c r="K4" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
@@ -32319,7 +32327,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.99690624999999999</v>
+        <v>0.94280555555555567</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32358,9 +32366,9 @@
         <f>IFERROR(IF('Captura Agosto'!D6=0,"",'Captura Agosto'!AQ6),"")</f>
         <v>0.92995000000000005</v>
       </c>
-      <c r="J5" s="10" t="str">
+      <c r="J5" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
-        <v/>
+        <v>0.47000000000000003</v>
       </c>
       <c r="K5" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
@@ -32376,7 +32384,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.96124374999999995</v>
+        <v>0.90666111111111114</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32415,9 +32423,9 @@
         <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
         <v>1</v>
       </c>
-      <c r="J6" s="10" t="str">
+      <c r="J6" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
-        <v/>
+        <v>0.49251428571428568</v>
       </c>
       <c r="K6" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
@@ -32433,7 +32441,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.97178571428571425</v>
+        <v>0.91853333333333331</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32472,9 +32480,9 @@
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
         <v>0.70295000000000007</v>
       </c>
-      <c r="J7" s="10" t="str">
+      <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v/>
+        <v>0.40857142857142859</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -32490,7 +32498,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.84808853021978026</v>
+        <v>0.7992532967032967</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32529,9 +32537,9 @@
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
         <v>0.64826000000000006</v>
       </c>
-      <c r="J8" s="10" t="str">
+      <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
-        <v/>
+        <v>0.50679999999999992</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
@@ -32547,7 +32555,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.90103250000000012</v>
+        <v>0.85722888888888904</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32586,9 +32594,9 @@
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
         <v>0.79</v>
       </c>
-      <c r="J9" s="10" t="str">
+      <c r="J9" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
-        <v/>
+        <v>0.50519999999999998</v>
       </c>
       <c r="K9" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
@@ -32604,7 +32612,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.92437500000000006</v>
+        <v>0.87780000000000014</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32643,9 +32651,9 @@
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
         <v>0.74768000000000001</v>
       </c>
-      <c r="J10" s="10" t="str">
+      <c r="J10" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
-        <v/>
+        <v>0.49316363636363636</v>
       </c>
       <c r="K10" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D13=0,"",'Captura Octubre'!AQ13),"")</f>
@@ -32661,7 +32669,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.82220999999999989</v>
+        <v>0.78564929292929286</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32700,9 +32708,9 @@
         <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
         <v>1</v>
       </c>
-      <c r="J11" s="10" t="str">
+      <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -32718,7 +32726,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.95687500000000003</v>
+        <v>0.89833333333333343</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32757,9 +32765,9 @@
         <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
         <v>0.97195000000000009</v>
       </c>
-      <c r="J12" s="10" t="str">
+      <c r="J12" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v/>
+        <v>0.5073700000000001</v>
       </c>
       <c r="K12" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
@@ -32775,7 +32783,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.98618125000000001</v>
+        <v>0.93298000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32814,9 +32822,9 @@
         <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
         <v>0.92700000000000005</v>
       </c>
-      <c r="J13" s="10" t="str">
+      <c r="J13" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
-        <v/>
+        <v>0.50600000000000001</v>
       </c>
       <c r="K13" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
@@ -32832,7 +32840,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.85853804347826101</v>
+        <v>0.81936714975845426</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32871,9 +32879,9 @@
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
         <v>0.69375000000000009</v>
       </c>
-      <c r="J14" s="10" t="str">
+      <c r="J14" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
-        <v/>
+        <v>0.47315789473684211</v>
       </c>
       <c r="K14" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
@@ -32889,7 +32897,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.83411641081871357</v>
+        <v>0.79400990903183899</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32985,9 +32993,9 @@
         <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
         <v>0.93700000000000006</v>
       </c>
-      <c r="J16" s="10" t="str">
+      <c r="J16" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
-        <v/>
+        <v>0.50679999999999992</v>
       </c>
       <c r="K16" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
@@ -33003,7 +33011,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.94337500000000007</v>
+        <v>0.8948666666666667</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33042,9 +33050,9 @@
         <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
         <v>0.9951000000000001</v>
       </c>
-      <c r="J17" s="10" t="str">
+      <c r="J17" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
@@ -33060,7 +33068,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.94154436274509801</v>
+        <v>0.88470610021786489</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33099,9 +33107,9 @@
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
         <v>0.97124999999999995</v>
       </c>
-      <c r="J18" s="10" t="str">
+      <c r="J18" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
-        <v/>
+        <v>0.51</v>
       </c>
       <c r="K18" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
@@ -33117,7 +33125,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.90796874999999999</v>
+        <v>0.86375000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -33156,9 +33164,9 @@
         <f t="shared" si="1"/>
         <v>0.86230933333333337</v>
       </c>
-      <c r="J19" s="104" t="str">
+      <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.48211266038472805</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -33178,21 +33186,21 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="148" t="s">
+      <c r="A20" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="148"/>
-      <c r="C20" s="148"/>
-      <c r="D20" s="148"/>
-      <c r="E20" s="148"/>
-      <c r="F20" s="148"/>
-      <c r="G20" s="148"/>
-      <c r="H20" s="148"/>
-      <c r="I20" s="148"/>
-      <c r="J20" s="148"/>
-      <c r="K20" s="148"/>
-      <c r="L20" s="148"/>
-      <c r="M20" s="148"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="149"/>
+      <c r="I20" s="149"/>
+      <c r="J20" s="149"/>
+      <c r="K20" s="149"/>
+      <c r="L20" s="149"/>
+      <c r="M20" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -33217,16 +33225,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -33237,12 +33245,12 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
@@ -33268,11 +33276,11 @@
       </c>
       <c r="C5" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G20"))</f>
-        <v>0</v>
+        <v>8.4745149692412855E-2</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" ref="D5:D11" ca="1" si="0">IFERROR(C5/B5,0)</f>
-        <v>0</v>
+        <v>0.42372574846206423</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33302,11 +33310,11 @@
       </c>
       <c r="C7" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>0</v>
+        <v>5.7226666666666655E-2</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>0.71533333333333315</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33319,11 +33327,11 @@
       </c>
       <c r="C8" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>0</v>
+        <v>5.7226666666666655E-2</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>0.71533333333333315</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33378,10 +33386,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="123"/>
+      <c r="B13" s="124"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
@@ -33438,12 +33446,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="123"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -33468,7 +33476,7 @@
       </c>
       <c r="B23" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,1),$E$23:$E$37,0))</f>
-        <v>Alrededores</v>
+        <v>Calidad</v>
       </c>
       <c r="C23" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),1)</f>
@@ -33489,7 +33497,7 @@
       </c>
       <c r="B24" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,2),$E$23:$E$37,0))</f>
-        <v>Calidad</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C24" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),2)</f>
@@ -33522,7 +33530,7 @@
       </c>
       <c r="E25" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ8")*100000-8</f>
-        <v>32992</v>
+        <v>50992</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33531,7 +33539,7 @@
       </c>
       <c r="B26" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,4),$E$23:$E$37,0))</f>
-        <v>ETEI</v>
+        <v>Linea 2</v>
       </c>
       <c r="C26" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),4)</f>
@@ -33543,7 +33551,7 @@
       </c>
       <c r="E26" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ9")*100000-9</f>
-        <v>32991</v>
+        <v>50728.000000000007</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33552,7 +33560,7 @@
       </c>
       <c r="B27" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,5),$E$23:$E$37,0))</f>
-        <v>Equipos Auxiliares</v>
+        <v>Jarabes</v>
       </c>
       <c r="C27" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),5)</f>
@@ -33564,7 +33572,7 @@
       </c>
       <c r="E27" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ10")*100000-10</f>
-        <v>32990</v>
+        <v>42990</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33573,7 +33581,7 @@
       </c>
       <c r="B28" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,6),$E$23:$E$37,0))</f>
-        <v>Jarabes</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C28" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),6)</f>
@@ -33585,7 +33593,7 @@
       </c>
       <c r="E28" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ11")*100000-11</f>
-        <v>32989</v>
+        <v>50509</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33606,7 +33614,7 @@
       </c>
       <c r="E29" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ12")*100000-12</f>
-        <v>32988</v>
+        <v>50588</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33615,7 +33623,7 @@
       </c>
       <c r="B30" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,8),$E$23:$E$37,0))</f>
-        <v>Linea 2</v>
+        <v>Linea 4</v>
       </c>
       <c r="C30" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),8)</f>
@@ -33627,7 +33635,7 @@
       </c>
       <c r="E30" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ13")*100000-13</f>
-        <v>32987</v>
+        <v>49303.363636363632</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33648,7 +33656,7 @@
       </c>
       <c r="E31" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ14")*100000-14</f>
-        <v>32986</v>
+        <v>50665.999999999993</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33657,7 +33665,7 @@
       </c>
       <c r="B32" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,10),$E$23:$E$37,0))</f>
-        <v>Linea 4</v>
+        <v>ETEI</v>
       </c>
       <c r="C32" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),10)</f>
@@ -33669,7 +33677,7 @@
       </c>
       <c r="E32" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ15")*100000-15</f>
-        <v>32985</v>
+        <v>47300.789473684214</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33678,7 +33686,7 @@
       </c>
       <c r="B33" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,11),$E$23:$E$37,0))</f>
-        <v>Linea 5</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C33" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),11)</f>
@@ -33690,7 +33698,7 @@
       </c>
       <c r="E33" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ16")*100000-16</f>
-        <v>32984</v>
+        <v>49235.428571428565</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33699,7 +33707,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>Mantenimiento</v>
+        <v>Linea 5</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33711,7 +33719,7 @@
       </c>
       <c r="E34" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ17")*100000-17</f>
-        <v>32983</v>
+        <v>40840.142857142855</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33720,7 +33728,7 @@
       </c>
       <c r="B35" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,13),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>Alrededores</v>
       </c>
       <c r="C35" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),13)</f>
@@ -33732,7 +33740,7 @@
       </c>
       <c r="E35" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ18")*100000-18</f>
-        <v>32982</v>
+        <v>42982</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33753,7 +33761,7 @@
       </c>
       <c r="E36" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ19")*100000-19</f>
-        <v>32981</v>
+        <v>50981</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33778,10 +33786,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="123" t="s">
+      <c r="A39" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="123"/>
+      <c r="B39" s="124"/>
     </row>
     <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
@@ -33816,7 +33824,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.33</v>
+        <v>0.47197181635907953</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33872,22 +33880,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="148" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
     </row>
     <row r="3" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="99" t="s">
@@ -33969,9 +33977,9 @@
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
         <v>0.97525000000000006</v>
       </c>
-      <c r="J4" s="10" t="str">
+      <c r="J4" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
-        <v/>
+        <v>0.51</v>
       </c>
       <c r="K4" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
@@ -33987,7 +33995,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.99690624999999999</v>
+        <v>0.94280555555555567</v>
       </c>
       <c r="O4" s="106"/>
     </row>
@@ -34027,9 +34035,9 @@
         <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
         <v>0.97195000000000009</v>
       </c>
-      <c r="J5" s="10" t="str">
+      <c r="J5" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v/>
+        <v>0.5073700000000001</v>
       </c>
       <c r="K5" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
@@ -34045,7 +34053,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.98618125000000001</v>
+        <v>0.93298000000000003</v>
       </c>
       <c r="O5" s="106"/>
     </row>
@@ -34085,9 +34093,9 @@
         <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
         <v>1</v>
       </c>
-      <c r="J6" s="10" t="str">
+      <c r="J6" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
-        <v/>
+        <v>0.49251428571428568</v>
       </c>
       <c r="K6" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
@@ -34103,7 +34111,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.97178571428571425</v>
+        <v>0.91853333333333331</v>
       </c>
       <c r="O6" s="106"/>
     </row>
@@ -34143,9 +34151,9 @@
         <f>IFERROR(IF('Captura Agosto'!D6=0,"",'Captura Agosto'!AQ6),"")</f>
         <v>0.92995000000000005</v>
       </c>
-      <c r="J7" s="10" t="str">
+      <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
-        <v/>
+        <v>0.47000000000000003</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
@@ -34161,7 +34169,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.96124374999999995</v>
+        <v>0.90666111111111114</v>
       </c>
       <c r="O7" s="106"/>
     </row>
@@ -34201,9 +34209,9 @@
         <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
         <v>1</v>
       </c>
-      <c r="J8" s="10" t="str">
+      <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -34219,7 +34227,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.95687500000000003</v>
+        <v>0.89833333333333343</v>
       </c>
       <c r="O8" s="106"/>
     </row>
@@ -34259,9 +34267,9 @@
         <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
         <v>0.93700000000000006</v>
       </c>
-      <c r="J9" s="10" t="str">
+      <c r="J9" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
-        <v/>
+        <v>0.50679999999999992</v>
       </c>
       <c r="K9" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
@@ -34277,7 +34285,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.94337500000000007</v>
+        <v>0.8948666666666667</v>
       </c>
       <c r="O9" s="106"/>
     </row>
@@ -34317,9 +34325,9 @@
         <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
         <v>0.9951000000000001</v>
       </c>
-      <c r="J10" s="10" t="str">
+      <c r="J10" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="K10" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
@@ -34335,7 +34343,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.94154436274509801</v>
+        <v>0.88470610021786489</v>
       </c>
       <c r="O10" s="106"/>
     </row>
@@ -34375,9 +34383,9 @@
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
         <v>0.79</v>
       </c>
-      <c r="J11" s="10" t="str">
+      <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
-        <v/>
+        <v>0.50519999999999998</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
@@ -34393,7 +34401,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.92437500000000006</v>
+        <v>0.87780000000000014</v>
       </c>
       <c r="O11" s="106"/>
     </row>
@@ -34433,9 +34441,9 @@
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
         <v>0.97124999999999995</v>
       </c>
-      <c r="J12" s="10" t="str">
+      <c r="J12" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
-        <v/>
+        <v>0.51</v>
       </c>
       <c r="K12" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
@@ -34451,7 +34459,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.90796874999999999</v>
+        <v>0.86375000000000002</v>
       </c>
       <c r="O12" s="106"/>
     </row>
@@ -34491,9 +34499,9 @@
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
         <v>0.64826000000000006</v>
       </c>
-      <c r="J13" s="10" t="str">
+      <c r="J13" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
-        <v/>
+        <v>0.50679999999999992</v>
       </c>
       <c r="K13" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
@@ -34509,7 +34517,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.90103250000000012</v>
+        <v>0.85722888888888904</v>
       </c>
       <c r="O13" s="106"/>
     </row>
@@ -34549,9 +34557,9 @@
         <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
         <v>0.92700000000000005</v>
       </c>
-      <c r="J14" s="10" t="str">
+      <c r="J14" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
-        <v/>
+        <v>0.50600000000000001</v>
       </c>
       <c r="K14" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
@@ -34567,7 +34575,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.85853804347826101</v>
+        <v>0.81936714975845426</v>
       </c>
       <c r="O14" s="106"/>
     </row>
@@ -34607,9 +34615,9 @@
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
         <v>0.70295000000000007</v>
       </c>
-      <c r="J15" s="10" t="str">
+      <c r="J15" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v/>
+        <v>0.40857142857142859</v>
       </c>
       <c r="K15" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -34625,7 +34633,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.84808853021978026</v>
+        <v>0.7992532967032967</v>
       </c>
       <c r="O15" s="106"/>
     </row>
@@ -34665,9 +34673,9 @@
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
         <v>0.69375000000000009</v>
       </c>
-      <c r="J16" s="10" t="str">
+      <c r="J16" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
-        <v/>
+        <v>0.47315789473684211</v>
       </c>
       <c r="K16" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
@@ -34683,7 +34691,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.83411641081871357</v>
+        <v>0.79400990903183899</v>
       </c>
       <c r="O16" s="106"/>
     </row>
@@ -34723,9 +34731,9 @@
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
         <v>0.74768000000000001</v>
       </c>
-      <c r="J17" s="10" t="str">
+      <c r="J17" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
-        <v/>
+        <v>0.49316363636363636</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D13=0,"",'Captura Octubre'!AQ13),"")</f>
@@ -34741,7 +34749,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.82220999999999989</v>
+        <v>0.78564929292929286</v>
       </c>
       <c r="O17" s="106"/>
     </row>
@@ -34839,9 +34847,9 @@
         <f t="shared" si="1"/>
         <v>0.86230933333333348</v>
       </c>
-      <c r="J19" s="104" t="str">
+      <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.48211266038472811</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -34893,44 +34901,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-      <c r="R3" s="129"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34940,153 +34948,153 @@
         <f>Calculos!$B$2</f>
         <v>Septiembre</v>
       </c>
-      <c r="F4" s="130" t="s">
+      <c r="F4" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="130"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="128"/>
+      <c r="Q4" s="128"/>
+      <c r="R4" s="128"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="131" t="s">
+      <c r="B6" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131" t="s">
+      <c r="C6" s="129"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="131"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="131" t="s">
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="131"/>
-      <c r="L6" s="131"/>
-      <c r="M6" s="131" t="s">
+      <c r="K6" s="129"/>
+      <c r="L6" s="129"/>
+      <c r="M6" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="131"/>
-      <c r="O6" s="131"/>
-      <c r="P6" s="131" t="s">
+      <c r="N6" s="129"/>
+      <c r="O6" s="129"/>
+      <c r="P6" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="131"/>
-      <c r="R6" s="131"/>
+      <c r="Q6" s="129"/>
+      <c r="R6" s="129"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="131"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
-      <c r="N7" s="131"/>
-      <c r="O7" s="131"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="129"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="129"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="124">
+      <c r="B8" s="130">
         <f ca="1">Calculos!B44</f>
-        <v>0.33</v>
-      </c>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="125" t="str">
+        <v>0.47197181635907953</v>
+      </c>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="131" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="126">
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="132">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="126"/>
-      <c r="L8" s="126"/>
-      <c r="M8" s="127">
+      <c r="K8" s="132"/>
+      <c r="L8" s="132"/>
+      <c r="M8" s="125">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="127"/>
-      <c r="O8" s="127"/>
-      <c r="P8" s="128">
+      <c r="N8" s="125"/>
+      <c r="O8" s="125"/>
+      <c r="P8" s="126">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="128"/>
-      <c r="R8" s="128"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="124"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="127"/>
-      <c r="O9" s="127"/>
-      <c r="P9" s="128"/>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="128"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="131"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="125"/>
+      <c r="O9" s="125"/>
+      <c r="P9" s="126"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="126"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="126"/>
-      <c r="K10" s="126"/>
-      <c r="L10" s="126"/>
-      <c r="M10" s="127"/>
-      <c r="N10" s="127"/>
-      <c r="O10" s="127"/>
-      <c r="P10" s="128"/>
-      <c r="Q10" s="128"/>
-      <c r="R10" s="128"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
+      <c r="L10" s="132"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="125"/>
+      <c r="O10" s="125"/>
+      <c r="P10" s="126"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="126"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="123"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="123"/>
-      <c r="G12" s="123" t="s">
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="G12" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="123"/>
+      <c r="H12" s="124"/>
     </row>
     <row r="13" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
@@ -35105,7 +35113,7 @@
     <row r="14" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="str">
         <f ca="1">Calculos!B23</f>
-        <v>Alrededores</v>
+        <v>Calidad</v>
       </c>
       <c r="C14" s="21">
         <f ca="1">Calculos!C23</f>
@@ -35117,13 +35125,13 @@
       </c>
       <c r="H14" s="22">
         <f ca="1">Calculos!D5</f>
-        <v>0</v>
+        <v>0.42372574846206423</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="str">
         <f ca="1">Calculos!B24</f>
-        <v>Calidad</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C15" s="21">
         <f ca="1">Calculos!C24</f>
@@ -35153,13 +35161,13 @@
       </c>
       <c r="H16" s="22">
         <f ca="1">Calculos!D7</f>
-        <v>0</v>
+        <v>0.71533333333333315</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="str">
         <f ca="1">Calculos!B26</f>
-        <v>ETEI</v>
+        <v>Linea 2</v>
       </c>
       <c r="C17" s="21">
         <f ca="1">Calculos!C26</f>
@@ -35171,13 +35179,13 @@
       </c>
       <c r="H17" s="22">
         <f ca="1">Calculos!D8</f>
-        <v>0</v>
+        <v>0.71533333333333315</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="str">
         <f ca="1">Calculos!B27</f>
-        <v>Equipos Auxiliares</v>
+        <v>Jarabes</v>
       </c>
       <c r="C18" s="21">
         <f ca="1">Calculos!C27</f>
@@ -35195,7 +35203,7 @@
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="str">
         <f ca="1">Calculos!B28</f>
-        <v>Jarabes</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C19" s="21">
         <f ca="1">Calculos!C28</f>
@@ -35231,7 +35239,7 @@
     <row r="21" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="str">
         <f ca="1">Calculos!B30</f>
-        <v>Linea 2</v>
+        <v>Linea 4</v>
       </c>
       <c r="C21" s="21">
         <f ca="1">Calculos!C30</f>
@@ -35251,7 +35259,7 @@
     <row r="23" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="str">
         <f ca="1">Calculos!B32</f>
-        <v>Linea 4</v>
+        <v>ETEI</v>
       </c>
       <c r="C23" s="21">
         <f ca="1">Calculos!C32</f>
@@ -35261,7 +35269,7 @@
     <row r="24" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="str">
         <f ca="1">Calculos!B33</f>
-        <v>Linea 5</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C24" s="21">
         <f ca="1">Calculos!C33</f>
@@ -35271,7 +35279,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>Mantenimiento</v>
+        <v>Linea 5</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -35281,7 +35289,7 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="str">
         <f ca="1">Calculos!B35</f>
-        <v>Materias Primas</v>
+        <v>Alrededores</v>
       </c>
       <c r="C26" s="21">
         <f ca="1">Calculos!C35</f>
@@ -35337,6 +35345,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35346,11 +35359,6 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35380,61 +35388,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="143" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="135" t="s">
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="144" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="136" t="s">
+      <c r="B4" s="145" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="136"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="136"/>
-      <c r="M4" s="136"/>
-      <c r="N4" s="136"/>
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
+      <c r="O4" s="145"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="145"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="137" t="str">
+      <c r="B5" s="146" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  SEPTIEMBRE 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="137"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="137"/>
-      <c r="J5" s="137"/>
-      <c r="K5" s="137"/>
-      <c r="L5" s="137"/>
-      <c r="M5" s="137"/>
-      <c r="N5" s="137"/>
-      <c r="O5" s="137"/>
-      <c r="P5" s="137"/>
-      <c r="Q5" s="137"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="146"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="146"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="146"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35445,7 +35453,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="138" t="str">
+      <c r="A7" s="133" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>SEPTIEMBRE</v>
       </c>
@@ -35462,13 +35470,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="138"/>
-      <c r="G8" s="139">
+      <c r="A8" s="133"/>
+      <c r="G8" s="134">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="139"/>
-      <c r="I8" s="139"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="134"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35478,15 +35486,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="138"/>
-      <c r="F9" s="140">
+      <c r="A9" s="133"/>
+      <c r="F9" s="135">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35496,17 +35504,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="138"/>
-      <c r="E10" s="141">
+      <c r="A10" s="133"/>
+      <c r="E10" s="136">
         <f ca="1">X33</f>
         <v>0</v>
       </c>
-      <c r="F10" s="141"/>
-      <c r="G10" s="141"/>
-      <c r="H10" s="141"/>
-      <c r="I10" s="141"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="141"/>
+      <c r="F10" s="136"/>
+      <c r="G10" s="136"/>
+      <c r="H10" s="136"/>
+      <c r="I10" s="136"/>
+      <c r="J10" s="136"/>
+      <c r="K10" s="136"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35516,19 +35524,19 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="138"/>
-      <c r="D11" s="142">
+      <c r="A11" s="133"/>
+      <c r="D11" s="137">
         <f ca="1">X34</f>
         <v>0</v>
       </c>
-      <c r="E11" s="142"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="142"/>
-      <c r="I11" s="142"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="142"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35538,21 +35546,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="138"/>
-      <c r="C12" s="143">
+      <c r="A12" s="133"/>
+      <c r="C12" s="138">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="143"/>
-      <c r="E12" s="143"/>
-      <c r="F12" s="143"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="143"/>
-      <c r="L12" s="143"/>
-      <c r="M12" s="143"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="138"/>
+      <c r="G12" s="138"/>
+      <c r="H12" s="138"/>
+      <c r="I12" s="138"/>
+      <c r="J12" s="138"/>
+      <c r="K12" s="138"/>
+      <c r="L12" s="138"/>
+      <c r="M12" s="138"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35562,75 +35570,75 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="138"/>
-      <c r="B13" s="144">
+      <c r="A13" s="133"/>
+      <c r="B13" s="139">
         <f ca="1">X36</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
+        <v>17</v>
+      </c>
+      <c r="C13" s="139"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="139"/>
+      <c r="K13" s="139"/>
+      <c r="L13" s="139"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="139"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
       <c r="Q13" s="34">
         <f>Y36</f>
-        <v>463</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="138"/>
-      <c r="B14" s="145">
+      <c r="A14" s="133"/>
+      <c r="B14" s="140">
         <f ca="1">X37</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="145"/>
-      <c r="D14" s="145"/>
-      <c r="E14" s="145"/>
-      <c r="F14" s="145"/>
-      <c r="G14" s="145"/>
-      <c r="H14" s="145"/>
-      <c r="I14" s="145"/>
-      <c r="J14" s="145"/>
-      <c r="K14" s="145"/>
-      <c r="L14" s="145"/>
-      <c r="M14" s="145"/>
-      <c r="N14" s="145"/>
+        <v>89</v>
+      </c>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="140"/>
+      <c r="M14" s="140"/>
+      <c r="N14" s="140"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
       <c r="Q14" s="34">
         <f t="shared" si="0"/>
-        <v>1924</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="132" t="s">
+      <c r="S16" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="132"/>
-      <c r="U16" s="132"/>
-      <c r="V16" s="132"/>
+      <c r="T16" s="141"/>
+      <c r="U16" s="141"/>
+      <c r="V16" s="141"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S18" s="35">
         <f ca="1">IF(T20="","—",INT(TODAY()-T20))</f>
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="U18" s="35">
         <f ca="1">IF(V20="","—",INT(TODAY()-V20))</f>
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35659,11 +35667,11 @@
     <row r="22" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S22" s="35">
         <f ca="1">IF(T24="","—",INT(TODAY()-T24))</f>
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="U22" s="35">
         <f ca="1">IF(V24="","—",INT(TODAY()-V24))</f>
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35691,42 +35699,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="133" t="s">
+      <c r="B27" s="142" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="133"/>
-      <c r="D27" s="133"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="133"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="133"/>
-      <c r="L27" s="133"/>
-      <c r="M27" s="133"/>
-      <c r="N27" s="133"/>
-      <c r="O27" s="133"/>
-      <c r="P27" s="133"/>
-      <c r="Q27" s="133"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="142"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="142"/>
+      <c r="G27" s="142"/>
+      <c r="H27" s="142"/>
+      <c r="I27" s="142"/>
+      <c r="J27" s="142"/>
+      <c r="K27" s="142"/>
+      <c r="L27" s="142"/>
+      <c r="M27" s="142"/>
+      <c r="N27" s="142"/>
+      <c r="O27" s="142"/>
+      <c r="P27" s="142"/>
+      <c r="Q27" s="142"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="133"/>
-      <c r="C28" s="133"/>
-      <c r="D28" s="133"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="133"/>
-      <c r="J28" s="133"/>
-      <c r="K28" s="133"/>
-      <c r="L28" s="133"/>
-      <c r="M28" s="133"/>
-      <c r="N28" s="133"/>
-      <c r="O28" s="133"/>
-      <c r="P28" s="133"/>
-      <c r="Q28" s="133"/>
+      <c r="B28" s="142"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="142"/>
+      <c r="J28" s="142"/>
+      <c r="K28" s="142"/>
+      <c r="L28" s="142"/>
+      <c r="M28" s="142"/>
+      <c r="N28" s="142"/>
+      <c r="O28" s="142"/>
+      <c r="P28" s="142"/>
+      <c r="Q28" s="142"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35810,11 +35818,11 @@
       </c>
       <c r="X36" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC3"),0)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y36" s="41">
         <f>'Captura Enero'!BC3+'Captura Febrero'!BC3+'Captura Marzo'!BC3+'Captura Abril'!BC3+'Captura Mayo'!BC3+'Captura Junio'!BC3+'Captura Julio'!BC3+'Captura Agosto'!BC3+'Captura Septiembre'!BC3+'Captura Octubre'!BC3+'Captura Noviembre'!BC3+'Captura Diciembre'!BC3</f>
-        <v>463</v>
+        <v>480</v>
       </c>
     </row>
     <row r="37" spans="23:25" x14ac:dyDescent="0.35">
@@ -35823,15 +35831,21 @@
       </c>
       <c r="X37" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC4"),0)</f>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="Y37" s="41">
         <f>'Captura Enero'!BC4+'Captura Febrero'!BC4+'Captura Marzo'!BC4+'Captura Abril'!BC4+'Captura Mayo'!BC4+'Captura Junio'!BC4+'Captura Julio'!BC4+'Captura Agosto'!BC4+'Captura Septiembre'!BC4+'Captura Octubre'!BC4+'Captura Noviembre'!BC4+'Captura Diciembre'!BC4</f>
-        <v>1924</v>
+        <v>2013</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35840,12 +35854,6 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -35880,26 +35888,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="124" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123"/>
-      <c r="H4" s="123" t="s">
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="H4" s="124" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="123"/>
+      <c r="I4" s="124"/>
     </row>
     <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
@@ -36160,13 +36168,13 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="124" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="123"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
       <c r="H16" s="8">
         <v>11</v>
       </c>
@@ -36249,13 +36257,13 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="123" t="s">
+      <c r="B21" s="124" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="123"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="124"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
@@ -36302,13 +36310,13 @@
       <c r="F25" s="52"/>
     </row>
     <row r="27" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="123" t="s">
+      <c r="B27" s="124" t="s">
         <v>149</v>
       </c>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="123"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
     </row>
     <row r="28" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
@@ -36377,13 +36385,13 @@
       <c r="F33" s="52"/>
     </row>
     <row r="35" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="123" t="s">
+      <c r="B35" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="123"/>
-      <c r="D35" s="123"/>
-      <c r="E35" s="123"/>
-      <c r="F35" s="123"/>
+      <c r="C35" s="124"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="124"/>
     </row>
     <row r="36" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="7" t="s">
@@ -36480,62 +36488,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36544,20 +36552,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36605,66 +36613,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36876,10 +36884,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39446,16 +39454,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93297435897435899</v>
@@ -39627,9 +39635,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39656,11 +39664,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39718,12 +39726,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39738,6 +39740,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39819,62 +39827,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39883,20 +39891,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39944,66 +39952,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -40215,10 +40223,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42785,16 +42793,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42961,9 +42969,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42990,11 +42998,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -43052,12 +43060,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -43072,6 +43074,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -43153,62 +43161,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -43217,20 +43225,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -43278,66 +43286,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43549,10 +43557,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -46119,16 +46127,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46295,9 +46303,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46324,11 +46332,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46386,12 +46394,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46406,6 +46408,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46487,62 +46495,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="107" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="114"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="114"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="115" t="s">
+      <c r="AS1" s="108" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="115"/>
-      <c r="AU1" s="115"/>
-      <c r="AV1" s="115"/>
-      <c r="AW1" s="115"/>
-      <c r="AX1" s="115"/>
-      <c r="AY1" s="115"/>
-      <c r="AZ1" s="115"/>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116" t="s">
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="108"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="109" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="116"/>
+      <c r="BC1" s="109"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="110" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46551,20 +46559,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="118" t="s">
+      <c r="AT2" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="118"/>
-      <c r="AV2" s="118"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="119" t="s">
+      <c r="AX2" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46612,66 +46620,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="111" t="s">
+      <c r="D4" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111" t="s">
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111" t="s">
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111" t="s">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111" t="s">
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="111"/>
-      <c r="W4" s="112" t="s">
+      <c r="V4" s="118"/>
+      <c r="W4" s="119" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="111" t="s">
+      <c r="X4" s="119"/>
+      <c r="Y4" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="111"/>
-      <c r="AD4" s="112" t="s">
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="112"/>
-      <c r="AF4" s="112"/>
-      <c r="AG4" s="112"/>
-      <c r="AH4" s="112"/>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112"/>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112"/>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="113" t="s">
+      <c r="AE4" s="119"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="119"/>
+      <c r="AH4" s="119"/>
+      <c r="AI4" s="119"/>
+      <c r="AJ4" s="119"/>
+      <c r="AK4" s="119"/>
+      <c r="AL4" s="119"/>
+      <c r="AM4" s="119"/>
+      <c r="AN4" s="119"/>
+      <c r="AO4" s="119"/>
+      <c r="AP4" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="113"/>
+      <c r="AQ4" s="120"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46883,10 +46891,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="107" t="s">
+      <c r="BB5" s="114" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="107"/>
+      <c r="BC5" s="114"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49453,16 +49461,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="108" t="s">
+      <c r="AS19" s="115" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="108"/>
-      <c r="AU19" s="108"/>
-      <c r="AV19" s="108"/>
-      <c r="AW19" s="108"/>
-      <c r="AX19" s="108"/>
-      <c r="AY19" s="108"/>
-      <c r="AZ19" s="108"/>
+      <c r="AT19" s="115"/>
+      <c r="AU19" s="115"/>
+      <c r="AV19" s="115"/>
+      <c r="AW19" s="115"/>
+      <c r="AX19" s="115"/>
+      <c r="AY19" s="115"/>
+      <c r="AZ19" s="115"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49629,9 +49637,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="109"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49658,11 +49666,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="110" t="s">
+      <c r="A23" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49720,12 +49728,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49740,6 +49742,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49809,17 +49817,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -50066,6 +50063,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
   <ds:schemaRefs>
@@ -50075,23 +50083,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
-    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76AB9A25-5769-416B-8E9A-2215F01CC611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50108,4 +50099,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C61EE5C6-F26D-4FF2-A94B-2F09B6B1F642}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CC1B93-9E4F-4CF5-93D8-DC6F21136255}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2131,6 +2131,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2255,12 +2261,6 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="21" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3282,40 +3282,40 @@
                   <c:v>Calidad</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Centro de Distribucion</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Materias Primas</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>Centro de Distribucion</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>Linea 2</c:v>
+                  <c:v>Linea 3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jarabes</c:v>
+                  <c:v>Equipos Auxiliares</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Equipos Auxiliares</c:v>
+                  <c:v>Jarabes</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Linea 1</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>Linea 2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Mantenimiento</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Linea 4</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>Linea 3</c:v>
+                <c:pt idx="10">
+                  <c:v>Alrededores</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>ETEI</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>Mantenimiento</c:v>
-                </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Linea 5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alrededores</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Almacen de Repuestos</c:v>
@@ -3696,16 +3696,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.42372574846206423</c:v>
+                  <c:v>0.4863333333333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.71533333333333315</c:v>
+                  <c:v>0.84466666666666668</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.71533333333333315</c:v>
+                  <c:v>0.84466666666666668</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -4383,7 +4383,7 @@
                   <c:v>0.86230933333333326</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.47197181635907953</c:v>
+                  <c:v>0.56254666666666664</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5119,38 +5119,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="122" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
+      <c r="B3" s="124" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
     </row>
     <row r="4" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="122"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="122"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
     </row>
     <row r="5" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="122"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
     </row>
     <row r="6" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
     </row>
     <row r="7" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="123" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
+      <c r="B7" s="125" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
     </row>
     <row r="10" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C13" s="4">
         <f ca="1">TODAY()</f>
-        <v>46279</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5204,72 +5204,72 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="124" t="s">
+      <c r="B18" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="126"/>
     </row>
     <row r="19" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="121" t="s">
+      <c r="C19" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="123"/>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="121" t="s">
+      <c r="C20" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
     </row>
     <row r="21" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="121" t="s">
+      <c r="C21" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
     </row>
     <row r="22" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="121" t="s">
+      <c r="C22" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="121"/>
-      <c r="E22" s="121"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="123"/>
     </row>
     <row r="23" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="121" t="s">
+      <c r="C23" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="123"/>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="121" t="s">
+      <c r="C24" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5310,62 +5310,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5374,20 +5374,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5435,66 +5435,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5706,10 +5706,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8276,16 +8276,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.8793333333333333</v>
@@ -8452,9 +8452,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8481,11 +8481,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8644,62 +8644,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8708,20 +8708,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8769,66 +8769,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -9040,10 +9040,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11610,16 +11610,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11786,9 +11786,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11815,11 +11815,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11980,62 +11980,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -12044,20 +12044,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -12105,66 +12105,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12376,10 +12376,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14946,16 +14946,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -15122,9 +15122,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -15151,11 +15151,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -15318,62 +15318,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15382,20 +15382,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15443,66 +15443,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15714,10 +15714,10 @@
         <f>'Captura Agosto'!AQ7</f>
         <v>0.64449999999999996</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -18284,16 +18284,16 @@
         <v>0.97124999999999995</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.86230933333333326</v>
@@ -18460,9 +18460,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18489,11 +18489,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18655,90 +18655,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="113" t="s">
+      <c r="G2" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18779,81 +18779,81 @@
         <v>180</v>
       </c>
       <c r="BC3" s="69">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:55" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
-      <c r="AS4" s="150" t="str">
+      <c r="AS4" s="107" t="str">
         <f>'Captura Septiembre'!B6</f>
         <v>Almacen de Repuestos</v>
       </c>
       <c r="AT4" s="72">
         <f>'Captura Septiembre'!K6+'Captura Septiembre'!N6+'Captura Septiembre'!Q6</f>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="AU4" s="72">
         <f>'Captura Septiembre'!T6</f>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="AW4" s="72">
         <f>'Captura Septiembre'!G6</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" s="72">
         <f>'Captura Septiembre'!X6</f>
@@ -18881,13 +18881,13 @@
       </c>
       <c r="BA4" s="74">
         <f>'Captura Septiembre'!AQ6</f>
-        <v>0.47000000000000003</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="BB4" s="68" t="s">
         <v>191</v>
       </c>
       <c r="BC4" s="75">
-        <v>89</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:55" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="AT5" s="80">
         <f>'Captura Septiembre'!K7+'Captura Septiembre'!N7+'Captura Septiembre'!Q7</f>
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="AU5" s="80">
         <f>'Captura Septiembre'!T7</f>
@@ -19039,7 +19039,7 @@
       </c>
       <c r="AW5" s="80">
         <f>'Captura Septiembre'!G7</f>
-        <v>0</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="AX5" s="80">
         <f>'Captura Septiembre'!X7</f>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="BA5" s="82">
         <f>'Captura Septiembre'!AQ7</f>
-        <v>0.33</v>
-      </c>
-      <c r="BB5" s="114" t="s">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -19074,18 +19074,18 @@
         <v>Fredy Fuentes</v>
       </c>
       <c r="D6" s="85">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E6" s="85">
         <v>0</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ref="F6:F20" si="0">AVERAGE(D6,E6)</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="86">
         <f>F6*Parametros!$E$6</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H6" s="87">
         <v>38</v>
@@ -19111,14 +19111,14 @@
         <v>0.08</v>
       </c>
       <c r="O6" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q6" s="86">
         <f>IF(P6="NO",0,O6*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R6" s="85">
         <v>0</v>
@@ -19202,11 +19202,11 @@
       </c>
       <c r="AP6" s="11">
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
-        <v>0.47000000000000003</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AQ6" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6-AN6-IF(AO6="SI",Parametros!$E$33,0)))</f>
-        <v>0.47000000000000003</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AR6" s="58"/>
       <c r="AS6" s="71" t="str">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="AT6" s="72">
         <f>'Captura Septiembre'!K8+'Captura Septiembre'!N8+'Captura Septiembre'!Q8</f>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="AU6" s="72">
         <f>'Captura Septiembre'!T8</f>
@@ -19243,7 +19243,7 @@
       </c>
       <c r="BA6" s="74">
         <f>'Captura Septiembre'!AQ8</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="BB6" s="58"/>
       <c r="BC6" s="58"/>
@@ -19260,18 +19260,18 @@
         <v>Carlos Chavez</v>
       </c>
       <c r="D7" s="85">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="E7" s="85">
         <v>0</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="G7" s="86">
         <f>F7*Parametros!$E$6</f>
-        <v>0</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="H7" s="87">
         <v>38</v>
@@ -19287,24 +19287,24 @@
         <v>0.08</v>
       </c>
       <c r="L7" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N7" s="86">
         <f>IF(M7="NO",0,L7*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O7" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q7" s="86">
         <f>IF(P7="NO",0,O7*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R7" s="85">
         <v>0</v>
@@ -19388,20 +19388,20 @@
       </c>
       <c r="AP7" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="AQ7" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7-AN7-IF(AO7="SI",Parametros!$E$33,0)))</f>
-        <v>0.33</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="AR7" s="58"/>
-      <c r="AS7" s="151" t="str">
+      <c r="AS7" s="108" t="str">
         <f>'Captura Septiembre'!B9</f>
         <v>Centro de Distribucion</v>
       </c>
       <c r="AT7" s="80">
         <f>'Captura Septiembre'!K9+'Captura Septiembre'!N9+'Captura Septiembre'!Q9</f>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="AU7" s="80">
         <f>'Captura Septiembre'!T9</f>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="AW7" s="80">
         <f>'Captura Septiembre'!G9</f>
-        <v>9.7370000000000012E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AX7" s="80">
         <f>'Captura Septiembre'!X9</f>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="BA7" s="82">
         <f>'Captura Septiembre'!AQ9</f>
-        <v>0.5073700000000001</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="BB7" s="58"/>
       <c r="BC7" s="58"/>
@@ -19483,14 +19483,14 @@
         <v>0.08</v>
       </c>
       <c r="O8" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q8" s="86">
         <f>IF(P8="NO",0,O8*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R8" s="85">
         <v>0</v>
@@ -19574,11 +19574,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AQ8" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8-AN8-IF(AO8="SI",Parametros!$E$33,0)))</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AR8" s="58"/>
       <c r="AS8" s="71" t="str">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="AT8" s="72">
         <f>'Captura Septiembre'!K10+'Captura Septiembre'!N10+'Captura Septiembre'!Q10</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU8" s="72">
         <f>'Captura Septiembre'!T10</f>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="BA8" s="74">
         <f>'Captura Septiembre'!AQ10</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="BB8" s="58"/>
       <c r="BC8" s="58"/>
@@ -19632,18 +19632,18 @@
         <v>Jimmy Velasquez</v>
       </c>
       <c r="D9" s="85">
-        <v>0.97370000000000001</v>
+        <v>1</v>
       </c>
       <c r="E9" s="85">
         <v>0</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="0"/>
-        <v>0.48685</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="86">
         <f>F9*Parametros!$E$6</f>
-        <v>9.7370000000000012E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H9" s="87">
         <v>38</v>
@@ -19669,14 +19669,14 @@
         <v>0.08</v>
       </c>
       <c r="O9" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q9" s="86">
         <f>IF(P9="NO",0,O9*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R9" s="85">
         <v>0</v>
@@ -19760,11 +19760,11 @@
       </c>
       <c r="AP9" s="11">
         <f t="shared" si="3"/>
-        <v>0.5073700000000001</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AQ9" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9-AN9-IF(AO9="SI",Parametros!$E$33,0)))</f>
-        <v>0.5073700000000001</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AR9" s="58"/>
       <c r="AS9" s="79" t="str">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="AT9" s="80">
         <f>'Captura Septiembre'!K11+'Captura Septiembre'!N11+'Captura Septiembre'!Q11</f>
-        <v>0.1552</v>
+        <v>0.23520000000000002</v>
       </c>
       <c r="AU9" s="80">
         <f>'Captura Septiembre'!T11</f>
@@ -19801,7 +19801,7 @@
       </c>
       <c r="BA9" s="82">
         <f>'Captura Septiembre'!AQ11</f>
-        <v>0.50519999999999998</v>
+        <v>0.58519999999999994</v>
       </c>
       <c r="BB9" s="58"/>
       <c r="BC9" s="58"/>
@@ -19855,14 +19855,14 @@
         <v>0</v>
       </c>
       <c r="O10" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q10" s="86">
         <f>IF(P10="NO",0,O10*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R10" s="85">
         <v>0</v>
@@ -19946,11 +19946,11 @@
       </c>
       <c r="AP10" s="11">
         <f t="shared" si="3"/>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AQ10" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10-AN10-IF(AO10="SI",Parametros!$E$33,0)))</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AR10" s="58"/>
       <c r="AS10" s="71" t="str">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="AT10" s="72">
         <f>'Captura Septiembre'!K12+'Captura Septiembre'!N12+'Captura Septiembre'!Q12</f>
-        <v>0.156</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="AU10" s="72">
         <f>'Captura Septiembre'!T12</f>
@@ -19987,7 +19987,7 @@
       </c>
       <c r="BA10" s="74">
         <f>'Captura Septiembre'!AQ12</f>
-        <v>0.50600000000000001</v>
+        <v>0.58200000000000007</v>
       </c>
       <c r="BB10" s="58"/>
       <c r="BC10" s="58"/>
@@ -20041,14 +20041,14 @@
         <v>7.5200000000000003E-2</v>
       </c>
       <c r="O11" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q11" s="86">
         <f>IF(P11="NO",0,O11*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R11" s="85">
         <v>0</v>
@@ -20132,11 +20132,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.50519999999999998</v>
+        <v>0.58519999999999994</v>
       </c>
       <c r="AQ11" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11-AN11-IF(AO11="SI",Parametros!$E$33,0)))</f>
-        <v>0.50519999999999998</v>
+        <v>0.58519999999999994</v>
       </c>
       <c r="AR11" s="58"/>
       <c r="AS11" s="79" t="str">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="AT11" s="80">
         <f>'Captura Septiembre'!K13+'Captura Septiembre'!N13+'Captura Septiembre'!Q13</f>
-        <v>0.15679999999999999</v>
+        <v>0.23039999999999999</v>
       </c>
       <c r="AU11" s="80">
         <f>'Captura Septiembre'!T13</f>
@@ -20157,7 +20157,7 @@
       </c>
       <c r="AW11" s="80">
         <f>'Captura Septiembre'!G13</f>
-        <v>8.6363636363636365E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" s="80">
         <f>'Captura Septiembre'!X13</f>
@@ -20173,7 +20173,7 @@
       </c>
       <c r="BA11" s="82">
         <f>'Captura Septiembre'!AQ13</f>
-        <v>0.49316363636363636</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="BB11" s="58"/>
       <c r="BC11" s="58"/>
@@ -20227,14 +20227,14 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="O12" s="85">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="P12" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q12" s="86">
         <f>IF(P12="NO",0,O12*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="R12" s="85">
         <v>0</v>
@@ -20318,11 +20318,11 @@
       </c>
       <c r="AP12" s="11">
         <f t="shared" si="3"/>
-        <v>0.50600000000000001</v>
+        <v>0.58200000000000007</v>
       </c>
       <c r="AQ12" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12-AN12-IF(AO12="SI",Parametros!$E$33,0)))</f>
-        <v>0.50600000000000001</v>
+        <v>0.58200000000000007</v>
       </c>
       <c r="AR12" s="58"/>
       <c r="AS12" s="71" t="str">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="AT12" s="72">
         <f>'Captura Septiembre'!K14+'Captura Septiembre'!N14+'Captura Septiembre'!Q14</f>
-        <v>0.15679999999999999</v>
+        <v>0.23039999999999999</v>
       </c>
       <c r="AU12" s="72">
         <f>'Captura Septiembre'!T14</f>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="BA12" s="74">
         <f>'Captura Septiembre'!AQ14</f>
-        <v>0.50679999999999992</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="BB12" s="58"/>
       <c r="BC12" s="58"/>
@@ -20376,18 +20376,18 @@
         <v>Amilcar Ralda</v>
       </c>
       <c r="D13" s="85">
-        <v>0.86363636363636365</v>
+        <v>1</v>
       </c>
       <c r="E13" s="85">
         <v>0</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="0"/>
-        <v>0.43181818181818182</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="86">
         <f>F13*Parametros!$E$6</f>
-        <v>8.6363636363636365E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H13" s="87">
         <v>38</v>
@@ -20413,14 +20413,14 @@
         <v>7.6799999999999993E-2</v>
       </c>
       <c r="O13" s="85">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="P13" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q13" s="86">
         <f>IF(P13="NO",0,O13*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.3599999999999999E-2</v>
       </c>
       <c r="R13" s="85">
         <v>0</v>
@@ -20504,11 +20504,11 @@
       </c>
       <c r="AP13" s="11">
         <f t="shared" si="3"/>
-        <v>0.49316363636363636</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="AQ13" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13-AN13-IF(AO13="SI",Parametros!$E$33,0)))</f>
-        <v>0.49316363636363636</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="AR13" s="58"/>
       <c r="AS13" s="79" t="str">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="AT13" s="80">
         <f>'Captura Septiembre'!K15+'Captura Septiembre'!N15+'Captura Septiembre'!Q15</f>
-        <v>0.16</v>
+        <v>0.23680000000000001</v>
       </c>
       <c r="AU13" s="80">
         <f>'Captura Septiembre'!T15</f>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="AW13" s="80">
         <f>'Captura Septiembre'!G15</f>
-        <v>6.3157894736842107E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AX13" s="80">
         <f>'Captura Septiembre'!X15</f>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="BA13" s="82">
         <f>'Captura Septiembre'!AQ15</f>
-        <v>0.47315789473684211</v>
+        <v>0.58679999999999999</v>
       </c>
       <c r="BB13" s="58"/>
       <c r="BC13" s="58"/>
@@ -20599,14 +20599,14 @@
         <v>7.6799999999999993E-2</v>
       </c>
       <c r="O14" s="85">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="P14" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q14" s="86">
         <f>IF(P14="NO",0,O14*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.3599999999999999E-2</v>
       </c>
       <c r="R14" s="85">
         <v>0</v>
@@ -20690,11 +20690,11 @@
       </c>
       <c r="AP14" s="11">
         <f t="shared" si="3"/>
-        <v>0.50679999999999992</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="AQ14" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14-AN14-IF(AO14="SI",Parametros!$E$33,0)))</f>
-        <v>0.50679999999999992</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="AR14" s="58"/>
       <c r="AS14" s="71" t="str">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="AT14" s="72">
         <f>'Captura Septiembre'!K16+'Captura Septiembre'!N16+'Captura Septiembre'!Q16</f>
-        <v>0.15679999999999999</v>
+        <v>0.23359999999999997</v>
       </c>
       <c r="AU14" s="72">
         <f>'Captura Septiembre'!T16</f>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="AW14" s="72">
         <f>'Captura Septiembre'!G16</f>
-        <v>8.5714285714285715E-2</v>
+        <v>9.3000000000000013E-2</v>
       </c>
       <c r="AX14" s="72">
         <f>'Captura Septiembre'!X16</f>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="BA14" s="74">
         <f>'Captura Septiembre'!AQ16</f>
-        <v>0.49251428571428568</v>
+        <v>0.5766</v>
       </c>
       <c r="BB14" s="58"/>
       <c r="BC14" s="58"/>
@@ -20748,18 +20748,18 @@
         <v>Mario Ramos</v>
       </c>
       <c r="D15" s="85">
-        <v>0.63157894736842102</v>
+        <v>1</v>
       </c>
       <c r="E15" s="85">
         <v>0</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
-        <v>0.31578947368421051</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="86">
         <f>F15*Parametros!$E$6</f>
-        <v>6.3157894736842107E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H15" s="87">
         <v>38</v>
@@ -20785,14 +20785,14 @@
         <v>0.08</v>
       </c>
       <c r="O15" s="85">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="P15" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q15" s="86">
         <f>IF(P15="NO",0,O15*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="R15" s="85">
         <v>0</v>
@@ -20876,11 +20876,11 @@
       </c>
       <c r="AP15" s="11">
         <f t="shared" si="3"/>
-        <v>0.47315789473684211</v>
+        <v>0.58679999999999999</v>
       </c>
       <c r="AQ15" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15-AN15-IF(AO15="SI",Parametros!$E$33,0)))</f>
-        <v>0.47315789473684211</v>
+        <v>0.58679999999999999</v>
       </c>
       <c r="AR15" s="58"/>
       <c r="AS15" s="79" t="str">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="AT15" s="80">
         <f>'Captura Septiembre'!K17+'Captura Septiembre'!N17+'Captura Septiembre'!Q17</f>
-        <v>0.08</v>
+        <v>0.15679999999999999</v>
       </c>
       <c r="AU15" s="80">
         <f>'Captura Septiembre'!T17</f>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="AW15" s="80">
         <f>'Captura Septiembre'!G17</f>
-        <v>7.857142857142857E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AX15" s="80">
         <f>'Captura Septiembre'!X17</f>
@@ -20913,11 +20913,11 @@
       </c>
       <c r="AZ15" s="81">
         <f>-'Captura Septiembre'!AN17</f>
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="BA15" s="82">
         <f>'Captura Septiembre'!AQ17</f>
-        <v>0.40857142857142859</v>
+        <v>0.3567999999999999</v>
       </c>
       <c r="BB15" s="58"/>
       <c r="BC15" s="58"/>
@@ -20934,18 +20934,18 @@
         <v>Mario Ramos</v>
       </c>
       <c r="D16" s="85">
-        <v>0.8571428571428571</v>
+        <v>0.93</v>
       </c>
       <c r="E16" s="85">
         <v>0</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="G16" s="86">
         <f>F16*Parametros!$E$6</f>
-        <v>8.5714285714285715E-2</v>
+        <v>9.3000000000000013E-2</v>
       </c>
       <c r="H16" s="87">
         <v>38</v>
@@ -20971,14 +20971,14 @@
         <v>7.6799999999999993E-2</v>
       </c>
       <c r="O16" s="85">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="P16" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q16" s="86">
         <f>IF(P16="NO",0,O16*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="R16" s="85">
         <v>0</v>
@@ -21062,11 +21062,11 @@
       </c>
       <c r="AP16" s="11">
         <f t="shared" si="3"/>
-        <v>0.49251428571428568</v>
+        <v>0.5766</v>
       </c>
       <c r="AQ16" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16-AN16-IF(AO16="SI",Parametros!$E$33,0)))</f>
-        <v>0.49251428571428568</v>
+        <v>0.5766</v>
       </c>
       <c r="AR16" s="58"/>
       <c r="AS16" s="71" t="str">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="AT16" s="72">
         <f>'Captura Septiembre'!K18+'Captura Septiembre'!N18+'Captura Septiembre'!Q18</f>
-        <v>0.08</v>
+        <v>0.23039999999999999</v>
       </c>
       <c r="AU16" s="72">
         <f>'Captura Septiembre'!T18</f>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="BA16" s="74">
         <f>'Captura Septiembre'!AQ18</f>
-        <v>0.43</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="BB16" s="58"/>
       <c r="BC16" s="58"/>
@@ -21120,18 +21120,18 @@
         <v>Roy Luarca</v>
       </c>
       <c r="D17" s="85">
-        <v>0.7857142857142857</v>
+        <v>1</v>
       </c>
       <c r="E17" s="85">
         <v>0</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>0.39285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="86">
         <f>F17*Parametros!$E$6</f>
-        <v>7.857142857142857E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="87">
         <v>38</v>
@@ -21157,14 +21157,14 @@
         <v>0</v>
       </c>
       <c r="O17" s="85">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="P17" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q17" s="86">
         <f>IF(P17="NO",0,O17*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="R17" s="85">
         <v>0</v>
@@ -21221,7 +21221,7 @@
         <v>222</v>
       </c>
       <c r="AH17" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" s="88" t="s">
         <v>222</v>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="AN17" s="89">
         <f>AD17*Parametros!$E$28+AF17*Parametros!$E$29+AH17*Parametros!$E$30+AJ17*Parametros!$E$31+AL17*Parametros!$E$32</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AO17" s="12" t="str">
         <f t="shared" si="2"/>
@@ -21248,11 +21248,11 @@
       </c>
       <c r="AP17" s="11">
         <f t="shared" si="3"/>
-        <v>0.40857142857142859</v>
+        <v>0.50679999999999992</v>
       </c>
       <c r="AQ17" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17-AN17-IF(AO17="SI",Parametros!$E$33,0)))</f>
-        <v>0.40857142857142859</v>
+        <v>0.3567999999999999</v>
       </c>
       <c r="AR17" s="58"/>
       <c r="AS17" s="79" t="str">
@@ -21261,7 +21261,7 @@
       </c>
       <c r="AT17" s="80">
         <f>'Captura Septiembre'!K19+'Captura Septiembre'!N19+'Captura Septiembre'!Q19</f>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="AU17" s="80">
         <f>'Captura Septiembre'!T19</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="BA17" s="82">
         <f>'Captura Septiembre'!AQ19</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="BB17" s="58"/>
       <c r="BC17" s="58"/>
@@ -21333,24 +21333,24 @@
         <v>0.08</v>
       </c>
       <c r="L18" s="85">
-        <v>0</v>
+        <v>0.94</v>
       </c>
       <c r="M18" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N18" s="86">
         <f>IF(M18="NO",0,L18*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="O18" s="85">
-        <v>0</v>
+        <v>0.94</v>
       </c>
       <c r="P18" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q18" s="86">
         <f>IF(P18="NO",0,O18*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="R18" s="85">
         <v>0</v>
@@ -21434,11 +21434,11 @@
       </c>
       <c r="AP18" s="11">
         <f t="shared" si="3"/>
-        <v>0.43</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="AQ18" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18-AN18-IF(AO18="SI",Parametros!$E$33,0)))</f>
-        <v>0.43</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="AR18" s="58"/>
       <c r="AS18" s="71" t="str">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AT18" s="72">
         <f>'Captura Septiembre'!K20+'Captura Septiembre'!N20+'Captura Septiembre'!Q20</f>
-        <v>0.15679999999999999</v>
+        <v>0.23359999999999997</v>
       </c>
       <c r="AU18" s="72">
         <f>'Captura Septiembre'!T20</f>
@@ -21475,7 +21475,7 @@
       </c>
       <c r="BA18" s="74">
         <f>'Captura Septiembre'!AQ20</f>
-        <v>0.50679999999999992</v>
+        <v>0.5835999999999999</v>
       </c>
       <c r="BB18" s="58"/>
       <c r="BC18" s="58"/>
@@ -21529,14 +21529,14 @@
         <v>0.08</v>
       </c>
       <c r="O19" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q19" s="86">
         <f>IF(P19="NO",0,O19*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R19" s="85">
         <v>0</v>
@@ -21620,26 +21620,26 @@
       </c>
       <c r="AP19" s="11">
         <f t="shared" si="3"/>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AQ19" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19-AN19-IF(AO19="SI",Parametros!$E$33,0)))</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.47197181635907953</v>
+        <v>0.56254666666666664</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -21693,14 +21693,14 @@
         <v>7.6799999999999993E-2</v>
       </c>
       <c r="O20" s="85">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="P20" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q20" s="86">
         <f>IF(P20="NO",0,O20*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="R20" s="85">
         <v>0</v>
@@ -21784,11 +21784,11 @@
       </c>
       <c r="AP20" s="11">
         <f t="shared" si="3"/>
-        <v>0.50679999999999992</v>
+        <v>0.5835999999999999</v>
       </c>
       <c r="AQ20" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20-AN20-IF(AO20="SI",Parametros!$E$33,0)))</f>
-        <v>0.50679999999999992</v>
+        <v>0.5835999999999999</v>
       </c>
       <c r="AR20" s="58"/>
       <c r="AS20" s="58"/>
@@ -21803,9 +21803,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21832,11 +21832,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21878,7 +21878,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="94">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.47197181635907953</v>
+        <v>0.56254666666666664</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -21928,12 +21928,12 @@
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV6:AV20">
+  <conditionalFormatting sqref="AV19:AV20">
     <cfRule type="cellIs" dxfId="35" priority="2" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="expression" dxfId="34" priority="3">
-      <formula>AND(AV6&gt;=0.7,AV6&lt;0.9)</formula>
+      <formula>AND(AV19&gt;=0.7,AV19&lt;0.9)</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="33" priority="4" operator="lessThan">
       <formula>0.7</formula>
@@ -21956,7 +21956,7 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="decimal" showErrorMessage="1" errorTitle="Valor invalido" error="Ingrese un porcentaje entre 0% y 100%" sqref="D6:E20 L6:L20 O6:O20 R6:R20 U6:U20" xr:uid="{00000000-0002-0000-0D00-000001000000}">
+    <dataValidation type="decimal" showErrorMessage="1" errorTitle="Valor invalido" error="Ingrese un porcentaje entre 0% y 100%" sqref="U6:U20 L6:L20 O6:O20 R6:R20 D6:E20" xr:uid="{00000000-0002-0000-0D00-000001000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -21996,62 +21996,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -22060,20 +22060,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -22121,66 +22121,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22392,10 +22392,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24962,16 +24962,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -25138,9 +25138,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -25167,11 +25167,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -25330,62 +25330,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25394,20 +25394,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25455,66 +25455,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25726,10 +25726,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28296,16 +28296,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28472,9 +28472,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28501,11 +28501,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28664,62 +28664,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28728,20 +28728,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28789,66 +28789,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -29060,10 +29060,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31630,16 +31630,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31806,9 +31806,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31835,11 +31835,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31990,21 +31990,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="147" t="s">
+      <c r="A3" s="149" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -32127,7 +32127,7 @@
       </c>
       <c r="B14" s="97">
         <f>IF(AVERAGE('Captura Septiembre'!D6:D20)=0,"",'Captura Septiembre'!AQ23)</f>
-        <v>0.47197181635907953</v>
+        <v>0.56254666666666664</v>
       </c>
       <c r="C14" s="12" t="str">
         <f>IF(B14="","",IF(B14&gt;=Parametros!$C$37,"Verde",IF(B14&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -32212,22 +32212,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="150" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="99" t="s">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="J4" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="K4" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.94280555555555567</v>
+        <v>0.95169444444444451</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32368,7 +32368,7 @@
       </c>
       <c r="J5" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
-        <v>0.47000000000000003</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="K5" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
@@ -32384,7 +32384,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.90666111111111114</v>
+        <v>0.91999444444444434</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32425,7 +32425,7 @@
       </c>
       <c r="J6" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
-        <v>0.49251428571428568</v>
+        <v>0.5766</v>
       </c>
       <c r="K6" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
@@ -32441,7 +32441,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.91853333333333331</v>
+        <v>0.9278761904761903</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v>0.40857142857142859</v>
+        <v>0.3567999999999999</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -32498,7 +32498,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.7992532967032967</v>
+        <v>0.79350091575091575</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32539,7 +32539,7 @@
       </c>
       <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
-        <v>0.50679999999999992</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.85722888888888904</v>
+        <v>0.86540666666666677</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32596,7 +32596,7 @@
       </c>
       <c r="J9" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
-        <v>0.50519999999999998</v>
+        <v>0.58519999999999994</v>
       </c>
       <c r="K9" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
@@ -32612,7 +32612,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.87780000000000014</v>
+        <v>0.88668888888888886</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32653,7 +32653,7 @@
       </c>
       <c r="J10" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
-        <v>0.49316363636363636</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="K10" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D13=0,"",'Captura Octubre'!AQ13),"")</f>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.78564929292929286</v>
+        <v>0.79534222222222217</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32710,7 +32710,7 @@
       </c>
       <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.89833333333333343</v>
+        <v>0.90722222222222237</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32767,7 +32767,7 @@
       </c>
       <c r="J12" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v>0.5073700000000001</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="K12" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
@@ -32783,7 +32783,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.93298000000000003</v>
+        <v>0.94216111111111112</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32824,7 +32824,7 @@
       </c>
       <c r="J13" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
-        <v>0.50600000000000001</v>
+        <v>0.58200000000000007</v>
       </c>
       <c r="K13" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.81936714975845426</v>
+        <v>0.82781159420289863</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32881,7 +32881,7 @@
       </c>
       <c r="J14" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
-        <v>0.47315789473684211</v>
+        <v>0.58679999999999999</v>
       </c>
       <c r="K14" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
@@ -32897,7 +32897,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.79400990903183899</v>
+        <v>0.80663680961663431</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32936,9 +32936,9 @@
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
         <v>0.64449999999999996</v>
       </c>
-      <c r="J15" s="10" t="str">
+      <c r="J15" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
-        <v/>
+        <v>0.55600000000000005</v>
       </c>
       <c r="K15" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D7=0,"",'Captura Octubre'!AQ7),"")</f>
@@ -32954,7 +32954,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.78306249999999999</v>
+        <v>0.75783333333333336</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32995,7 +32995,7 @@
       </c>
       <c r="J16" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
-        <v>0.50679999999999992</v>
+        <v>0.5835999999999999</v>
       </c>
       <c r="K16" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
@@ -33011,7 +33011,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.8948666666666667</v>
+        <v>0.90340000000000009</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33052,7 +33052,7 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
-        <v>0.43</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
@@ -33068,7 +33068,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.88470610021786489</v>
+        <v>0.90141721132897601</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33109,7 +33109,7 @@
       </c>
       <c r="J18" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="K18" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
@@ -33125,7 +33125,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.86375000000000002</v>
+        <v>0.87263888888888885</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -33166,7 +33166,7 @@
       </c>
       <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v>0.48211266038472805</v>
+        <v>0.56254666666666664</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -33186,21 +33186,21 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="149" t="s">
+      <c r="A20" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="149"/>
-      <c r="C20" s="149"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="149"/>
-      <c r="I20" s="149"/>
-      <c r="J20" s="149"/>
-      <c r="K20" s="149"/>
-      <c r="L20" s="149"/>
-      <c r="M20" s="149"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="151"/>
+      <c r="E20" s="151"/>
+      <c r="F20" s="151"/>
+      <c r="G20" s="151"/>
+      <c r="H20" s="151"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="151"/>
+      <c r="K20" s="151"/>
+      <c r="L20" s="151"/>
+      <c r="M20" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -33225,16 +33225,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -33245,12 +33245,12 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
@@ -33276,11 +33276,11 @@
       </c>
       <c r="C5" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G20"))</f>
-        <v>8.4745149692412855E-2</v>
+        <v>9.7266666666666682E-2</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" ref="D5:D11" ca="1" si="0">IFERROR(C5/B5,0)</f>
-        <v>0.42372574846206423</v>
+        <v>0.4863333333333334</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33310,11 +33310,11 @@
       </c>
       <c r="C7" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>5.7226666666666655E-2</v>
+        <v>6.7573333333333332E-2</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.71533333333333315</v>
+        <v>0.84466666666666668</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33327,11 +33327,11 @@
       </c>
       <c r="C8" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>5.7226666666666655E-2</v>
+        <v>6.7573333333333332E-2</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.71533333333333315</v>
+        <v>0.84466666666666668</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33386,10 +33386,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="124" t="s">
+      <c r="A13" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="124"/>
+      <c r="B13" s="126"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
@@ -33415,7 +33415,7 @@
       </c>
       <c r="B16" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AN6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AN20"))</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33446,12 +33446,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="124" t="s">
+      <c r="A21" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="124"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="124"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="B24" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,2),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C24" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),2)</f>
@@ -33509,7 +33509,7 @@
       </c>
       <c r="E24" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ7")*100000-7</f>
-        <v>32993</v>
+        <v>55593.000000000007</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33518,7 +33518,7 @@
       </c>
       <c r="B25" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,3),$E$23:$E$37,0))</f>
-        <v>Centro de Distribucion</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C25" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),3)</f>
@@ -33530,7 +33530,7 @@
       </c>
       <c r="E25" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ8")*100000-8</f>
-        <v>50992</v>
+        <v>58992.000000000007</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33539,7 +33539,7 @@
       </c>
       <c r="B26" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,4),$E$23:$E$37,0))</f>
-        <v>Linea 2</v>
+        <v>Linea 3</v>
       </c>
       <c r="C26" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),4)</f>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="E26" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ9")*100000-9</f>
-        <v>50728.000000000007</v>
+        <v>58991.000000000007</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33560,7 +33560,7 @@
       </c>
       <c r="B27" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,5),$E$23:$E$37,0))</f>
-        <v>Jarabes</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C27" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),5)</f>
@@ -33572,7 +33572,7 @@
       </c>
       <c r="E27" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ10")*100000-10</f>
-        <v>42990</v>
+        <v>50990</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33581,7 +33581,7 @@
       </c>
       <c r="B28" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,6),$E$23:$E$37,0))</f>
-        <v>Equipos Auxiliares</v>
+        <v>Jarabes</v>
       </c>
       <c r="C28" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),6)</f>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="E28" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ11")*100000-11</f>
-        <v>50509</v>
+        <v>58508.999999999993</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="E29" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ12")*100000-12</f>
-        <v>50588</v>
+        <v>58188.000000000007</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33623,7 +33623,7 @@
       </c>
       <c r="B30" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,8),$E$23:$E$37,0))</f>
-        <v>Linea 4</v>
+        <v>Linea 2</v>
       </c>
       <c r="C30" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),8)</f>
@@ -33635,7 +33635,7 @@
       </c>
       <c r="E30" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ13")*100000-13</f>
-        <v>49303.363636363632</v>
+        <v>58027</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33644,7 +33644,7 @@
       </c>
       <c r="B31" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,9),$E$23:$E$37,0))</f>
-        <v>Linea 3</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C31" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),9)</f>
@@ -33656,7 +33656,7 @@
       </c>
       <c r="E31" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ14")*100000-14</f>
-        <v>50665.999999999993</v>
+        <v>58026</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="B32" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,10),$E$23:$E$37,0))</f>
-        <v>ETEI</v>
+        <v>Linea 4</v>
       </c>
       <c r="C32" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),10)</f>
@@ -33677,7 +33677,7 @@
       </c>
       <c r="E32" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ15")*100000-15</f>
-        <v>47300.789473684214</v>
+        <v>58665</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="B33" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,11),$E$23:$E$37,0))</f>
-        <v>Mantenimiento</v>
+        <v>Alrededores</v>
       </c>
       <c r="C33" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),11)</f>
@@ -33698,7 +33698,7 @@
       </c>
       <c r="E33" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ16")*100000-16</f>
-        <v>49235.428571428565</v>
+        <v>57644</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33707,7 +33707,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>Linea 5</v>
+        <v>ETEI</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33719,7 +33719,7 @@
       </c>
       <c r="E34" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ17")*100000-17</f>
-        <v>40840.142857142855</v>
+        <v>35662.999999999993</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="B35" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,13),$E$23:$E$37,0))</f>
-        <v>Alrededores</v>
+        <v>Linea 5</v>
       </c>
       <c r="C35" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),13)</f>
@@ -33740,7 +33740,7 @@
       </c>
       <c r="E35" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ18")*100000-18</f>
-        <v>42982</v>
+        <v>58022</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33761,7 +33761,7 @@
       </c>
       <c r="E36" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ19")*100000-19</f>
-        <v>50981</v>
+        <v>58981.000000000007</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33786,10 +33786,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="124" t="s">
+      <c r="A39" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="124"/>
+      <c r="B39" s="126"/>
     </row>
     <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.47197181635907953</v>
+        <v>0.56254666666666664</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33880,22 +33880,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="150" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
     </row>
     <row r="3" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="99" t="s">
@@ -33979,7 +33979,7 @@
       </c>
       <c r="J4" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="K4" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.94280555555555567</v>
+        <v>0.95169444444444451</v>
       </c>
       <c r="O4" s="106"/>
     </row>
@@ -34037,7 +34037,7 @@
       </c>
       <c r="J5" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v>0.5073700000000001</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="K5" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
@@ -34053,7 +34053,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.93298000000000003</v>
+        <v>0.94216111111111112</v>
       </c>
       <c r="O5" s="106"/>
     </row>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="J6" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
-        <v>0.49251428571428568</v>
+        <v>0.5766</v>
       </c>
       <c r="K6" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
@@ -34111,7 +34111,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.91853333333333331</v>
+        <v>0.9278761904761903</v>
       </c>
       <c r="O6" s="106"/>
     </row>
@@ -34153,7 +34153,7 @@
       </c>
       <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
-        <v>0.47000000000000003</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
@@ -34169,7 +34169,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.90666111111111114</v>
+        <v>0.91999444444444434</v>
       </c>
       <c r="O7" s="106"/>
     </row>
@@ -34211,7 +34211,7 @@
       </c>
       <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -34227,7 +34227,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.89833333333333343</v>
+        <v>0.90722222222222237</v>
       </c>
       <c r="O8" s="106"/>
     </row>
@@ -34269,7 +34269,7 @@
       </c>
       <c r="J9" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
-        <v>0.50679999999999992</v>
+        <v>0.5835999999999999</v>
       </c>
       <c r="K9" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
@@ -34285,7 +34285,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.8948666666666667</v>
+        <v>0.90340000000000009</v>
       </c>
       <c r="O9" s="106"/>
     </row>
@@ -34327,7 +34327,7 @@
       </c>
       <c r="J10" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
-        <v>0.43</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="K10" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.88470610021786489</v>
+        <v>0.90141721132897601</v>
       </c>
       <c r="O10" s="106"/>
     </row>
@@ -34385,7 +34385,7 @@
       </c>
       <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
-        <v>0.50519999999999998</v>
+        <v>0.58519999999999994</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
@@ -34401,7 +34401,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.87780000000000014</v>
+        <v>0.88668888888888886</v>
       </c>
       <c r="O11" s="106"/>
     </row>
@@ -34443,7 +34443,7 @@
       </c>
       <c r="J12" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="K12" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
@@ -34459,7 +34459,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.86375000000000002</v>
+        <v>0.87263888888888885</v>
       </c>
       <c r="O12" s="106"/>
     </row>
@@ -34501,7 +34501,7 @@
       </c>
       <c r="J13" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
-        <v>0.50679999999999992</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="K13" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
@@ -34517,7 +34517,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.85722888888888904</v>
+        <v>0.86540666666666677</v>
       </c>
       <c r="O13" s="106"/>
     </row>
@@ -34559,7 +34559,7 @@
       </c>
       <c r="J14" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
-        <v>0.50600000000000001</v>
+        <v>0.58200000000000007</v>
       </c>
       <c r="K14" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
@@ -34575,7 +34575,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.81936714975845426</v>
+        <v>0.82781159420289863</v>
       </c>
       <c r="O14" s="106"/>
     </row>
@@ -34617,7 +34617,7 @@
       </c>
       <c r="J15" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v>0.40857142857142859</v>
+        <v>0.3567999999999999</v>
       </c>
       <c r="K15" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -34633,7 +34633,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.7992532967032967</v>
+        <v>0.79350091575091575</v>
       </c>
       <c r="O15" s="106"/>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="J16" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
-        <v>0.47315789473684211</v>
+        <v>0.58679999999999999</v>
       </c>
       <c r="K16" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
@@ -34691,7 +34691,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.79400990903183899</v>
+        <v>0.80663680961663431</v>
       </c>
       <c r="O16" s="106"/>
     </row>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
-        <v>0.49316363636363636</v>
+        <v>0.58040000000000003</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D13=0,"",'Captura Octubre'!AQ13),"")</f>
@@ -34749,7 +34749,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.78564929292929286</v>
+        <v>0.79534222222222217</v>
       </c>
       <c r="O17" s="106"/>
     </row>
@@ -34789,9 +34789,9 @@
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
         <v>0.64449999999999996</v>
       </c>
-      <c r="J18" s="10" t="str">
+      <c r="J18" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
-        <v/>
+        <v>0.55600000000000005</v>
       </c>
       <c r="K18" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D7=0,"",'Captura Octubre'!AQ7),"")</f>
@@ -34807,7 +34807,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.78306249999999999</v>
+        <v>0.75783333333333336</v>
       </c>
       <c r="O18" s="106"/>
     </row>
@@ -34849,7 +34849,7 @@
       </c>
       <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v>0.48211266038472811</v>
+        <v>0.56254666666666664</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -34901,44 +34901,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="127"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
-      <c r="N3" s="127"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="127"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
+      <c r="R3" s="129"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34948,153 +34948,153 @@
         <f>Calculos!$B$2</f>
         <v>Septiembre</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="128"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="129" t="s">
+      <c r="B6" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="129"/>
-      <c r="D6" s="129"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129" t="s">
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="131" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="129" t="s">
+      <c r="G6" s="131"/>
+      <c r="H6" s="131"/>
+      <c r="I6" s="131"/>
+      <c r="J6" s="131" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="129"/>
-      <c r="L6" s="129"/>
-      <c r="M6" s="129" t="s">
+      <c r="K6" s="131"/>
+      <c r="L6" s="131"/>
+      <c r="M6" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="129"/>
-      <c r="O6" s="129"/>
-      <c r="P6" s="129" t="s">
+      <c r="N6" s="131"/>
+      <c r="O6" s="131"/>
+      <c r="P6" s="131" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="129"/>
-      <c r="R6" s="129"/>
+      <c r="Q6" s="131"/>
+      <c r="R6" s="131"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="129"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="129"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="129"/>
-      <c r="O7" s="129"/>
-      <c r="P7" s="129"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="129"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="131"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="130">
+      <c r="B8" s="132">
         <f ca="1">Calculos!B44</f>
-        <v>0.47197181635907953</v>
-      </c>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="131" t="str">
+        <v>0.56254666666666664</v>
+      </c>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="133" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="132">
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="134">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="132"/>
-      <c r="L8" s="132"/>
-      <c r="M8" s="125">
+      <c r="K8" s="134"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="127">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
-      <c r="P8" s="126">
+      <c r="N8" s="127"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="128">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="126"/>
-      <c r="R8" s="126"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="128"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="125"/>
-      <c r="N9" s="125"/>
-      <c r="O9" s="125"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="134"/>
+      <c r="L9" s="134"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="127"/>
+      <c r="O9" s="127"/>
+      <c r="P9" s="128"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="128"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="132"/>
-      <c r="K10" s="132"/>
-      <c r="L10" s="132"/>
-      <c r="M10" s="125"/>
-      <c r="N10" s="125"/>
-      <c r="O10" s="125"/>
-      <c r="P10" s="126"/>
-      <c r="Q10" s="126"/>
-      <c r="R10" s="126"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="134"/>
+      <c r="K10" s="134"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="127"/>
+      <c r="N10" s="127"/>
+      <c r="O10" s="127"/>
+      <c r="P10" s="128"/>
+      <c r="Q10" s="128"/>
+      <c r="R10" s="128"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="124" t="s">
+      <c r="B12" s="126" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="124"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="G12" s="124" t="s">
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
+      <c r="G12" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="124"/>
+      <c r="H12" s="126"/>
     </row>
     <row r="13" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
@@ -35125,13 +35125,13 @@
       </c>
       <c r="H14" s="22">
         <f ca="1">Calculos!D5</f>
-        <v>0.42372574846206423</v>
+        <v>0.4863333333333334</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="str">
         <f ca="1">Calculos!B24</f>
-        <v>Materias Primas</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C15" s="21">
         <f ca="1">Calculos!C24</f>
@@ -35149,7 +35149,7 @@
     <row r="16" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="str">
         <f ca="1">Calculos!B25</f>
-        <v>Centro de Distribucion</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C16" s="21">
         <f ca="1">Calculos!C25</f>
@@ -35161,13 +35161,13 @@
       </c>
       <c r="H16" s="22">
         <f ca="1">Calculos!D7</f>
-        <v>0.71533333333333315</v>
+        <v>0.84466666666666668</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="str">
         <f ca="1">Calculos!B26</f>
-        <v>Linea 2</v>
+        <v>Linea 3</v>
       </c>
       <c r="C17" s="21">
         <f ca="1">Calculos!C26</f>
@@ -35179,13 +35179,13 @@
       </c>
       <c r="H17" s="22">
         <f ca="1">Calculos!D8</f>
-        <v>0.71533333333333315</v>
+        <v>0.84466666666666668</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="str">
         <f ca="1">Calculos!B27</f>
-        <v>Jarabes</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C18" s="21">
         <f ca="1">Calculos!C27</f>
@@ -35203,7 +35203,7 @@
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="str">
         <f ca="1">Calculos!B28</f>
-        <v>Equipos Auxiliares</v>
+        <v>Jarabes</v>
       </c>
       <c r="C19" s="21">
         <f ca="1">Calculos!C28</f>
@@ -35239,7 +35239,7 @@
     <row r="21" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="str">
         <f ca="1">Calculos!B30</f>
-        <v>Linea 4</v>
+        <v>Linea 2</v>
       </c>
       <c r="C21" s="21">
         <f ca="1">Calculos!C30</f>
@@ -35249,7 +35249,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="str">
         <f ca="1">Calculos!B31</f>
-        <v>Linea 3</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C22" s="21">
         <f ca="1">Calculos!C31</f>
@@ -35259,7 +35259,7 @@
     <row r="23" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="str">
         <f ca="1">Calculos!B32</f>
-        <v>ETEI</v>
+        <v>Linea 4</v>
       </c>
       <c r="C23" s="21">
         <f ca="1">Calculos!C32</f>
@@ -35269,7 +35269,7 @@
     <row r="24" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="str">
         <f ca="1">Calculos!B33</f>
-        <v>Mantenimiento</v>
+        <v>Alrededores</v>
       </c>
       <c r="C24" s="21">
         <f ca="1">Calculos!C33</f>
@@ -35279,7 +35279,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>Linea 5</v>
+        <v>ETEI</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -35289,7 +35289,7 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="str">
         <f ca="1">Calculos!B35</f>
-        <v>Alrededores</v>
+        <v>Linea 5</v>
       </c>
       <c r="C26" s="21">
         <f ca="1">Calculos!C35</f>
@@ -35388,61 +35388,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="144" t="s">
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="146" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="145" t="s">
+      <c r="B4" s="147" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="145"/>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="145"/>
-      <c r="N4" s="145"/>
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="147"/>
+      <c r="L4" s="147"/>
+      <c r="M4" s="147"/>
+      <c r="N4" s="147"/>
+      <c r="O4" s="147"/>
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="146" t="str">
+      <c r="B5" s="148" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  SEPTIEMBRE 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="146"/>
-      <c r="D5" s="146"/>
-      <c r="E5" s="146"/>
-      <c r="F5" s="146"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="146"/>
-      <c r="J5" s="146"/>
-      <c r="K5" s="146"/>
-      <c r="L5" s="146"/>
-      <c r="M5" s="146"/>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="146"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="148"/>
+      <c r="Q5" s="148"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35453,7 +35453,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="133" t="str">
+      <c r="A7" s="135" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>SEPTIEMBRE</v>
       </c>
@@ -35470,13 +35470,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="133"/>
-      <c r="G8" s="134">
+      <c r="A8" s="135"/>
+      <c r="G8" s="136">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
+      <c r="H8" s="136"/>
+      <c r="I8" s="136"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35486,15 +35486,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="133"/>
-      <c r="F9" s="135">
+      <c r="A9" s="135"/>
+      <c r="F9" s="137">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="135"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="137"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35504,39 +35504,39 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="133"/>
-      <c r="E10" s="136">
+      <c r="A10" s="135"/>
+      <c r="E10" s="138">
         <f ca="1">X33</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="136"/>
-      <c r="K10" s="136"/>
+        <v>1</v>
+      </c>
+      <c r="F10" s="138"/>
+      <c r="G10" s="138"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="138"/>
+      <c r="K10" s="138"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
       <c r="Q10" s="32">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="133"/>
-      <c r="D11" s="137">
+      <c r="A11" s="135"/>
+      <c r="D11" s="139">
         <f ca="1">X34</f>
         <v>0</v>
       </c>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="139"/>
+      <c r="L11" s="139"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35546,21 +35546,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="133"/>
-      <c r="C12" s="138">
+      <c r="A12" s="135"/>
+      <c r="C12" s="140">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="138"/>
-      <c r="E12" s="138"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="138"/>
-      <c r="J12" s="138"/>
-      <c r="K12" s="138"/>
-      <c r="L12" s="138"/>
-      <c r="M12" s="138"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="140"/>
+      <c r="L12" s="140"/>
+      <c r="M12" s="140"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35570,75 +35570,75 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="133"/>
-      <c r="B13" s="139">
+      <c r="A13" s="135"/>
+      <c r="B13" s="141">
         <f ca="1">X36</f>
-        <v>17</v>
-      </c>
-      <c r="C13" s="139"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="139"/>
-      <c r="G13" s="139"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="139"/>
-      <c r="J13" s="139"/>
-      <c r="K13" s="139"/>
-      <c r="L13" s="139"/>
-      <c r="M13" s="139"/>
-      <c r="N13" s="139"/>
+        <v>24</v>
+      </c>
+      <c r="C13" s="141"/>
+      <c r="D13" s="141"/>
+      <c r="E13" s="141"/>
+      <c r="F13" s="141"/>
+      <c r="G13" s="141"/>
+      <c r="H13" s="141"/>
+      <c r="I13" s="141"/>
+      <c r="J13" s="141"/>
+      <c r="K13" s="141"/>
+      <c r="L13" s="141"/>
+      <c r="M13" s="141"/>
+      <c r="N13" s="141"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
       <c r="Q13" s="34">
         <f>Y36</f>
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="133"/>
-      <c r="B14" s="140">
+      <c r="A14" s="135"/>
+      <c r="B14" s="142">
         <f ca="1">X37</f>
-        <v>89</v>
-      </c>
-      <c r="C14" s="140"/>
-      <c r="D14" s="140"/>
-      <c r="E14" s="140"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="140"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="140"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="140"/>
-      <c r="N14" s="140"/>
+        <v>153</v>
+      </c>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
+      <c r="M14" s="142"/>
+      <c r="N14" s="142"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
       <c r="Q14" s="34">
         <f t="shared" si="0"/>
-        <v>2013</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="141" t="s">
+      <c r="S16" s="143" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="141"/>
-      <c r="U16" s="141"/>
-      <c r="V16" s="141"/>
+      <c r="T16" s="143"/>
+      <c r="U16" s="143"/>
+      <c r="V16" s="143"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S18" s="35">
         <f ca="1">IF(T20="","—",INT(TODAY()-T20))</f>
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="U18" s="35">
         <f ca="1">IF(V20="","—",INT(TODAY()-V20))</f>
-        <v>67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35660,18 +35660,18 @@
         <v>84</v>
       </c>
       <c r="V20" s="38">
-        <v>46212</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="21" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S22" s="35">
         <f ca="1">IF(T24="","—",INT(TODAY()-T24))</f>
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="U22" s="35">
         <f ca="1">IF(V24="","—",INT(TODAY()-V24))</f>
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35699,42 +35699,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="142" t="s">
+      <c r="B27" s="144" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="142"/>
-      <c r="D27" s="142"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="142"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="142"/>
-      <c r="I27" s="142"/>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="142"/>
-      <c r="M27" s="142"/>
-      <c r="N27" s="142"/>
-      <c r="O27" s="142"/>
-      <c r="P27" s="142"/>
-      <c r="Q27" s="142"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="144"/>
+      <c r="E27" s="144"/>
+      <c r="F27" s="144"/>
+      <c r="G27" s="144"/>
+      <c r="H27" s="144"/>
+      <c r="I27" s="144"/>
+      <c r="J27" s="144"/>
+      <c r="K27" s="144"/>
+      <c r="L27" s="144"/>
+      <c r="M27" s="144"/>
+      <c r="N27" s="144"/>
+      <c r="O27" s="144"/>
+      <c r="P27" s="144"/>
+      <c r="Q27" s="144"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="142"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="142"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="142"/>
-      <c r="G28" s="142"/>
-      <c r="H28" s="142"/>
-      <c r="I28" s="142"/>
-      <c r="J28" s="142"/>
-      <c r="K28" s="142"/>
-      <c r="L28" s="142"/>
-      <c r="M28" s="142"/>
-      <c r="N28" s="142"/>
-      <c r="O28" s="142"/>
-      <c r="P28" s="142"/>
-      <c r="Q28" s="142"/>
+      <c r="B28" s="144"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="144"/>
+      <c r="E28" s="144"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="144"/>
+      <c r="H28" s="144"/>
+      <c r="I28" s="144"/>
+      <c r="J28" s="144"/>
+      <c r="K28" s="144"/>
+      <c r="L28" s="144"/>
+      <c r="M28" s="144"/>
+      <c r="N28" s="144"/>
+      <c r="O28" s="144"/>
+      <c r="P28" s="144"/>
+      <c r="Q28" s="144"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35779,11 +35779,11 @@
       </c>
       <c r="X33" s="41">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH6")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH7")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH8")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH9")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH10")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH11")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH12")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH13")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH14")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH15")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH16")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH17")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH18")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH19")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AH20"),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" s="41">
         <f>SUM('Captura Enero'!AH6:AH20)+SUM('Captura Febrero'!AH6:AH20)+SUM('Captura Marzo'!AH6:AH20)+SUM('Captura Abril'!AH6:AH20)+SUM('Captura Mayo'!AH6:AH20)+SUM('Captura Junio'!AH6:AH20)+SUM('Captura Julio'!AH6:AH20)+SUM('Captura Agosto'!AH6:AH20)+SUM('Captura Septiembre'!AH6:AH20)+SUM('Captura Octubre'!AH6:AH20)+SUM('Captura Noviembre'!AH6:AH20)+SUM('Captura Diciembre'!AH6:AH20)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="23:25" x14ac:dyDescent="0.35">
@@ -35818,11 +35818,11 @@
       </c>
       <c r="X36" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC3"),0)</f>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Y36" s="41">
         <f>'Captura Enero'!BC3+'Captura Febrero'!BC3+'Captura Marzo'!BC3+'Captura Abril'!BC3+'Captura Mayo'!BC3+'Captura Junio'!BC3+'Captura Julio'!BC3+'Captura Agosto'!BC3+'Captura Septiembre'!BC3+'Captura Octubre'!BC3+'Captura Noviembre'!BC3+'Captura Diciembre'!BC3</f>
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="37" spans="23:25" x14ac:dyDescent="0.35">
@@ -35831,11 +35831,11 @@
       </c>
       <c r="X37" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC4"),0)</f>
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="Y37" s="41">
         <f>'Captura Enero'!BC4+'Captura Febrero'!BC4+'Captura Marzo'!BC4+'Captura Abril'!BC4+'Captura Mayo'!BC4+'Captura Junio'!BC4+'Captura Julio'!BC4+'Captura Agosto'!BC4+'Captura Septiembre'!BC4+'Captura Octubre'!BC4+'Captura Noviembre'!BC4+'Captura Diciembre'!BC4</f>
-        <v>2013</v>
+        <v>2077</v>
       </c>
     </row>
   </sheetData>
@@ -35888,26 +35888,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="126" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124"/>
-      <c r="H4" s="124" t="s">
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="H4" s="126" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="124"/>
+      <c r="I4" s="126"/>
     </row>
     <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
@@ -36168,13 +36168,13 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="124" t="s">
+      <c r="B16" s="126" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
+      <c r="C16" s="126"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
       <c r="H16" s="8">
         <v>11</v>
       </c>
@@ -36257,13 +36257,13 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="124" t="s">
+      <c r="B21" s="126" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="124"/>
-      <c r="D21" s="124"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="124"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="126"/>
+      <c r="F21" s="126"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
@@ -36310,13 +36310,13 @@
       <c r="F25" s="52"/>
     </row>
     <row r="27" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="124" t="s">
+      <c r="B27" s="126" t="s">
         <v>149</v>
       </c>
-      <c r="C27" s="124"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
     </row>
     <row r="28" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
@@ -36385,13 +36385,13 @@
       <c r="F33" s="52"/>
     </row>
     <row r="35" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="124" t="s">
+      <c r="B35" s="126" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="124"/>
-      <c r="D35" s="124"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="124"/>
+      <c r="C35" s="126"/>
+      <c r="D35" s="126"/>
+      <c r="E35" s="126"/>
+      <c r="F35" s="126"/>
     </row>
     <row r="36" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="7" t="s">
@@ -36488,62 +36488,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36552,20 +36552,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36613,66 +36613,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36884,10 +36884,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39454,16 +39454,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93297435897435899</v>
@@ -39635,9 +39635,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39664,11 +39664,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39827,62 +39827,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39891,20 +39891,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39952,66 +39952,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -40223,10 +40223,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42793,16 +42793,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42969,9 +42969,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42998,11 +42998,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -43161,62 +43161,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -43225,20 +43225,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -43286,66 +43286,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43557,10 +43557,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -46127,16 +46127,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46303,9 +46303,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46332,11 +46332,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46495,62 +46495,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
+      <c r="W1" s="109"/>
+      <c r="X1" s="109"/>
+      <c r="Y1" s="109"/>
+      <c r="Z1" s="109"/>
+      <c r="AA1" s="109"/>
+      <c r="AB1" s="109"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="108" t="s">
+      <c r="AS1" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="108"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="109" t="s">
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
+      <c r="AV1" s="110"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="110"/>
+      <c r="AY1" s="110"/>
+      <c r="AZ1" s="110"/>
+      <c r="BA1" s="110"/>
+      <c r="BB1" s="111" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="109"/>
+      <c r="BC1" s="111"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="112" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46559,20 +46559,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="111" t="s">
+      <c r="AT2" s="113" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="112" t="s">
+      <c r="AX2" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="112"/>
-      <c r="AZ2" s="112"/>
-      <c r="BA2" s="112"/>
+      <c r="AY2" s="114"/>
+      <c r="AZ2" s="114"/>
+      <c r="BA2" s="114"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46620,66 +46620,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="118" t="s">
+      <c r="D4" s="120" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118" t="s">
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118" t="s">
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118" t="s">
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118" t="s">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="118"/>
-      <c r="W4" s="119" t="s">
+      <c r="V4" s="120"/>
+      <c r="W4" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="119"/>
-      <c r="Y4" s="118" t="s">
+      <c r="X4" s="121"/>
+      <c r="Y4" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="119" t="s">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="119"/>
-      <c r="AF4" s="119"/>
-      <c r="AG4" s="119"/>
-      <c r="AH4" s="119"/>
-      <c r="AI4" s="119"/>
-      <c r="AJ4" s="119"/>
-      <c r="AK4" s="119"/>
-      <c r="AL4" s="119"/>
-      <c r="AM4" s="119"/>
-      <c r="AN4" s="119"/>
-      <c r="AO4" s="119"/>
-      <c r="AP4" s="120" t="s">
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="121"/>
+      <c r="AG4" s="121"/>
+      <c r="AH4" s="121"/>
+      <c r="AI4" s="121"/>
+      <c r="AJ4" s="121"/>
+      <c r="AK4" s="121"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="121"/>
+      <c r="AN4" s="121"/>
+      <c r="AO4" s="121"/>
+      <c r="AP4" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="120"/>
+      <c r="AQ4" s="122"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46891,10 +46891,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="114" t="s">
+      <c r="BB5" s="116" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="114"/>
+      <c r="BC5" s="116"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49461,16 +49461,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="115" t="s">
+      <c r="AS19" s="117" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="115"/>
-      <c r="AU19" s="115"/>
-      <c r="AV19" s="115"/>
-      <c r="AW19" s="115"/>
-      <c r="AX19" s="115"/>
-      <c r="AY19" s="115"/>
-      <c r="AZ19" s="115"/>
+      <c r="AT19" s="117"/>
+      <c r="AU19" s="117"/>
+      <c r="AV19" s="117"/>
+      <c r="AW19" s="117"/>
+      <c r="AX19" s="117"/>
+      <c r="AY19" s="117"/>
+      <c r="AZ19" s="117"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49637,9 +49637,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
+      <c r="A22" s="118"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49666,11 +49666,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="117" t="s">
+      <c r="A23" s="119" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>

--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CC1B93-9E4F-4CF5-93D8-DC6F21136255}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA67CA16-A5A2-4E0A-8AD2-841C1B21F8D6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'ACUMULADO - 2026'!$A$3:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Dashboard Ejecutivo'!$A$1:$Y$75</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1883,7 +1883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="56" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2137,6 +2137,27 @@
     <xf numFmtId="0" fontId="45" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2158,27 +2179,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2187,6 +2187,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2202,14 +2211,23 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2235,24 +2253,6 @@
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2261,6 +2261,9 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3279,40 +3282,40 @@
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>Equipos Auxiliares</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Materias Primas</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Centro de Distribucion</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Calidad</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Centro de Distribucion</c:v>
+                <c:pt idx="4">
+                  <c:v>Linea 2</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>Materias Primas</c:v>
+                <c:pt idx="5">
+                  <c:v>ETEI</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>Linea 4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Linea 1</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Linea 3</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>Equipos Auxiliares</c:v>
+                <c:pt idx="9">
+                  <c:v>Mantenimiento</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
                   <c:v>Jarabes</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Linea 1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Linea 2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Mantenimiento</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Linea 4</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Alrededores</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>ETEI</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Linea 5</c:v>
@@ -3696,7 +3699,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.4863333333333334</c:v>
+                  <c:v>0.85692000000000013</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -3708,7 +3711,7 @@
                   <c:v>0.84466666666666668</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.13333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -4383,7 +4386,7 @@
                   <c:v>0.86230933333333326</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.56254666666666664</c:v>
+                  <c:v>0.64466400000000013</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5183,7 +5186,7 @@
       </c>
       <c r="C13" s="4">
         <f ca="1">TODAY()</f>
-        <v>46287</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5310,62 +5313,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5374,20 +5377,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5435,66 +5438,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5706,10 +5709,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8276,16 +8279,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.8793333333333333</v>
@@ -8452,9 +8455,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8481,11 +8484,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8543,6 +8546,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8557,12 +8566,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8644,62 +8647,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8708,20 +8711,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8769,66 +8772,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -9040,10 +9043,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11610,16 +11613,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11786,9 +11789,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11815,11 +11818,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11877,6 +11880,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11891,12 +11900,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11980,62 +11983,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -12044,20 +12047,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -12105,66 +12108,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12376,10 +12379,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14946,16 +14949,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -15122,9 +15125,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -15151,11 +15154,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -15213,6 +15216,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -15227,12 +15236,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15318,62 +15321,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15382,20 +15385,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15443,66 +15446,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15714,10 +15717,10 @@
         <f>'Captura Agosto'!AQ7</f>
         <v>0.64449999999999996</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -18284,16 +18287,16 @@
         <v>0.97124999999999995</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.86230933333333326</v>
@@ -18460,9 +18463,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18489,11 +18492,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18551,6 +18554,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18565,12 +18574,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18655,90 +18658,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="115" t="s">
+      <c r="G2" s="122" t="s">
         <v>166</v>
       </c>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18786,66 +18789,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="107" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -18865,7 +18868,7 @@
       </c>
       <c r="AW4" s="72">
         <f>'Captura Septiembre'!G6</f>
-        <v>0.1</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="AX4" s="72">
         <f>'Captura Septiembre'!X6</f>
@@ -18881,7 +18884,7 @@
       </c>
       <c r="BA4" s="74">
         <f>'Captura Septiembre'!AQ6</f>
-        <v>0.59000000000000008</v>
+        <v>0.67</v>
       </c>
       <c r="BB4" s="68" t="s">
         <v>191</v>
@@ -19057,10 +19060,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.55600000000000005</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -19077,15 +19080,15 @@
         <v>1</v>
       </c>
       <c r="E6" s="85">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ref="F6:F20" si="0">AVERAGE(D6,E6)</f>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G6" s="86">
         <f>F6*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="H6" s="87">
         <v>38</v>
@@ -19200,13 +19203,13 @@
         <f t="shared" ref="AO6:AO20" si="2">IF(OR(AND(AD6&gt;0,AE6="NO"),AND(AF6&gt;0,AG6="NO"),AND(AH6&gt;0,AI6="NO"),AND(AJ6&gt;0,AK6="NO"),AND(AL6&gt;0,AM6="NO")),"SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="AP6" s="11">
+      <c r="AP6" s="86">
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="AQ6" s="90">
+        <v>0.67</v>
+      </c>
+      <c r="AQ6" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6-AN6-IF(AO6="SI",Parametros!$E$33,0)))</f>
-        <v>0.59000000000000008</v>
+        <v>0.67</v>
       </c>
       <c r="AR6" s="58"/>
       <c r="AS6" s="71" t="str">
@@ -19227,7 +19230,7 @@
       </c>
       <c r="AW6" s="72">
         <f>'Captura Septiembre'!G8</f>
-        <v>0.1</v>
+        <v>0.19375000000000001</v>
       </c>
       <c r="AX6" s="72">
         <f>'Captura Septiembre'!X8</f>
@@ -19243,7 +19246,7 @@
       </c>
       <c r="BA6" s="74">
         <f>'Captura Septiembre'!AQ8</f>
-        <v>0.59000000000000008</v>
+        <v>0.68375000000000008</v>
       </c>
       <c r="BB6" s="58"/>
       <c r="BC6" s="58"/>
@@ -19386,11 +19389,11 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP7" s="11">
+      <c r="AP7" s="86">
         <f t="shared" si="3"/>
         <v>0.55600000000000005</v>
       </c>
-      <c r="AQ7" s="90">
+      <c r="AQ7" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7-AN7-IF(AO7="SI",Parametros!$E$33,0)))</f>
         <v>0.55600000000000005</v>
       </c>
@@ -19413,7 +19416,7 @@
       </c>
       <c r="AW7" s="80">
         <f>'Captura Septiembre'!G9</f>
-        <v>0.1</v>
+        <v>0.19737000000000002</v>
       </c>
       <c r="AX7" s="80">
         <f>'Captura Septiembre'!X9</f>
@@ -19429,7 +19432,7 @@
       </c>
       <c r="BA7" s="82">
         <f>'Captura Septiembre'!AQ9</f>
-        <v>0.59000000000000008</v>
+        <v>0.68737000000000004</v>
       </c>
       <c r="BB7" s="58"/>
       <c r="BC7" s="58"/>
@@ -19449,15 +19452,15 @@
         <v>1</v>
       </c>
       <c r="E8" s="85">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.96875</v>
       </c>
       <c r="G8" s="86">
         <f>F8*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.19375000000000001</v>
       </c>
       <c r="H8" s="87">
         <v>38</v>
@@ -19572,13 +19575,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP8" s="11">
+      <c r="AP8" s="86">
         <f t="shared" si="3"/>
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="AQ8" s="90">
+        <v>0.68375000000000008</v>
+      </c>
+      <c r="AQ8" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8-AN8-IF(AO8="SI",Parametros!$E$33,0)))</f>
-        <v>0.59000000000000008</v>
+        <v>0.68375000000000008</v>
       </c>
       <c r="AR8" s="58"/>
       <c r="AS8" s="71" t="str">
@@ -19591,7 +19594,7 @@
       </c>
       <c r="AU8" s="72">
         <f>'Captura Septiembre'!T10</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AV8" s="72">
         <f>'Captura Septiembre'!V10</f>
@@ -19599,7 +19602,7 @@
       </c>
       <c r="AW8" s="72">
         <f>'Captura Septiembre'!G10</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AX8" s="72">
         <f>'Captura Septiembre'!X10</f>
@@ -19615,7 +19618,7 @@
       </c>
       <c r="BA8" s="74">
         <f>'Captura Septiembre'!AQ10</f>
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="BB8" s="58"/>
       <c r="BC8" s="58"/>
@@ -19635,15 +19638,15 @@
         <v>1</v>
       </c>
       <c r="E9" s="85">
-        <v>0</v>
+        <v>0.97370000000000001</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.98685</v>
       </c>
       <c r="G9" s="86">
         <f>F9*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.19737000000000002</v>
       </c>
       <c r="H9" s="87">
         <v>38</v>
@@ -19758,13 +19761,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP9" s="11">
+      <c r="AP9" s="86">
         <f t="shared" si="3"/>
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="AQ9" s="90">
+        <v>0.68737000000000004</v>
+      </c>
+      <c r="AQ9" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9-AN9-IF(AO9="SI",Parametros!$E$33,0)))</f>
-        <v>0.59000000000000008</v>
+        <v>0.68737000000000004</v>
       </c>
       <c r="AR9" s="58"/>
       <c r="AS9" s="79" t="str">
@@ -19777,7 +19780,7 @@
       </c>
       <c r="AU9" s="80">
         <f>'Captura Septiembre'!T11</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AV9" s="80">
         <f>'Captura Septiembre'!V11</f>
@@ -19785,7 +19788,7 @@
       </c>
       <c r="AW9" s="80">
         <f>'Captura Septiembre'!G11</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" s="80">
         <f>'Captura Septiembre'!X11</f>
@@ -19801,7 +19804,7 @@
       </c>
       <c r="BA9" s="82">
         <f>'Captura Septiembre'!AQ11</f>
-        <v>0.58519999999999994</v>
+        <v>0.74520000000000008</v>
       </c>
       <c r="BB9" s="58"/>
       <c r="BC9" s="58"/>
@@ -19821,15 +19824,15 @@
         <v>1</v>
       </c>
       <c r="E10" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="86">
         <f>F10*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="87">
         <v>38</v>
@@ -19865,14 +19868,14 @@
         <v>0.08</v>
       </c>
       <c r="R10" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T10" s="86">
         <f>IF(S10="NO",0,R10*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U10" s="85">
         <v>0</v>
@@ -19944,13 +19947,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP10" s="11">
+      <c r="AP10" s="86">
         <f t="shared" si="3"/>
-        <v>0.51</v>
-      </c>
-      <c r="AQ10" s="90">
+        <v>0.67</v>
+      </c>
+      <c r="AQ10" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10-AN10-IF(AO10="SI",Parametros!$E$33,0)))</f>
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="AR10" s="58"/>
       <c r="AS10" s="71" t="str">
@@ -19971,7 +19974,7 @@
       </c>
       <c r="AW10" s="72">
         <f>'Captura Septiembre'!G12</f>
-        <v>0.1</v>
+        <v>0.11364000000000002</v>
       </c>
       <c r="AX10" s="72">
         <f>'Captura Septiembre'!X12</f>
@@ -19987,7 +19990,7 @@
       </c>
       <c r="BA10" s="74">
         <f>'Captura Septiembre'!AQ12</f>
-        <v>0.58200000000000007</v>
+        <v>0.59564000000000006</v>
       </c>
       <c r="BB10" s="58"/>
       <c r="BC10" s="58"/>
@@ -20007,15 +20010,15 @@
         <v>1</v>
       </c>
       <c r="E11" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="86">
         <f>F11*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="87">
         <v>38</v>
@@ -20051,14 +20054,14 @@
         <v>0.08</v>
       </c>
       <c r="R11" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T11" s="86">
         <f>IF(S11="NO",0,R11*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U11" s="85">
         <v>0</v>
@@ -20130,13 +20133,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP11" s="11">
+      <c r="AP11" s="86">
         <f t="shared" si="3"/>
-        <v>0.58519999999999994</v>
-      </c>
-      <c r="AQ11" s="90">
+        <v>0.74520000000000008</v>
+      </c>
+      <c r="AQ11" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11-AN11-IF(AO11="SI",Parametros!$E$33,0)))</f>
-        <v>0.58519999999999994</v>
+        <v>0.74520000000000008</v>
       </c>
       <c r="AR11" s="58"/>
       <c r="AS11" s="79" t="str">
@@ -20157,7 +20160,7 @@
       </c>
       <c r="AW11" s="80">
         <f>'Captura Septiembre'!G13</f>
-        <v>0.1</v>
+        <v>0.184</v>
       </c>
       <c r="AX11" s="80">
         <f>'Captura Septiembre'!X13</f>
@@ -20173,7 +20176,7 @@
       </c>
       <c r="BA11" s="82">
         <f>'Captura Septiembre'!AQ13</f>
-        <v>0.58040000000000003</v>
+        <v>0.66439999999999999</v>
       </c>
       <c r="BB11" s="58"/>
       <c r="BC11" s="58"/>
@@ -20193,15 +20196,15 @@
         <v>1</v>
       </c>
       <c r="E12" s="85">
-        <v>0</v>
+        <v>0.13639999999999999</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.56820000000000004</v>
       </c>
       <c r="G12" s="86">
         <f>F12*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.11364000000000002</v>
       </c>
       <c r="H12" s="87">
         <v>38</v>
@@ -20316,13 +20319,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP12" s="11">
+      <c r="AP12" s="86">
         <f t="shared" si="3"/>
-        <v>0.58200000000000007</v>
-      </c>
-      <c r="AQ12" s="90">
+        <v>0.59564000000000006</v>
+      </c>
+      <c r="AQ12" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12-AN12-IF(AO12="SI",Parametros!$E$33,0)))</f>
-        <v>0.58200000000000007</v>
+        <v>0.59564000000000006</v>
       </c>
       <c r="AR12" s="58"/>
       <c r="AS12" s="71" t="str">
@@ -20343,7 +20346,7 @@
       </c>
       <c r="AW12" s="72">
         <f>'Captura Septiembre'!G14</f>
-        <v>0.1</v>
+        <v>0.192</v>
       </c>
       <c r="AX12" s="72">
         <f>'Captura Septiembre'!X14</f>
@@ -20359,7 +20362,7 @@
       </c>
       <c r="BA12" s="74">
         <f>'Captura Septiembre'!AQ14</f>
-        <v>0.58040000000000003</v>
+        <v>0.6724</v>
       </c>
       <c r="BB12" s="58"/>
       <c r="BC12" s="58"/>
@@ -20379,15 +20382,15 @@
         <v>1</v>
       </c>
       <c r="E13" s="85">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.91999999999999993</v>
       </c>
       <c r="G13" s="86">
         <f>F13*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.184</v>
       </c>
       <c r="H13" s="87">
         <v>38</v>
@@ -20502,13 +20505,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP13" s="11">
+      <c r="AP13" s="86">
         <f t="shared" si="3"/>
-        <v>0.58040000000000003</v>
-      </c>
-      <c r="AQ13" s="90">
+        <v>0.66439999999999999</v>
+      </c>
+      <c r="AQ13" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13-AN13-IF(AO13="SI",Parametros!$E$33,0)))</f>
-        <v>0.58040000000000003</v>
+        <v>0.66439999999999999</v>
       </c>
       <c r="AR13" s="58"/>
       <c r="AS13" s="79" t="str">
@@ -20529,7 +20532,7 @@
       </c>
       <c r="AW13" s="80">
         <f>'Captura Septiembre'!G15</f>
-        <v>0.1</v>
+        <v>0.17700000000000002</v>
       </c>
       <c r="AX13" s="80">
         <f>'Captura Septiembre'!X15</f>
@@ -20545,7 +20548,7 @@
       </c>
       <c r="BA13" s="82">
         <f>'Captura Septiembre'!AQ15</f>
-        <v>0.58679999999999999</v>
+        <v>0.66379999999999995</v>
       </c>
       <c r="BB13" s="58"/>
       <c r="BC13" s="58"/>
@@ -20565,15 +20568,15 @@
         <v>1</v>
       </c>
       <c r="E14" s="85">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.96</v>
       </c>
       <c r="G14" s="86">
         <f>F14*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.192</v>
       </c>
       <c r="H14" s="87">
         <v>38</v>
@@ -20688,13 +20691,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP14" s="11">
+      <c r="AP14" s="86">
         <f t="shared" si="3"/>
-        <v>0.58040000000000003</v>
-      </c>
-      <c r="AQ14" s="90">
+        <v>0.6724</v>
+      </c>
+      <c r="AQ14" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14-AN14-IF(AO14="SI",Parametros!$E$33,0)))</f>
-        <v>0.58040000000000003</v>
+        <v>0.6724</v>
       </c>
       <c r="AR14" s="58"/>
       <c r="AS14" s="71" t="str">
@@ -20715,7 +20718,7 @@
       </c>
       <c r="AW14" s="72">
         <f>'Captura Septiembre'!G16</f>
-        <v>9.3000000000000013E-2</v>
+        <v>0.18600000000000003</v>
       </c>
       <c r="AX14" s="72">
         <f>'Captura Septiembre'!X16</f>
@@ -20731,7 +20734,7 @@
       </c>
       <c r="BA14" s="74">
         <f>'Captura Septiembre'!AQ16</f>
-        <v>0.5766</v>
+        <v>0.66959999999999997</v>
       </c>
       <c r="BB14" s="58"/>
       <c r="BC14" s="58"/>
@@ -20751,15 +20754,15 @@
         <v>1</v>
       </c>
       <c r="E15" s="85">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="G15" s="86">
         <f>F15*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.17700000000000002</v>
       </c>
       <c r="H15" s="87">
         <v>38</v>
@@ -20874,13 +20877,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP15" s="11">
+      <c r="AP15" s="86">
         <f t="shared" si="3"/>
-        <v>0.58679999999999999</v>
-      </c>
-      <c r="AQ15" s="90">
+        <v>0.66379999999999995</v>
+      </c>
+      <c r="AQ15" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15-AN15-IF(AO15="SI",Parametros!$E$33,0)))</f>
-        <v>0.58679999999999999</v>
+        <v>0.66379999999999995</v>
       </c>
       <c r="AR15" s="58"/>
       <c r="AS15" s="79" t="str">
@@ -20901,7 +20904,7 @@
       </c>
       <c r="AW15" s="80">
         <f>'Captura Septiembre'!G17</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AX15" s="80">
         <f>'Captura Septiembre'!X17</f>
@@ -20917,7 +20920,7 @@
       </c>
       <c r="BA15" s="82">
         <f>'Captura Septiembre'!AQ17</f>
-        <v>0.3567999999999999</v>
+        <v>0.45679999999999998</v>
       </c>
       <c r="BB15" s="58"/>
       <c r="BC15" s="58"/>
@@ -20937,15 +20940,15 @@
         <v>0.93</v>
       </c>
       <c r="E16" s="85">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
-        <v>0.46500000000000002</v>
+        <v>0.93</v>
       </c>
       <c r="G16" s="86">
         <f>F16*Parametros!$E$6</f>
-        <v>9.3000000000000013E-2</v>
+        <v>0.18600000000000003</v>
       </c>
       <c r="H16" s="87">
         <v>38</v>
@@ -21060,13 +21063,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP16" s="11">
+      <c r="AP16" s="86">
         <f t="shared" si="3"/>
-        <v>0.5766</v>
-      </c>
-      <c r="AQ16" s="90">
+        <v>0.66959999999999997</v>
+      </c>
+      <c r="AQ16" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16-AN16-IF(AO16="SI",Parametros!$E$33,0)))</f>
-        <v>0.5766</v>
+        <v>0.66959999999999997</v>
       </c>
       <c r="AR16" s="58"/>
       <c r="AS16" s="71" t="str">
@@ -21087,7 +21090,7 @@
       </c>
       <c r="AW16" s="72">
         <f>'Captura Septiembre'!G18</f>
-        <v>0.1</v>
+        <v>0.18100000000000002</v>
       </c>
       <c r="AX16" s="72">
         <f>'Captura Septiembre'!X18</f>
@@ -21103,7 +21106,7 @@
       </c>
       <c r="BA16" s="74">
         <f>'Captura Septiembre'!AQ18</f>
-        <v>0.58040000000000003</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="BB16" s="58"/>
       <c r="BC16" s="58"/>
@@ -21123,15 +21126,15 @@
         <v>1</v>
       </c>
       <c r="E17" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G17" s="86">
         <f>F17*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H17" s="87">
         <v>38</v>
@@ -21246,13 +21249,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP17" s="11">
+      <c r="AP17" s="86">
         <f t="shared" si="3"/>
-        <v>0.50679999999999992</v>
-      </c>
-      <c r="AQ17" s="90">
+        <v>0.60680000000000001</v>
+      </c>
+      <c r="AQ17" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17-AN17-IF(AO17="SI",Parametros!$E$33,0)))</f>
-        <v>0.3567999999999999</v>
+        <v>0.45679999999999998</v>
       </c>
       <c r="AR17" s="58"/>
       <c r="AS17" s="79" t="str">
@@ -21273,7 +21276,7 @@
       </c>
       <c r="AW17" s="80">
         <f>'Captura Septiembre'!G19</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AX17" s="80">
         <f>'Captura Septiembre'!X19</f>
@@ -21289,7 +21292,7 @@
       </c>
       <c r="BA17" s="82">
         <f>'Captura Septiembre'!AQ19</f>
-        <v>0.59000000000000008</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="BB17" s="58"/>
       <c r="BC17" s="58"/>
@@ -21309,15 +21312,15 @@
         <v>1</v>
       </c>
       <c r="E18" s="85">
-        <v>0</v>
+        <v>0.81</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="G18" s="86">
         <f>F18*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.18100000000000002</v>
       </c>
       <c r="H18" s="87">
         <v>38</v>
@@ -21432,13 +21435,13 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP18" s="11">
+      <c r="AP18" s="86">
         <f t="shared" si="3"/>
-        <v>0.58040000000000003</v>
-      </c>
-      <c r="AQ18" s="90">
+        <v>0.66139999999999999</v>
+      </c>
+      <c r="AQ18" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18-AN18-IF(AO18="SI",Parametros!$E$33,0)))</f>
-        <v>0.58040000000000003</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="AR18" s="58"/>
       <c r="AS18" s="71" t="str">
@@ -21495,15 +21498,15 @@
         <v>1</v>
       </c>
       <c r="E19" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G19" s="86">
         <f>F19*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="87">
         <v>38</v>
@@ -21618,28 +21621,28 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP19" s="11">
+      <c r="AP19" s="86">
         <f t="shared" si="3"/>
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="AQ19" s="90">
+        <v>0.69000000000000006</v>
+      </c>
+      <c r="AQ19" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19-AN19-IF(AO19="SI",Parametros!$E$33,0)))</f>
-        <v>0.59000000000000008</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.56254666666666664</v>
+        <v>0.64466400000000013</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -21782,11 +21785,11 @@
         <f t="shared" si="2"/>
         <v>NO</v>
       </c>
-      <c r="AP20" s="11">
+      <c r="AP20" s="86">
         <f t="shared" si="3"/>
         <v>0.5835999999999999</v>
       </c>
-      <c r="AQ20" s="90">
+      <c r="AQ20" s="152">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20-AN20-IF(AO20="SI",Parametros!$E$33,0)))</f>
         <v>0.5835999999999999</v>
       </c>
@@ -21803,9 +21806,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21832,11 +21835,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21878,7 +21881,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="94">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.56254666666666664</v>
+        <v>0.64466400000000013</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -21894,6 +21897,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
+    <mergeCell ref="G2:M2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21908,13 +21918,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
-    <mergeCell ref="G2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21996,62 +21999,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -22060,20 +22063,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -22121,66 +22124,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22392,10 +22395,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24962,16 +24965,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -25138,9 +25141,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -25167,11 +25170,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -25229,6 +25232,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -25243,12 +25252,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25330,62 +25333,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25394,20 +25397,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25455,66 +25458,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25726,10 +25729,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28296,16 +28299,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28472,9 +28475,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28501,11 +28504,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28563,6 +28566,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28577,12 +28586,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28664,62 +28667,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28728,20 +28731,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28789,66 +28792,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -29060,10 +29063,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31630,16 +31633,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31806,9 +31809,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31835,11 +31838,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31897,6 +31900,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31911,12 +31920,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31990,11 +31993,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="149" t="s">
@@ -32127,7 +32130,7 @@
       </c>
       <c r="B14" s="97">
         <f>IF(AVERAGE('Captura Septiembre'!D6:D20)=0,"",'Captura Septiembre'!AQ23)</f>
-        <v>0.56254666666666664</v>
+        <v>0.64466400000000013</v>
       </c>
       <c r="C14" s="12" t="str">
         <f>IF(B14="","",IF(B14&gt;=Parametros!$C$37,"Verde",IF(B14&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -32311,7 +32314,7 @@
       </c>
       <c r="J4" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.68375000000000008</v>
       </c>
       <c r="K4" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
@@ -32327,7 +32330,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.95169444444444451</v>
+        <v>0.96211111111111114</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32368,7 +32371,7 @@
       </c>
       <c r="J5" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.67</v>
       </c>
       <c r="K5" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
@@ -32384,7 +32387,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.91999444444444434</v>
+        <v>0.92888333333333328</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32425,7 +32428,7 @@
       </c>
       <c r="J6" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
-        <v>0.5766</v>
+        <v>0.66959999999999997</v>
       </c>
       <c r="K6" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
@@ -32441,7 +32444,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.9278761904761903</v>
+        <v>0.93820952380952372</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32482,7 +32485,7 @@
       </c>
       <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v>0.3567999999999999</v>
+        <v>0.45679999999999998</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -32498,7 +32501,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.79350091575091575</v>
+        <v>0.80461202686202693</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32539,7 +32542,7 @@
       </c>
       <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
-        <v>0.58040000000000003</v>
+        <v>0.6724</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
@@ -32555,7 +32558,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.86540666666666677</v>
+        <v>0.87562888888888901</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32596,7 +32599,7 @@
       </c>
       <c r="J9" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
-        <v>0.58519999999999994</v>
+        <v>0.74520000000000008</v>
       </c>
       <c r="K9" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
@@ -32612,7 +32615,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.88668888888888886</v>
+        <v>0.90446666666666664</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32653,7 +32656,7 @@
       </c>
       <c r="J10" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
-        <v>0.58040000000000003</v>
+        <v>0.66439999999999999</v>
       </c>
       <c r="K10" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D13=0,"",'Captura Octubre'!AQ13),"")</f>
@@ -32669,7 +32672,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.79534222222222217</v>
+        <v>0.80467555555555537</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32710,7 +32713,7 @@
       </c>
       <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -32726,7 +32729,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.90722222222222237</v>
+        <v>0.92500000000000016</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32767,7 +32770,7 @@
       </c>
       <c r="J12" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.68737000000000004</v>
       </c>
       <c r="K12" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
@@ -32783,7 +32786,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.94216111111111112</v>
+        <v>0.95297999999999994</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32824,7 +32827,7 @@
       </c>
       <c r="J13" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
-        <v>0.58200000000000007</v>
+        <v>0.59564000000000006</v>
       </c>
       <c r="K13" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
@@ -32840,7 +32843,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.82781159420289863</v>
+        <v>0.82932714975845423</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32881,7 +32884,7 @@
       </c>
       <c r="J14" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
-        <v>0.58679999999999999</v>
+        <v>0.66379999999999995</v>
       </c>
       <c r="K14" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
@@ -32897,7 +32900,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.80663680961663431</v>
+        <v>0.81519236517218985</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33052,7 +33055,7 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
-        <v>0.58040000000000003</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
@@ -33068,7 +33071,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.90141721132897601</v>
+        <v>0.91041721132897591</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33109,7 +33112,7 @@
       </c>
       <c r="J18" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="K18" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
@@ -33125,7 +33128,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.87263888888888885</v>
+        <v>0.88375000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -33166,7 +33169,7 @@
       </c>
       <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v>0.56254666666666664</v>
+        <v>0.64466400000000013</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -33225,16 +33228,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -33276,11 +33279,11 @@
       </c>
       <c r="C5" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G20"))</f>
-        <v>9.7266666666666682E-2</v>
+        <v>0.17138400000000004</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" ref="D5:D11" ca="1" si="0">IFERROR(C5/B5,0)</f>
-        <v>0.4863333333333334</v>
+        <v>0.85692000000000013</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33344,11 +33347,11 @@
       </c>
       <c r="C9" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T20"))</f>
-        <v>0</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33476,7 +33479,7 @@
       </c>
       <c r="B23" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,1),$E$23:$E$37,0))</f>
-        <v>Calidad</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C23" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),1)</f>
@@ -33497,7 +33500,7 @@
       </c>
       <c r="B24" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,2),$E$23:$E$37,0))</f>
-        <v>Centro de Distribucion</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C24" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),2)</f>
@@ -33518,7 +33521,7 @@
       </c>
       <c r="B25" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,3),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C25" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),3)</f>
@@ -33530,7 +33533,7 @@
       </c>
       <c r="E25" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ8")*100000-8</f>
-        <v>58992.000000000007</v>
+        <v>68367.000000000015</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33539,7 +33542,7 @@
       </c>
       <c r="B26" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,4),$E$23:$E$37,0))</f>
-        <v>Linea 3</v>
+        <v>Calidad</v>
       </c>
       <c r="C26" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),4)</f>
@@ -33551,7 +33554,7 @@
       </c>
       <c r="E26" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ9")*100000-9</f>
-        <v>58991.000000000007</v>
+        <v>68728</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33560,7 +33563,7 @@
       </c>
       <c r="B27" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,5),$E$23:$E$37,0))</f>
-        <v>Equipos Auxiliares</v>
+        <v>Linea 2</v>
       </c>
       <c r="C27" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),5)</f>
@@ -33572,7 +33575,7 @@
       </c>
       <c r="E27" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ10")*100000-10</f>
-        <v>50990</v>
+        <v>66990</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33581,7 +33584,7 @@
       </c>
       <c r="B28" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,6),$E$23:$E$37,0))</f>
-        <v>Jarabes</v>
+        <v>ETEI</v>
       </c>
       <c r="C28" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),6)</f>
@@ -33593,7 +33596,7 @@
       </c>
       <c r="E28" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ11")*100000-11</f>
-        <v>58508.999999999993</v>
+        <v>74509.000000000015</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33602,7 +33605,7 @@
       </c>
       <c r="B29" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,7),$E$23:$E$37,0))</f>
-        <v>Linea 1</v>
+        <v>Linea 4</v>
       </c>
       <c r="C29" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),7)</f>
@@ -33614,7 +33617,7 @@
       </c>
       <c r="E29" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ12")*100000-12</f>
-        <v>58188.000000000007</v>
+        <v>59552.000000000007</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33623,7 +33626,7 @@
       </c>
       <c r="B30" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,8),$E$23:$E$37,0))</f>
-        <v>Linea 2</v>
+        <v>Linea 1</v>
       </c>
       <c r="C30" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),8)</f>
@@ -33635,7 +33638,7 @@
       </c>
       <c r="E30" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ13")*100000-13</f>
-        <v>58027</v>
+        <v>66427</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33644,7 +33647,7 @@
       </c>
       <c r="B31" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,9),$E$23:$E$37,0))</f>
-        <v>Mantenimiento</v>
+        <v>Linea 3</v>
       </c>
       <c r="C31" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),9)</f>
@@ -33656,7 +33659,7 @@
       </c>
       <c r="E31" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ14")*100000-14</f>
-        <v>58026</v>
+        <v>67226</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33665,7 +33668,7 @@
       </c>
       <c r="B32" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,10),$E$23:$E$37,0))</f>
-        <v>Linea 4</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C32" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),10)</f>
@@ -33677,7 +33680,7 @@
       </c>
       <c r="E32" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ15")*100000-15</f>
-        <v>58665</v>
+        <v>66365</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33686,7 +33689,7 @@
       </c>
       <c r="B33" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,11),$E$23:$E$37,0))</f>
-        <v>Alrededores</v>
+        <v>Jarabes</v>
       </c>
       <c r="C33" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),11)</f>
@@ -33698,7 +33701,7 @@
       </c>
       <c r="E33" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ16")*100000-16</f>
-        <v>57644</v>
+        <v>66944</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33707,7 +33710,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>ETEI</v>
+        <v>Alrededores</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33719,7 +33722,7 @@
       </c>
       <c r="E34" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ17")*100000-17</f>
-        <v>35662.999999999993</v>
+        <v>45663</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33740,7 +33743,7 @@
       </c>
       <c r="E35" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ18")*100000-18</f>
-        <v>58022</v>
+        <v>66122</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33761,7 +33764,7 @@
       </c>
       <c r="E36" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ19")*100000-19</f>
-        <v>58981.000000000007</v>
+        <v>68981</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33824,7 +33827,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.56254666666666664</v>
+        <v>0.64466400000000013</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33979,7 +33982,7 @@
       </c>
       <c r="J4" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.68375000000000008</v>
       </c>
       <c r="K4" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
@@ -33995,7 +33998,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.95169444444444451</v>
+        <v>0.96211111111111114</v>
       </c>
       <c r="O4" s="106"/>
     </row>
@@ -34037,7 +34040,7 @@
       </c>
       <c r="J5" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.68737000000000004</v>
       </c>
       <c r="K5" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
@@ -34053,7 +34056,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.94216111111111112</v>
+        <v>0.95297999999999994</v>
       </c>
       <c r="O5" s="106"/>
     </row>
@@ -34095,7 +34098,7 @@
       </c>
       <c r="J6" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
-        <v>0.5766</v>
+        <v>0.66959999999999997</v>
       </c>
       <c r="K6" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
@@ -34111,7 +34114,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.9278761904761903</v>
+        <v>0.93820952380952372</v>
       </c>
       <c r="O6" s="106"/>
     </row>
@@ -34153,7 +34156,7 @@
       </c>
       <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.67</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
@@ -34169,7 +34172,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.91999444444444434</v>
+        <v>0.92888333333333328</v>
       </c>
       <c r="O7" s="106"/>
     </row>
@@ -34211,7 +34214,7 @@
       </c>
       <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -34227,7 +34230,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.90722222222222237</v>
+        <v>0.92500000000000016</v>
       </c>
       <c r="O8" s="106"/>
     </row>
@@ -34327,7 +34330,7 @@
       </c>
       <c r="J10" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
-        <v>0.58040000000000003</v>
+        <v>0.66139999999999999</v>
       </c>
       <c r="K10" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
@@ -34343,7 +34346,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.90141721132897601</v>
+        <v>0.91041721132897591</v>
       </c>
       <c r="O10" s="106"/>
     </row>
@@ -34385,7 +34388,7 @@
       </c>
       <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
-        <v>0.58519999999999994</v>
+        <v>0.74520000000000008</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
@@ -34401,7 +34404,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.88668888888888886</v>
+        <v>0.90446666666666664</v>
       </c>
       <c r="O11" s="106"/>
     </row>
@@ -34443,7 +34446,7 @@
       </c>
       <c r="J12" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="K12" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
@@ -34459,7 +34462,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.87263888888888885</v>
+        <v>0.88375000000000004</v>
       </c>
       <c r="O12" s="106"/>
     </row>
@@ -34501,7 +34504,7 @@
       </c>
       <c r="J13" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
-        <v>0.58040000000000003</v>
+        <v>0.6724</v>
       </c>
       <c r="K13" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
@@ -34517,7 +34520,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.86540666666666677</v>
+        <v>0.87562888888888901</v>
       </c>
       <c r="O13" s="106"/>
     </row>
@@ -34559,7 +34562,7 @@
       </c>
       <c r="J14" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
-        <v>0.58200000000000007</v>
+        <v>0.59564000000000006</v>
       </c>
       <c r="K14" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
@@ -34575,7 +34578,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.82781159420289863</v>
+        <v>0.82932714975845423</v>
       </c>
       <c r="O14" s="106"/>
     </row>
@@ -34617,7 +34620,7 @@
       </c>
       <c r="J15" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v>0.3567999999999999</v>
+        <v>0.45679999999999998</v>
       </c>
       <c r="K15" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -34633,7 +34636,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.79350091575091575</v>
+        <v>0.80461202686202693</v>
       </c>
       <c r="O15" s="106"/>
     </row>
@@ -34675,7 +34678,7 @@
       </c>
       <c r="J16" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
-        <v>0.58679999999999999</v>
+        <v>0.66379999999999995</v>
       </c>
       <c r="K16" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
@@ -34691,7 +34694,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.80663680961663431</v>
+        <v>0.81519236517218985</v>
       </c>
       <c r="O16" s="106"/>
     </row>
@@ -34733,7 +34736,7 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
-        <v>0.58040000000000003</v>
+        <v>0.66439999999999999</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D13=0,"",'Captura Octubre'!AQ13),"")</f>
@@ -34749,7 +34752,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.79534222222222217</v>
+        <v>0.80467555555555537</v>
       </c>
       <c r="O17" s="106"/>
     </row>
@@ -34849,7 +34852,7 @@
       </c>
       <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v>0.56254666666666664</v>
+        <v>0.64466400000000001</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -34901,44 +34904,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
+      <c r="R2" s="132"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="129"/>
-      <c r="Q3" s="129"/>
-      <c r="R3" s="129"/>
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="132"/>
+      <c r="L3" s="132"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="132"/>
+      <c r="P3" s="132"/>
+      <c r="Q3" s="132"/>
+      <c r="R3" s="132"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34948,141 +34951,141 @@
         <f>Calculos!$B$2</f>
         <v>Septiembre</v>
       </c>
-      <c r="F4" s="130" t="s">
+      <c r="F4" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="130"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="133"/>
+      <c r="R4" s="133"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="131" t="s">
+      <c r="B6" s="134" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131" t="s">
+      <c r="C6" s="134"/>
+      <c r="D6" s="134"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="131"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="131" t="s">
+      <c r="G6" s="134"/>
+      <c r="H6" s="134"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="134" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="131"/>
-      <c r="L6" s="131"/>
-      <c r="M6" s="131" t="s">
+      <c r="K6" s="134"/>
+      <c r="L6" s="134"/>
+      <c r="M6" s="134" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="131"/>
-      <c r="O6" s="131"/>
-      <c r="P6" s="131" t="s">
+      <c r="N6" s="134"/>
+      <c r="O6" s="134"/>
+      <c r="P6" s="134" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="131"/>
-      <c r="R6" s="131"/>
+      <c r="Q6" s="134"/>
+      <c r="R6" s="134"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="131"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
-      <c r="N7" s="131"/>
-      <c r="O7" s="131"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="134"/>
+      <c r="M7" s="134"/>
+      <c r="N7" s="134"/>
+      <c r="O7" s="134"/>
+      <c r="P7" s="134"/>
+      <c r="Q7" s="134"/>
+      <c r="R7" s="134"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="132">
+      <c r="B8" s="127">
         <f ca="1">Calculos!B44</f>
-        <v>0.56254666666666664</v>
-      </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="133" t="str">
+        <v>0.64466400000000013</v>
+      </c>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="128" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="133"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="134">
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="129">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="134"/>
-      <c r="L8" s="134"/>
-      <c r="M8" s="127">
+      <c r="K8" s="129"/>
+      <c r="L8" s="129"/>
+      <c r="M8" s="130">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="127"/>
-      <c r="O8" s="127"/>
-      <c r="P8" s="128">
+      <c r="N8" s="130"/>
+      <c r="O8" s="130"/>
+      <c r="P8" s="131">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="128"/>
-      <c r="R8" s="128"/>
+      <c r="Q8" s="131"/>
+      <c r="R8" s="131"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
-      <c r="L9" s="134"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="127"/>
-      <c r="O9" s="127"/>
-      <c r="P9" s="128"/>
-      <c r="Q9" s="128"/>
-      <c r="R9" s="128"/>
+      <c r="B9" s="127"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="129"/>
+      <c r="K9" s="129"/>
+      <c r="L9" s="129"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="131"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="127"/>
-      <c r="N10" s="127"/>
-      <c r="O10" s="127"/>
-      <c r="P10" s="128"/>
-      <c r="Q10" s="128"/>
-      <c r="R10" s="128"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="129"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="129"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="130"/>
+      <c r="O10" s="130"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="126" t="s">
@@ -35113,7 +35116,7 @@
     <row r="14" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="str">
         <f ca="1">Calculos!B23</f>
-        <v>Calidad</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C14" s="21">
         <f ca="1">Calculos!C23</f>
@@ -35125,13 +35128,13 @@
       </c>
       <c r="H14" s="22">
         <f ca="1">Calculos!D5</f>
-        <v>0.4863333333333334</v>
+        <v>0.85692000000000013</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="str">
         <f ca="1">Calculos!B24</f>
-        <v>Centro de Distribucion</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C15" s="21">
         <f ca="1">Calculos!C24</f>
@@ -35149,7 +35152,7 @@
     <row r="16" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="str">
         <f ca="1">Calculos!B25</f>
-        <v>Materias Primas</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C16" s="21">
         <f ca="1">Calculos!C25</f>
@@ -35167,7 +35170,7 @@
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="str">
         <f ca="1">Calculos!B26</f>
-        <v>Linea 3</v>
+        <v>Calidad</v>
       </c>
       <c r="C17" s="21">
         <f ca="1">Calculos!C26</f>
@@ -35185,7 +35188,7 @@
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="str">
         <f ca="1">Calculos!B27</f>
-        <v>Equipos Auxiliares</v>
+        <v>Linea 2</v>
       </c>
       <c r="C18" s="21">
         <f ca="1">Calculos!C27</f>
@@ -35197,13 +35200,13 @@
       </c>
       <c r="H18" s="22">
         <f ca="1">Calculos!D9</f>
-        <v>0</v>
+        <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="str">
         <f ca="1">Calculos!B28</f>
-        <v>Jarabes</v>
+        <v>ETEI</v>
       </c>
       <c r="C19" s="21">
         <f ca="1">Calculos!C28</f>
@@ -35221,7 +35224,7 @@
     <row r="20" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="str">
         <f ca="1">Calculos!B29</f>
-        <v>Linea 1</v>
+        <v>Linea 4</v>
       </c>
       <c r="C20" s="21">
         <f ca="1">Calculos!C29</f>
@@ -35239,7 +35242,7 @@
     <row r="21" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="str">
         <f ca="1">Calculos!B30</f>
-        <v>Linea 2</v>
+        <v>Linea 1</v>
       </c>
       <c r="C21" s="21">
         <f ca="1">Calculos!C30</f>
@@ -35249,7 +35252,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="str">
         <f ca="1">Calculos!B31</f>
-        <v>Mantenimiento</v>
+        <v>Linea 3</v>
       </c>
       <c r="C22" s="21">
         <f ca="1">Calculos!C31</f>
@@ -35259,7 +35262,7 @@
     <row r="23" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="str">
         <f ca="1">Calculos!B32</f>
-        <v>Linea 4</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C23" s="21">
         <f ca="1">Calculos!C32</f>
@@ -35269,7 +35272,7 @@
     <row r="24" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="str">
         <f ca="1">Calculos!B33</f>
-        <v>Alrededores</v>
+        <v>Jarabes</v>
       </c>
       <c r="C24" s="21">
         <f ca="1">Calculos!C33</f>
@@ -35279,7 +35282,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>ETEI</v>
+        <v>Alrededores</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -35345,11 +35348,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35359,6 +35357,11 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35388,61 +35391,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="145" t="s">
+      <c r="B2" s="137" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="146" t="s">
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="138" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-      <c r="M4" s="147"/>
-      <c r="N4" s="147"/>
-      <c r="O4" s="147"/>
-      <c r="P4" s="147"/>
-      <c r="Q4" s="147"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
+      <c r="I4" s="139"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="139"/>
+      <c r="N4" s="139"/>
+      <c r="O4" s="139"/>
+      <c r="P4" s="139"/>
+      <c r="Q4" s="139"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="148" t="str">
+      <c r="B5" s="140" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  SEPTIEMBRE 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="148"/>
-      <c r="D5" s="148"/>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="148"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="148"/>
-      <c r="Q5" s="148"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35453,7 +35456,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="135" t="str">
+      <c r="A7" s="141" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>SEPTIEMBRE</v>
       </c>
@@ -35470,13 +35473,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="135"/>
-      <c r="G8" s="136">
+      <c r="A8" s="141"/>
+      <c r="G8" s="142">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="136"/>
-      <c r="I8" s="136"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35486,15 +35489,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="135"/>
-      <c r="F9" s="137">
+      <c r="A9" s="141"/>
+      <c r="F9" s="143">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35504,17 +35507,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="135"/>
-      <c r="E10" s="138">
+      <c r="A10" s="141"/>
+      <c r="E10" s="144">
         <f ca="1">X33</f>
         <v>1</v>
       </c>
-      <c r="F10" s="138"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="138"/>
-      <c r="I10" s="138"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="138"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="144"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="144"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35524,19 +35527,19 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="135"/>
-      <c r="D11" s="139">
+      <c r="A11" s="141"/>
+      <c r="D11" s="145">
         <f ca="1">X34</f>
         <v>0</v>
       </c>
-      <c r="E11" s="139"/>
-      <c r="F11" s="139"/>
-      <c r="G11" s="139"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="139"/>
-      <c r="K11" s="139"/>
-      <c r="L11" s="139"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35546,21 +35549,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="135"/>
-      <c r="C12" s="140">
+      <c r="A12" s="141"/>
+      <c r="C12" s="146">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="140"/>
-      <c r="E12" s="140"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="140"/>
-      <c r="L12" s="140"/>
-      <c r="M12" s="140"/>
+      <c r="D12" s="146"/>
+      <c r="E12" s="146"/>
+      <c r="F12" s="146"/>
+      <c r="G12" s="146"/>
+      <c r="H12" s="146"/>
+      <c r="I12" s="146"/>
+      <c r="J12" s="146"/>
+      <c r="K12" s="146"/>
+      <c r="L12" s="146"/>
+      <c r="M12" s="146"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35570,23 +35573,23 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="135"/>
-      <c r="B13" s="141">
+      <c r="A13" s="141"/>
+      <c r="B13" s="147">
         <f ca="1">X36</f>
         <v>24</v>
       </c>
-      <c r="C13" s="141"/>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
-      <c r="M13" s="141"/>
-      <c r="N13" s="141"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="147"/>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="147"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
@@ -35596,23 +35599,23 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="135"/>
-      <c r="B14" s="142">
+      <c r="A14" s="141"/>
+      <c r="B14" s="148">
         <f ca="1">X37</f>
         <v>153</v>
       </c>
-      <c r="C14" s="142"/>
-      <c r="D14" s="142"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="142"/>
-      <c r="G14" s="142"/>
-      <c r="H14" s="142"/>
-      <c r="I14" s="142"/>
-      <c r="J14" s="142"/>
-      <c r="K14" s="142"/>
-      <c r="L14" s="142"/>
-      <c r="M14" s="142"/>
-      <c r="N14" s="142"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="148"/>
+      <c r="I14" s="148"/>
+      <c r="J14" s="148"/>
+      <c r="K14" s="148"/>
+      <c r="L14" s="148"/>
+      <c r="M14" s="148"/>
+      <c r="N14" s="148"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
@@ -35623,22 +35626,22 @@
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="143" t="s">
+      <c r="S16" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="143"/>
-      <c r="U16" s="143"/>
-      <c r="V16" s="143"/>
+      <c r="T16" s="135"/>
+      <c r="U16" s="135"/>
+      <c r="V16" s="135"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S18" s="35">
         <f ca="1">IF(T20="","—",INT(TODAY()-T20))</f>
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="U18" s="35">
         <f ca="1">IF(V20="","—",INT(TODAY()-V20))</f>
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35667,11 +35670,11 @@
     <row r="22" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S22" s="35">
         <f ca="1">IF(T24="","—",INT(TODAY()-T24))</f>
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="U22" s="35">
         <f ca="1">IF(V24="","—",INT(TODAY()-V24))</f>
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35699,42 +35702,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="144" t="s">
+      <c r="B27" s="136" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="144"/>
-      <c r="D27" s="144"/>
-      <c r="E27" s="144"/>
-      <c r="F27" s="144"/>
-      <c r="G27" s="144"/>
-      <c r="H27" s="144"/>
-      <c r="I27" s="144"/>
-      <c r="J27" s="144"/>
-      <c r="K27" s="144"/>
-      <c r="L27" s="144"/>
-      <c r="M27" s="144"/>
-      <c r="N27" s="144"/>
-      <c r="O27" s="144"/>
-      <c r="P27" s="144"/>
-      <c r="Q27" s="144"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="136"/>
+      <c r="G27" s="136"/>
+      <c r="H27" s="136"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="136"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="136"/>
+      <c r="N27" s="136"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="136"/>
+      <c r="Q27" s="136"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="144"/>
-      <c r="C28" s="144"/>
-      <c r="D28" s="144"/>
-      <c r="E28" s="144"/>
-      <c r="F28" s="144"/>
-      <c r="G28" s="144"/>
-      <c r="H28" s="144"/>
-      <c r="I28" s="144"/>
-      <c r="J28" s="144"/>
-      <c r="K28" s="144"/>
-      <c r="L28" s="144"/>
-      <c r="M28" s="144"/>
-      <c r="N28" s="144"/>
-      <c r="O28" s="144"/>
-      <c r="P28" s="144"/>
-      <c r="Q28" s="144"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="136"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="136"/>
+      <c r="O28" s="136"/>
+      <c r="P28" s="136"/>
+      <c r="Q28" s="136"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35840,12 +35843,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35854,6 +35851,12 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -35888,13 +35891,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="126" t="s">
@@ -36488,62 +36491,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36552,20 +36555,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36613,66 +36616,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36884,10 +36887,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39454,16 +39457,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93297435897435899</v>
@@ -39635,9 +39638,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39664,11 +39667,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39726,6 +39729,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39740,12 +39749,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39827,62 +39830,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39891,20 +39894,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39952,66 +39955,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -40223,10 +40226,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42793,16 +42796,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42969,9 +42972,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42998,11 +43001,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -43060,6 +43063,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -43074,12 +43083,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -43161,62 +43164,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -43225,20 +43228,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -43286,66 +43289,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43557,10 +43560,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -46127,16 +46130,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46303,9 +46306,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46332,11 +46335,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46394,6 +46397,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46408,12 +46417,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46495,62 +46498,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="116" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="116"/>
+      <c r="Z1" s="116"/>
+      <c r="AA1" s="116"/>
+      <c r="AB1" s="116"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="110" t="s">
+      <c r="AS1" s="117" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="110"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="110"/>
-      <c r="AZ1" s="110"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="111" t="s">
+      <c r="AT1" s="117"/>
+      <c r="AU1" s="117"/>
+      <c r="AV1" s="117"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="117"/>
+      <c r="AY1" s="117"/>
+      <c r="AZ1" s="117"/>
+      <c r="BA1" s="117"/>
+      <c r="BB1" s="118" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="111"/>
+      <c r="BC1" s="118"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46559,20 +46562,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="113" t="s">
+      <c r="AT2" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="113"/>
-      <c r="AV2" s="113"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="114" t="s">
+      <c r="AX2" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="114"/>
-      <c r="AZ2" s="114"/>
-      <c r="BA2" s="114"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="121"/>
+      <c r="BA2" s="121"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46620,66 +46623,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="120" t="s">
+      <c r="D4" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120" t="s">
+      <c r="I4" s="113"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120" t="s">
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120" t="s">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="120"/>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120" t="s">
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="120"/>
-      <c r="W4" s="121" t="s">
+      <c r="V4" s="113"/>
+      <c r="W4" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="120" t="s">
+      <c r="X4" s="114"/>
+      <c r="Y4" s="113" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
-      <c r="AC4" s="120"/>
-      <c r="AD4" s="121" t="s">
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="121"/>
-      <c r="AF4" s="121"/>
-      <c r="AG4" s="121"/>
-      <c r="AH4" s="121"/>
-      <c r="AI4" s="121"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="122" t="s">
+      <c r="AE4" s="114"/>
+      <c r="AF4" s="114"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="122"/>
+      <c r="AQ4" s="115"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46891,10 +46894,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="116" t="s">
+      <c r="BB5" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="116"/>
+      <c r="BC5" s="109"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49461,16 +49464,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="117" t="s">
+      <c r="AS19" s="110" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="117"/>
-      <c r="AU19" s="117"/>
-      <c r="AV19" s="117"/>
-      <c r="AW19" s="117"/>
-      <c r="AX19" s="117"/>
-      <c r="AY19" s="117"/>
-      <c r="AZ19" s="117"/>
+      <c r="AT19" s="110"/>
+      <c r="AU19" s="110"/>
+      <c r="AV19" s="110"/>
+      <c r="AW19" s="110"/>
+      <c r="AX19" s="110"/>
+      <c r="AY19" s="110"/>
+      <c r="AZ19" s="110"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49637,9 +49640,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="118"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="118"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49666,11 +49669,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="112"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49728,6 +49731,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49742,12 +49751,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49817,6 +49820,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -50063,17 +50077,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
   <ds:schemaRefs>
@@ -50083,6 +50086,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76AB9A25-5769-416B-8E9A-2215F01CC611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50099,21 +50119,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA67CA16-A5A2-4E0A-8AD2-841C1B21F8D6}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0CAE63F-2B83-4D82-BBB4-F0D1F7017FC0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2137,26 +2137,8 @@
     <xf numFmtId="0" fontId="45" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2179,6 +2161,27 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2187,15 +2190,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2211,23 +2205,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2253,6 +2238,24 @@
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2261,9 +2264,6 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3282,22 +3282,22 @@
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>ETEI</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Equipos Auxiliares</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Materias Primas</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>Centro de Distribucion</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Calidad</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Linea 2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>ETEI</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Linea 4</c:v>
@@ -3705,10 +3705,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.84466666666666668</c:v>
+                  <c:v>0.96933333333333327</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.84466666666666668</c:v>
+                  <c:v>0.96933333333333327</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.13333333333333333</c:v>
@@ -4386,7 +4386,7 @@
                   <c:v>0.86230933333333326</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64466400000000013</c:v>
+                  <c:v>0.6546373333333334</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5122,38 +5122,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="124" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
+      <c r="B3" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
     </row>
     <row r="4" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="124"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
     </row>
     <row r="5" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
     </row>
     <row r="6" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="124"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
+      <c r="B6" s="125"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
     </row>
     <row r="7" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="125" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
+      <c r="B7" s="126" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
     </row>
     <row r="10" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -5207,72 +5207,72 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="126"/>
-      <c r="D18" s="126"/>
-      <c r="E18" s="126"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="127"/>
     </row>
     <row r="19" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="123" t="s">
+      <c r="C19" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="C20" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
     </row>
     <row r="21" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="123" t="s">
+      <c r="C21" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
     </row>
     <row r="22" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="123" t="s">
+      <c r="C22" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="123"/>
-      <c r="E22" s="123"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="124"/>
     </row>
     <row r="23" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="123" t="s">
+      <c r="C23" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="123"/>
-      <c r="E23" s="123"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="124"/>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="123" t="s">
+      <c r="C24" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="123"/>
-      <c r="E24" s="123"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5313,62 +5313,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5377,20 +5377,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5438,66 +5438,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5709,10 +5709,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8279,16 +8279,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.8793333333333333</v>
@@ -8455,9 +8455,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8484,11 +8484,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8546,12 +8546,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8566,6 +8560,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8647,62 +8647,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8711,20 +8711,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8772,66 +8772,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -9043,10 +9043,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11613,16 +11613,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11789,9 +11789,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11818,11 +11818,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11880,12 +11880,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11900,6 +11894,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11983,62 +11983,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -12047,20 +12047,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -12108,66 +12108,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12379,10 +12379,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14949,16 +14949,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -15125,9 +15125,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -15154,11 +15154,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -15216,12 +15216,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -15236,6 +15230,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15321,62 +15321,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15385,20 +15385,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15446,66 +15446,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15717,10 +15717,10 @@
         <f>'Captura Agosto'!AQ7</f>
         <v>0.64449999999999996</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -18287,16 +18287,16 @@
         <v>0.97124999999999995</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.86230933333333326</v>
@@ -18463,9 +18463,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18492,11 +18492,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18554,12 +18554,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18574,6 +18568,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18658,90 +18658,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="122" t="s">
+      <c r="G2" s="116" t="s">
         <v>166</v>
       </c>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18789,66 +18789,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="107" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -19060,10 +19060,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.55600000000000005</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -19207,7 +19207,7 @@
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
         <v>0.67</v>
       </c>
-      <c r="AQ6" s="152">
+      <c r="AQ6" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6-AN6-IF(AO6="SI",Parametros!$E$33,0)))</f>
         <v>0.67</v>
       </c>
@@ -19393,7 +19393,7 @@
         <f t="shared" si="3"/>
         <v>0.55600000000000005</v>
       </c>
-      <c r="AQ7" s="152">
+      <c r="AQ7" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7-AN7-IF(AO7="SI",Parametros!$E$33,0)))</f>
         <v>0.55600000000000005</v>
       </c>
@@ -19579,7 +19579,7 @@
         <f t="shared" si="3"/>
         <v>0.68375000000000008</v>
       </c>
-      <c r="AQ8" s="152">
+      <c r="AQ8" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8-AN8-IF(AO8="SI",Parametros!$E$33,0)))</f>
         <v>0.68375000000000008</v>
       </c>
@@ -19590,7 +19590,7 @@
       </c>
       <c r="AT8" s="72">
         <f>'Captura Septiembre'!K10+'Captura Septiembre'!N10+'Captura Septiembre'!Q10</f>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="AU8" s="72">
         <f>'Captura Septiembre'!T10</f>
@@ -19618,7 +19618,7 @@
       </c>
       <c r="BA8" s="74">
         <f>'Captura Septiembre'!AQ10</f>
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BB8" s="58"/>
       <c r="BC8" s="58"/>
@@ -19765,7 +19765,7 @@
         <f t="shared" si="3"/>
         <v>0.68737000000000004</v>
       </c>
-      <c r="AQ9" s="152">
+      <c r="AQ9" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9-AN9-IF(AO9="SI",Parametros!$E$33,0)))</f>
         <v>0.68737000000000004</v>
       </c>
@@ -19848,14 +19848,14 @@
         <v>0.08</v>
       </c>
       <c r="L10" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N10" s="86">
         <f>IF(M10="NO",0,L10*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O10" s="85">
         <v>1</v>
@@ -19949,11 +19949,11 @@
       </c>
       <c r="AP10" s="86">
         <f t="shared" si="3"/>
-        <v>0.67</v>
-      </c>
-      <c r="AQ10" s="152">
+        <v>0.75</v>
+      </c>
+      <c r="AQ10" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10-AN10-IF(AO10="SI",Parametros!$E$33,0)))</f>
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AR10" s="58"/>
       <c r="AS10" s="71" t="str">
@@ -20137,7 +20137,7 @@
         <f t="shared" si="3"/>
         <v>0.74520000000000008</v>
       </c>
-      <c r="AQ11" s="152">
+      <c r="AQ11" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11-AN11-IF(AO11="SI",Parametros!$E$33,0)))</f>
         <v>0.74520000000000008</v>
       </c>
@@ -20323,7 +20323,7 @@
         <f t="shared" si="3"/>
         <v>0.59564000000000006</v>
       </c>
-      <c r="AQ12" s="152">
+      <c r="AQ12" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12-AN12-IF(AO12="SI",Parametros!$E$33,0)))</f>
         <v>0.59564000000000006</v>
       </c>
@@ -20509,7 +20509,7 @@
         <f t="shared" si="3"/>
         <v>0.66439999999999999</v>
       </c>
-      <c r="AQ13" s="152">
+      <c r="AQ13" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13-AN13-IF(AO13="SI",Parametros!$E$33,0)))</f>
         <v>0.66439999999999999</v>
       </c>
@@ -20695,7 +20695,7 @@
         <f t="shared" si="3"/>
         <v>0.6724</v>
       </c>
-      <c r="AQ14" s="152">
+      <c r="AQ14" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14-AN14-IF(AO14="SI",Parametros!$E$33,0)))</f>
         <v>0.6724</v>
       </c>
@@ -20881,7 +20881,7 @@
         <f t="shared" si="3"/>
         <v>0.66379999999999995</v>
       </c>
-      <c r="AQ15" s="152">
+      <c r="AQ15" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15-AN15-IF(AO15="SI",Parametros!$E$33,0)))</f>
         <v>0.66379999999999995</v>
       </c>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="AT15" s="80">
         <f>'Captura Septiembre'!K17+'Captura Septiembre'!N17+'Captura Septiembre'!Q17</f>
-        <v>0.15679999999999999</v>
+        <v>0.22639999999999999</v>
       </c>
       <c r="AU15" s="80">
         <f>'Captura Septiembre'!T17</f>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="BA15" s="82">
         <f>'Captura Septiembre'!AQ17</f>
-        <v>0.45679999999999998</v>
+        <v>0.52639999999999998</v>
       </c>
       <c r="BB15" s="58"/>
       <c r="BC15" s="58"/>
@@ -21067,7 +21067,7 @@
         <f t="shared" si="3"/>
         <v>0.66959999999999997</v>
       </c>
-      <c r="AQ16" s="152">
+      <c r="AQ16" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16-AN16-IF(AO16="SI",Parametros!$E$33,0)))</f>
         <v>0.66959999999999997</v>
       </c>
@@ -21150,14 +21150,14 @@
         <v>0.08</v>
       </c>
       <c r="L17" s="85">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M17" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N17" s="86">
         <f>IF(M17="NO",0,L17*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>6.9599999999999995E-2</v>
       </c>
       <c r="O17" s="85">
         <v>0.96</v>
@@ -21251,11 +21251,11 @@
       </c>
       <c r="AP17" s="86">
         <f t="shared" si="3"/>
-        <v>0.60680000000000001</v>
-      </c>
-      <c r="AQ17" s="152">
+        <v>0.6764</v>
+      </c>
+      <c r="AQ17" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17-AN17-IF(AO17="SI",Parametros!$E$33,0)))</f>
-        <v>0.45679999999999998</v>
+        <v>0.52639999999999998</v>
       </c>
       <c r="AR17" s="58"/>
       <c r="AS17" s="79" t="str">
@@ -21439,7 +21439,7 @@
         <f t="shared" si="3"/>
         <v>0.66139999999999999</v>
       </c>
-      <c r="AQ18" s="152">
+      <c r="AQ18" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18-AN18-IF(AO18="SI",Parametros!$E$33,0)))</f>
         <v>0.66139999999999999</v>
       </c>
@@ -21625,24 +21625,24 @@
         <f t="shared" si="3"/>
         <v>0.69000000000000006</v>
       </c>
-      <c r="AQ19" s="152">
+      <c r="AQ19" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19-AN19-IF(AO19="SI",Parametros!$E$33,0)))</f>
         <v>0.69000000000000006</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.64466400000000013</v>
+        <v>0.6546373333333334</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -21789,7 +21789,7 @@
         <f t="shared" si="3"/>
         <v>0.5835999999999999</v>
       </c>
-      <c r="AQ20" s="152">
+      <c r="AQ20" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20-AN20-IF(AO20="SI",Parametros!$E$33,0)))</f>
         <v>0.5835999999999999</v>
       </c>
@@ -21806,9 +21806,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21835,11 +21835,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21881,7 +21881,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="94">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.64466400000000013</v>
+        <v>0.6546373333333334</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -21897,13 +21897,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
-    <mergeCell ref="G2:M2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21918,6 +21911,13 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
+    <mergeCell ref="G2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21999,62 +21999,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -22063,20 +22063,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -22124,66 +22124,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22395,10 +22395,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24965,16 +24965,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -25141,9 +25141,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -25170,11 +25170,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -25232,12 +25232,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -25252,6 +25246,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25333,62 +25333,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25397,20 +25397,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25458,66 +25458,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25729,10 +25729,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28299,16 +28299,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28475,9 +28475,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28504,11 +28504,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28566,12 +28566,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28586,6 +28580,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28667,62 +28667,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28731,20 +28731,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28792,66 +28792,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -29063,10 +29063,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31633,16 +31633,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31809,9 +31809,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31838,11 +31838,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31900,12 +31900,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31920,6 +31914,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31993,21 +31993,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="149" t="s">
+      <c r="A3" s="150" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="149"/>
-      <c r="C3" s="149"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -32130,7 +32130,7 @@
       </c>
       <c r="B14" s="97">
         <f>IF(AVERAGE('Captura Septiembre'!D6:D20)=0,"",'Captura Septiembre'!AQ23)</f>
-        <v>0.64466400000000013</v>
+        <v>0.6546373333333334</v>
       </c>
       <c r="C14" s="12" t="str">
         <f>IF(B14="","",IF(B14&gt;=Parametros!$C$37,"Verde",IF(B14&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -32215,22 +32215,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="151" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="99" t="s">
@@ -32485,7 +32485,7 @@
       </c>
       <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v>0.45679999999999998</v>
+        <v>0.52639999999999998</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.80461202686202693</v>
+        <v>0.81234536019536019</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32713,7 +32713,7 @@
       </c>
       <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -32729,7 +32729,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.92500000000000016</v>
+        <v>0.93388888888888899</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v>0.64466400000000013</v>
+        <v>0.6546373333333334</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -33189,21 +33189,21 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="151" t="s">
+      <c r="A20" s="152" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="151"/>
-      <c r="C20" s="151"/>
-      <c r="D20" s="151"/>
-      <c r="E20" s="151"/>
-      <c r="F20" s="151"/>
-      <c r="G20" s="151"/>
-      <c r="H20" s="151"/>
-      <c r="I20" s="151"/>
-      <c r="J20" s="151"/>
-      <c r="K20" s="151"/>
-      <c r="L20" s="151"/>
-      <c r="M20" s="151"/>
+      <c r="B20" s="152"/>
+      <c r="C20" s="152"/>
+      <c r="D20" s="152"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="152"/>
+      <c r="G20" s="152"/>
+      <c r="H20" s="152"/>
+      <c r="I20" s="152"/>
+      <c r="J20" s="152"/>
+      <c r="K20" s="152"/>
+      <c r="L20" s="152"/>
+      <c r="M20" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -33228,16 +33228,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -33248,12 +33248,12 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="126" t="s">
+      <c r="A3" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
@@ -33313,11 +33313,11 @@
       </c>
       <c r="C7" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>6.7573333333333332E-2</v>
+        <v>7.7546666666666667E-2</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.84466666666666668</v>
+        <v>0.96933333333333327</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33330,11 +33330,11 @@
       </c>
       <c r="C8" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>6.7573333333333332E-2</v>
+        <v>7.7546666666666667E-2</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.84466666666666668</v>
+        <v>0.96933333333333327</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33389,10 +33389,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="126"/>
+      <c r="B13" s="127"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
@@ -33449,12 +33449,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="126" t="s">
+      <c r="A21" s="127" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
+      <c r="B21" s="127"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="127"/>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -33479,7 +33479,7 @@
       </c>
       <c r="B23" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,1),$E$23:$E$37,0))</f>
-        <v>Equipos Auxiliares</v>
+        <v>ETEI</v>
       </c>
       <c r="C23" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),1)</f>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="B24" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,2),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C24" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),2)</f>
@@ -33521,7 +33521,7 @@
       </c>
       <c r="B25" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,3),$E$23:$E$37,0))</f>
-        <v>Centro de Distribucion</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C25" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),3)</f>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="B26" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,4),$E$23:$E$37,0))</f>
-        <v>Calidad</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C26" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),4)</f>
@@ -33563,7 +33563,7 @@
       </c>
       <c r="B27" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,5),$E$23:$E$37,0))</f>
-        <v>Linea 2</v>
+        <v>Calidad</v>
       </c>
       <c r="C27" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),5)</f>
@@ -33575,7 +33575,7 @@
       </c>
       <c r="E27" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ10")*100000-10</f>
-        <v>66990</v>
+        <v>74990</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33584,7 +33584,7 @@
       </c>
       <c r="B28" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,6),$E$23:$E$37,0))</f>
-        <v>ETEI</v>
+        <v>Linea 2</v>
       </c>
       <c r="C28" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),6)</f>
@@ -33722,7 +33722,7 @@
       </c>
       <c r="E34" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ17")*100000-17</f>
-        <v>45663</v>
+        <v>52623</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33789,10 +33789,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="126" t="s">
+      <c r="A39" s="127" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="126"/>
+      <c r="B39" s="127"/>
     </row>
     <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
@@ -33827,7 +33827,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.64466400000000013</v>
+        <v>0.6546373333333334</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33883,22 +33883,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="151" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
     </row>
     <row r="3" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="99" t="s">
@@ -34214,7 +34214,7 @@
       </c>
       <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.92500000000000016</v>
+        <v>0.93388888888888899</v>
       </c>
       <c r="O8" s="106"/>
     </row>
@@ -34620,7 +34620,7 @@
       </c>
       <c r="J15" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v>0.45679999999999998</v>
+        <v>0.52639999999999998</v>
       </c>
       <c r="K15" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -34636,7 +34636,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.80461202686202693</v>
+        <v>0.81234536019536019</v>
       </c>
       <c r="O15" s="106"/>
     </row>
@@ -34852,7 +34852,7 @@
       </c>
       <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v>0.64466400000000001</v>
+        <v>0.65463733333333329</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -34904,44 +34904,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
-      <c r="R2" s="132"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="130"/>
+      <c r="Q2" s="130"/>
+      <c r="R2" s="130"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="132"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="132"/>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="132"/>
-      <c r="R3" s="132"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="130"/>
+      <c r="R3" s="130"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34951,153 +34951,153 @@
         <f>Calculos!$B$2</f>
         <v>Septiembre</v>
       </c>
-      <c r="F4" s="133" t="s">
+      <c r="F4" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="133"/>
-      <c r="N4" s="133"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="133"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="131"/>
+      <c r="O4" s="131"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134" t="s">
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="134" t="s">
+      <c r="G6" s="132"/>
+      <c r="H6" s="132"/>
+      <c r="I6" s="132"/>
+      <c r="J6" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="134" t="s">
+      <c r="K6" s="132"/>
+      <c r="L6" s="132"/>
+      <c r="M6" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="134"/>
-      <c r="O6" s="134"/>
-      <c r="P6" s="134" t="s">
+      <c r="N6" s="132"/>
+      <c r="O6" s="132"/>
+      <c r="P6" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="134"/>
-      <c r="R6" s="134"/>
+      <c r="Q6" s="132"/>
+      <c r="R6" s="132"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="134"/>
-      <c r="L7" s="134"/>
-      <c r="M7" s="134"/>
-      <c r="N7" s="134"/>
-      <c r="O7" s="134"/>
-      <c r="P7" s="134"/>
-      <c r="Q7" s="134"/>
-      <c r="R7" s="134"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="132"/>
+      <c r="M7" s="132"/>
+      <c r="N7" s="132"/>
+      <c r="O7" s="132"/>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="132"/>
+      <c r="R7" s="132"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="127">
+      <c r="B8" s="133">
         <f ca="1">Calculos!B44</f>
-        <v>0.64466400000000013</v>
-      </c>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="128" t="str">
+        <v>0.6546373333333334</v>
+      </c>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="134" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="128"/>
-      <c r="H8" s="128"/>
-      <c r="I8" s="128"/>
-      <c r="J8" s="129">
+      <c r="G8" s="134"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="134"/>
+      <c r="J8" s="135">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="129"/>
-      <c r="L8" s="129"/>
-      <c r="M8" s="130">
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
+      <c r="M8" s="128">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="130"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="131">
+      <c r="N8" s="128"/>
+      <c r="O8" s="128"/>
+      <c r="P8" s="129">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="131"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="129"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="129"/>
-      <c r="K9" s="129"/>
-      <c r="L9" s="129"/>
-      <c r="M9" s="130"/>
-      <c r="N9" s="130"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="131"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="135"/>
+      <c r="M9" s="128"/>
+      <c r="N9" s="128"/>
+      <c r="O9" s="128"/>
+      <c r="P9" s="129"/>
+      <c r="Q9" s="129"/>
+      <c r="R9" s="129"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="128"/>
-      <c r="G10" s="128"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="129"/>
-      <c r="K10" s="129"/>
-      <c r="L10" s="129"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="135"/>
+      <c r="L10" s="135"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
+      <c r="P10" s="129"/>
+      <c r="Q10" s="129"/>
+      <c r="R10" s="129"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="126" t="s">
+      <c r="B12" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="G12" s="126" t="s">
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="G12" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="126"/>
+      <c r="H12" s="127"/>
     </row>
     <row r="13" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
@@ -35116,7 +35116,7 @@
     <row r="14" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="str">
         <f ca="1">Calculos!B23</f>
-        <v>Equipos Auxiliares</v>
+        <v>ETEI</v>
       </c>
       <c r="C14" s="21">
         <f ca="1">Calculos!C23</f>
@@ -35134,7 +35134,7 @@
     <row r="15" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="str">
         <f ca="1">Calculos!B24</f>
-        <v>Materias Primas</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C15" s="21">
         <f ca="1">Calculos!C24</f>
@@ -35152,7 +35152,7 @@
     <row r="16" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="str">
         <f ca="1">Calculos!B25</f>
-        <v>Centro de Distribucion</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C16" s="21">
         <f ca="1">Calculos!C25</f>
@@ -35164,13 +35164,13 @@
       </c>
       <c r="H16" s="22">
         <f ca="1">Calculos!D7</f>
-        <v>0.84466666666666668</v>
+        <v>0.96933333333333327</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="str">
         <f ca="1">Calculos!B26</f>
-        <v>Calidad</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C17" s="21">
         <f ca="1">Calculos!C26</f>
@@ -35182,13 +35182,13 @@
       </c>
       <c r="H17" s="22">
         <f ca="1">Calculos!D8</f>
-        <v>0.84466666666666668</v>
+        <v>0.96933333333333327</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="str">
         <f ca="1">Calculos!B27</f>
-        <v>Linea 2</v>
+        <v>Calidad</v>
       </c>
       <c r="C18" s="21">
         <f ca="1">Calculos!C27</f>
@@ -35206,7 +35206,7 @@
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="str">
         <f ca="1">Calculos!B28</f>
-        <v>ETEI</v>
+        <v>Linea 2</v>
       </c>
       <c r="C19" s="21">
         <f ca="1">Calculos!C28</f>
@@ -35348,6 +35348,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35357,11 +35362,6 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35391,61 +35391,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="146" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="138" t="s">
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="147" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="139" t="s">
+      <c r="B4" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="139"/>
-      <c r="H4" s="139"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="139"/>
-      <c r="K4" s="139"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="139"/>
-      <c r="N4" s="139"/>
-      <c r="O4" s="139"/>
-      <c r="P4" s="139"/>
-      <c r="Q4" s="139"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148"/>
+      <c r="K4" s="148"/>
+      <c r="L4" s="148"/>
+      <c r="M4" s="148"/>
+      <c r="N4" s="148"/>
+      <c r="O4" s="148"/>
+      <c r="P4" s="148"/>
+      <c r="Q4" s="148"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="140" t="str">
+      <c r="B5" s="149" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  SEPTIEMBRE 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
-      <c r="M5" s="140"/>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="140"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="149"/>
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="149"/>
+      <c r="N5" s="149"/>
+      <c r="O5" s="149"/>
+      <c r="P5" s="149"/>
+      <c r="Q5" s="149"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35456,7 +35456,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="141" t="str">
+      <c r="A7" s="136" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>SEPTIEMBRE</v>
       </c>
@@ -35473,13 +35473,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="141"/>
-      <c r="G8" s="142">
+      <c r="A8" s="136"/>
+      <c r="G8" s="137">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35489,15 +35489,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="141"/>
-      <c r="F9" s="143">
+      <c r="A9" s="136"/>
+      <c r="F9" s="138">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="143"/>
-      <c r="H9" s="143"/>
-      <c r="I9" s="143"/>
-      <c r="J9" s="143"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="138"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35507,17 +35507,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="141"/>
-      <c r="E10" s="144">
+      <c r="A10" s="136"/>
+      <c r="E10" s="139">
         <f ca="1">X33</f>
         <v>1</v>
       </c>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="144"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="139"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35527,19 +35527,19 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="141"/>
-      <c r="D11" s="145">
+      <c r="A11" s="136"/>
+      <c r="D11" s="140">
         <f ca="1">X34</f>
         <v>0</v>
       </c>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="145"/>
-      <c r="K11" s="145"/>
-      <c r="L11" s="145"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="140"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35549,21 +35549,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="141"/>
-      <c r="C12" s="146">
+      <c r="A12" s="136"/>
+      <c r="C12" s="141">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="146"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="146"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="146"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="146"/>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
+      <c r="D12" s="141"/>
+      <c r="E12" s="141"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="141"/>
+      <c r="H12" s="141"/>
+      <c r="I12" s="141"/>
+      <c r="J12" s="141"/>
+      <c r="K12" s="141"/>
+      <c r="L12" s="141"/>
+      <c r="M12" s="141"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35573,23 +35573,23 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="141"/>
-      <c r="B13" s="147">
+      <c r="A13" s="136"/>
+      <c r="B13" s="142">
         <f ca="1">X36</f>
         <v>24</v>
       </c>
-      <c r="C13" s="147"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="147"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
+      <c r="C13" s="142"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="142"/>
+      <c r="N13" s="142"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
@@ -35599,23 +35599,23 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="141"/>
-      <c r="B14" s="148">
+      <c r="A14" s="136"/>
+      <c r="B14" s="143">
         <f ca="1">X37</f>
         <v>153</v>
       </c>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="H14" s="148"/>
-      <c r="I14" s="148"/>
-      <c r="J14" s="148"/>
-      <c r="K14" s="148"/>
-      <c r="L14" s="148"/>
-      <c r="M14" s="148"/>
-      <c r="N14" s="148"/>
+      <c r="C14" s="143"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="143"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="143"/>
+      <c r="L14" s="143"/>
+      <c r="M14" s="143"/>
+      <c r="N14" s="143"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
@@ -35626,12 +35626,12 @@
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="135" t="s">
+      <c r="S16" s="144" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="135"/>
-      <c r="U16" s="135"/>
-      <c r="V16" s="135"/>
+      <c r="T16" s="144"/>
+      <c r="U16" s="144"/>
+      <c r="V16" s="144"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -35702,42 +35702,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="136" t="s">
+      <c r="B27" s="145" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="136"/>
-      <c r="D27" s="136"/>
-      <c r="E27" s="136"/>
-      <c r="F27" s="136"/>
-      <c r="G27" s="136"/>
-      <c r="H27" s="136"/>
-      <c r="I27" s="136"/>
-      <c r="J27" s="136"/>
-      <c r="K27" s="136"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="136"/>
-      <c r="N27" s="136"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="136"/>
-      <c r="Q27" s="136"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="145"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="145"/>
+      <c r="H27" s="145"/>
+      <c r="I27" s="145"/>
+      <c r="J27" s="145"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="145"/>
+      <c r="N27" s="145"/>
+      <c r="O27" s="145"/>
+      <c r="P27" s="145"/>
+      <c r="Q27" s="145"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="136"/>
-      <c r="C28" s="136"/>
-      <c r="D28" s="136"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="136"/>
-      <c r="G28" s="136"/>
-      <c r="H28" s="136"/>
-      <c r="I28" s="136"/>
-      <c r="J28" s="136"/>
-      <c r="K28" s="136"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="136"/>
-      <c r="N28" s="136"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="136"/>
-      <c r="Q28" s="136"/>
+      <c r="B28" s="145"/>
+      <c r="C28" s="145"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="145"/>
+      <c r="G28" s="145"/>
+      <c r="H28" s="145"/>
+      <c r="I28" s="145"/>
+      <c r="J28" s="145"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="145"/>
+      <c r="N28" s="145"/>
+      <c r="O28" s="145"/>
+      <c r="P28" s="145"/>
+      <c r="Q28" s="145"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35843,6 +35843,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35851,12 +35857,6 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -35891,26 +35891,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="110" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="126" t="s">
+      <c r="B4" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="H4" s="126" t="s">
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="H4" s="127" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="126"/>
+      <c r="I4" s="127"/>
     </row>
     <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
@@ -36171,13 +36171,13 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="126" t="s">
+      <c r="B16" s="127" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
       <c r="H16" s="8">
         <v>11</v>
       </c>
@@ -36260,13 +36260,13 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="126" t="s">
+      <c r="B21" s="127" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="127"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
@@ -36313,13 +36313,13 @@
       <c r="F25" s="52"/>
     </row>
     <row r="27" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="C27" s="126"/>
-      <c r="D27" s="126"/>
-      <c r="E27" s="126"/>
-      <c r="F27" s="126"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="127"/>
+      <c r="E27" s="127"/>
+      <c r="F27" s="127"/>
     </row>
     <row r="28" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
@@ -36388,13 +36388,13 @@
       <c r="F33" s="52"/>
     </row>
     <row r="35" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="126" t="s">
+      <c r="B35" s="127" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="126"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="126"/>
-      <c r="F35" s="126"/>
+      <c r="C35" s="127"/>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
     </row>
     <row r="36" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="7" t="s">
@@ -36491,62 +36491,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36555,20 +36555,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36616,66 +36616,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36887,10 +36887,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39457,16 +39457,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93297435897435899</v>
@@ -39638,9 +39638,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39667,11 +39667,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39729,12 +39729,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39749,6 +39743,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39830,62 +39830,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39894,20 +39894,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39955,66 +39955,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -40226,10 +40226,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42796,16 +42796,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42972,9 +42972,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -43001,11 +43001,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -43063,12 +43063,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -43083,6 +43077,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -43164,62 +43164,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -43228,20 +43228,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -43289,66 +43289,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43560,10 +43560,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -46130,16 +46130,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46306,9 +46306,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46335,11 +46335,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46397,12 +46397,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46417,6 +46411,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46498,62 +46498,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="110" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="110"/>
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="117" t="s">
+      <c r="AS1" s="111" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="118" t="s">
+      <c r="AT1" s="111"/>
+      <c r="AU1" s="111"/>
+      <c r="AV1" s="111"/>
+      <c r="AW1" s="111"/>
+      <c r="AX1" s="111"/>
+      <c r="AY1" s="111"/>
+      <c r="AZ1" s="111"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="118"/>
+      <c r="BC1" s="112"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="113" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46562,20 +46562,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="120" t="s">
+      <c r="AT2" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
+      <c r="AU2" s="114"/>
+      <c r="AV2" s="114"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="121" t="s">
+      <c r="AX2" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="121"/>
-      <c r="AZ2" s="121"/>
-      <c r="BA2" s="121"/>
+      <c r="AY2" s="115"/>
+      <c r="AZ2" s="115"/>
+      <c r="BA2" s="115"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46623,66 +46623,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113" t="s">
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113" t="s">
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113" t="s">
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113" t="s">
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="113"/>
-      <c r="W4" s="114" t="s">
+      <c r="V4" s="121"/>
+      <c r="W4" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="113" t="s">
+      <c r="X4" s="122"/>
+      <c r="Y4" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="114" t="s">
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="121"/>
+      <c r="AB4" s="121"/>
+      <c r="AC4" s="121"/>
+      <c r="AD4" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="114"/>
-      <c r="AF4" s="114"/>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="115" t="s">
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="122"/>
+      <c r="AL4" s="122"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="115"/>
+      <c r="AQ4" s="123"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46894,10 +46894,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="109" t="s">
+      <c r="BB5" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="109"/>
+      <c r="BC5" s="117"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49464,16 +49464,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="110" t="s">
+      <c r="AS19" s="118" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="110"/>
-      <c r="AU19" s="110"/>
-      <c r="AV19" s="110"/>
-      <c r="AW19" s="110"/>
-      <c r="AX19" s="110"/>
-      <c r="AY19" s="110"/>
-      <c r="AZ19" s="110"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="118"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49640,9 +49640,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="119"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49669,11 +49669,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="120" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="112"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="120"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49731,12 +49731,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49751,6 +49745,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49820,17 +49820,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -50077,6 +50066,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
   <ds:schemaRefs>
@@ -50086,23 +50086,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76AB9A25-5769-416B-8E9A-2215F01CC611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50119,4 +50102,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="264" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0CAE63F-2B83-4D82-BBB4-F0D1F7017FC0}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92C06F2F-1DEF-44E1-8CBB-CE1043074280}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2140,6 +2140,27 @@
     <xf numFmtId="10" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2161,27 +2182,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2190,6 +2190,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2205,14 +2214,23 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2236,24 +2254,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3282,43 +3282,43 @@
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>Calidad</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Jarabes</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>ETEI</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Equipos Auxiliares</c:v>
+                <c:pt idx="3">
+                  <c:v>Linea 4</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>Mantenimiento</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Centro de Distribucion</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Materias Primas</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>Centro de Distribucion</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Calidad</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Linea 2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Linea 4</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>Linea 1</c:v>
+                  <c:v>Equipos Auxiliares</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>Linea 3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Mantenimiento</c:v>
+                  <c:v>Linea 2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Jarabes</c:v>
+                  <c:v>Linea 1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Alrededores</c:v>
+                  <c:v>Linea 5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Linea 5</c:v>
+                  <c:v>Alrededores</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Almacen de Repuestos</c:v>
@@ -3699,7 +3699,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.85692000000000013</c:v>
+                  <c:v>0.93656666666666688</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -3711,13 +3711,13 @@
                   <c:v>0.96933333333333327</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.13333333333333333</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.95280000000000009</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0.57333333333333347</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4386,7 +4386,7 @@
                   <c:v>0.86230933333333326</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6546373333333334</c:v>
+                  <c:v>0.83891666666666675</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C13" s="4">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5313,62 +5313,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5377,20 +5377,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5438,66 +5438,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5709,10 +5709,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8279,16 +8279,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.8793333333333333</v>
@@ -8455,9 +8455,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8484,11 +8484,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8546,6 +8546,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8560,12 +8566,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8647,62 +8647,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8711,20 +8711,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8772,66 +8772,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -9043,10 +9043,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11613,16 +11613,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11789,9 +11789,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11818,11 +11818,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11880,6 +11880,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11894,12 +11900,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11983,62 +11983,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -12047,20 +12047,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -12108,66 +12108,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12379,10 +12379,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14949,16 +14949,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -15125,9 +15125,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -15154,11 +15154,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -15216,6 +15216,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -15230,12 +15236,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15321,62 +15321,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15385,20 +15385,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15446,66 +15446,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15717,10 +15717,10 @@
         <f>'Captura Agosto'!AQ7</f>
         <v>0.64449999999999996</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -18287,16 +18287,16 @@
         <v>0.97124999999999995</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.86230933333333326</v>
@@ -18463,9 +18463,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18492,11 +18492,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18554,6 +18554,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18568,12 +18574,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18649,7 +18649,8 @@
     <col min="4" max="44" width="9.54296875" customWidth="1"/>
     <col min="45" max="45" width="19" customWidth="1"/>
     <col min="46" max="48" width="9.54296875" customWidth="1"/>
-    <col min="49" max="50" width="11" customWidth="1"/>
+    <col min="49" max="49" width="14.1796875" customWidth="1"/>
+    <col min="50" max="50" width="11" customWidth="1"/>
     <col min="51" max="51" width="13" customWidth="1"/>
     <col min="52" max="52" width="11" customWidth="1"/>
     <col min="53" max="53" width="14" customWidth="1"/>
@@ -18658,90 +18659,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="116" t="s">
+      <c r="G2" s="123" t="s">
         <v>166</v>
       </c>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18782,73 +18783,73 @@
         <v>180</v>
       </c>
       <c r="BC3" s="69">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:55" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="107" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -18864,7 +18865,7 @@
       </c>
       <c r="AV4" s="72">
         <f>'Captura Septiembre'!V6</f>
-        <v>0</v>
+        <v>0.23474999999999999</v>
       </c>
       <c r="AW4" s="72">
         <f>'Captura Septiembre'!G6</f>
@@ -18872,11 +18873,11 @@
       </c>
       <c r="AX4" s="72">
         <f>'Captura Septiembre'!X6</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AY4" s="72">
         <f>'Captura Septiembre'!AC6</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ4" s="73">
         <f>-'Captura Septiembre'!AN6</f>
@@ -18884,13 +18885,13 @@
       </c>
       <c r="BA4" s="74">
         <f>'Captura Septiembre'!AQ6</f>
-        <v>0.67</v>
+        <v>0.89475000000000016</v>
       </c>
       <c r="BB4" s="68" t="s">
         <v>191</v>
       </c>
       <c r="BC4" s="75">
-        <v>153</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:55" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -19038,7 +19039,7 @@
       </c>
       <c r="AV5" s="80">
         <f>'Captura Septiembre'!V7</f>
-        <v>0</v>
+        <v>0.2445</v>
       </c>
       <c r="AW5" s="80">
         <f>'Captura Septiembre'!G7</f>
@@ -19046,7 +19047,7 @@
       </c>
       <c r="AX5" s="80">
         <f>'Captura Septiembre'!X7</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AY5" s="80">
         <f>'Captura Septiembre'!AC7</f>
@@ -19058,12 +19059,12 @@
       </c>
       <c r="BA5" s="82">
         <f>'Captura Septiembre'!AQ7</f>
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="BB5" s="117" t="s">
+        <v>0.55049999999999999</v>
+      </c>
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -19134,24 +19135,24 @@
         <v>0</v>
       </c>
       <c r="U6" s="85">
-        <v>0</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="V6" s="86">
         <f>U6*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23474999999999999</v>
       </c>
       <c r="W6" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W6)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Y6" s="87">
         <v>0</v>
       </c>
       <c r="Z6" s="87">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA6" s="89">
         <f>IF(Y6&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -19159,11 +19160,11 @@
       </c>
       <c r="AB6" s="89">
         <f>IF(Z6&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC6" s="89">
         <f t="shared" ref="AC6:AC20" si="1">AA6+AB6</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AD6" s="87">
         <v>0</v>
@@ -19205,11 +19206,11 @@
       </c>
       <c r="AP6" s="86">
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
-        <v>0.67</v>
+        <v>0.85475000000000012</v>
       </c>
       <c r="AQ6" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6-AN6-IF(AO6="SI",Parametros!$E$33,0)))</f>
-        <v>0.67</v>
+        <v>0.89475000000000016</v>
       </c>
       <c r="AR6" s="58"/>
       <c r="AS6" s="71" t="str">
@@ -19226,7 +19227,7 @@
       </c>
       <c r="AV6" s="72">
         <f>'Captura Septiembre'!V8</f>
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="AW6" s="72">
         <f>'Captura Septiembre'!G8</f>
@@ -19238,7 +19239,7 @@
       </c>
       <c r="AY6" s="72">
         <f>'Captura Septiembre'!AC8</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AZ6" s="73">
         <f>-'Captura Septiembre'!AN8</f>
@@ -19246,7 +19247,7 @@
       </c>
       <c r="BA6" s="74">
         <f>'Captura Septiembre'!AQ8</f>
-        <v>0.68375000000000008</v>
+        <v>1</v>
       </c>
       <c r="BB6" s="58"/>
       <c r="BC6" s="58"/>
@@ -19320,18 +19321,18 @@
         <v>0</v>
       </c>
       <c r="U7" s="85">
-        <v>0</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="V7" s="86">
         <f>U7*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.2445</v>
       </c>
       <c r="W7" s="87">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X7" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W7)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="87">
         <v>0</v>
@@ -19391,11 +19392,11 @@
       </c>
       <c r="AP7" s="86">
         <f t="shared" si="3"/>
-        <v>0.55600000000000005</v>
+        <v>0.55049999999999999</v>
       </c>
       <c r="AQ7" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7-AN7-IF(AO7="SI",Parametros!$E$33,0)))</f>
-        <v>0.55600000000000005</v>
+        <v>0.55049999999999999</v>
       </c>
       <c r="AR7" s="58"/>
       <c r="AS7" s="108" t="str">
@@ -19412,19 +19413,19 @@
       </c>
       <c r="AV7" s="80">
         <f>'Captura Septiembre'!V9</f>
-        <v>0</v>
+        <v>0.23674999999999999</v>
       </c>
       <c r="AW7" s="80">
         <f>'Captura Septiembre'!G9</f>
-        <v>0.19737000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="AX7" s="80">
         <f>'Captura Septiembre'!X9</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AY7" s="80">
         <f>'Captura Septiembre'!AC9</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ7" s="81">
         <f>-'Captura Septiembre'!AN9</f>
@@ -19432,7 +19433,7 @@
       </c>
       <c r="BA7" s="82">
         <f>'Captura Septiembre'!AQ9</f>
-        <v>0.68737000000000004</v>
+        <v>0.86675000000000013</v>
       </c>
       <c r="BB7" s="58"/>
       <c r="BC7" s="58"/>
@@ -19506,11 +19507,11 @@
         <v>0</v>
       </c>
       <c r="U8" s="85">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="V8" s="86">
         <f>U8*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="W8" s="87">
         <v>0</v>
@@ -19520,22 +19521,22 @@
         <v>0.25</v>
       </c>
       <c r="Y8" s="87">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z8" s="87">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA8" s="89">
         <f>IF(Y8&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AB8" s="89">
         <f>IF(Z8&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC8" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AD8" s="87">
         <v>0</v>
@@ -19577,11 +19578,11 @@
       </c>
       <c r="AP8" s="86">
         <f t="shared" si="3"/>
-        <v>0.68375000000000008</v>
+        <v>0.92874999999999996</v>
       </c>
       <c r="AQ8" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8-AN8-IF(AO8="SI",Parametros!$E$33,0)))</f>
-        <v>0.68375000000000008</v>
+        <v>1</v>
       </c>
       <c r="AR8" s="58"/>
       <c r="AS8" s="71" t="str">
@@ -19598,7 +19599,7 @@
       </c>
       <c r="AV8" s="72">
         <f>'Captura Septiembre'!V10</f>
-        <v>0</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="AW8" s="72">
         <f>'Captura Septiembre'!G10</f>
@@ -19606,11 +19607,11 @@
       </c>
       <c r="AX8" s="72">
         <f>'Captura Septiembre'!X10</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AY8" s="72">
         <f>'Captura Septiembre'!AC10</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ8" s="73">
         <f>-'Captura Septiembre'!AN10</f>
@@ -19618,7 +19619,7 @@
       </c>
       <c r="BA8" s="74">
         <f>'Captura Septiembre'!AQ10</f>
-        <v>0.75</v>
+        <v>0.97300000000000009</v>
       </c>
       <c r="BB8" s="58"/>
       <c r="BC8" s="58"/>
@@ -19638,15 +19639,15 @@
         <v>1</v>
       </c>
       <c r="E9" s="85">
-        <v>0.97370000000000001</v>
+        <v>1</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="0"/>
-        <v>0.98685</v>
+        <v>1</v>
       </c>
       <c r="G9" s="86">
         <f>F9*Parametros!$E$6</f>
-        <v>0.19737000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="87">
         <v>38</v>
@@ -19692,24 +19693,24 @@
         <v>0</v>
       </c>
       <c r="U9" s="85">
-        <v>0</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="V9" s="86">
         <f>U9*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23674999999999999</v>
       </c>
       <c r="W9" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W9)</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="Y9" s="87">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z9" s="87">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA9" s="89">
         <f>IF(Y9&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -19717,11 +19718,11 @@
       </c>
       <c r="AB9" s="89">
         <f>IF(Z9&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC9" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AD9" s="87">
         <v>0</v>
@@ -19763,11 +19764,11 @@
       </c>
       <c r="AP9" s="86">
         <f t="shared" si="3"/>
-        <v>0.68737000000000004</v>
+        <v>0.8267500000000001</v>
       </c>
       <c r="AQ9" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9-AN9-IF(AO9="SI",Parametros!$E$33,0)))</f>
-        <v>0.68737000000000004</v>
+        <v>0.86675000000000013</v>
       </c>
       <c r="AR9" s="58"/>
       <c r="AS9" s="79" t="str">
@@ -19784,7 +19785,7 @@
       </c>
       <c r="AV9" s="80">
         <f>'Captura Septiembre'!V11</f>
-        <v>0</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="AW9" s="80">
         <f>'Captura Septiembre'!G11</f>
@@ -19792,19 +19793,19 @@
       </c>
       <c r="AX9" s="80">
         <f>'Captura Septiembre'!X11</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AY9" s="80">
         <f>'Captura Septiembre'!AC11</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ9" s="81">
         <f>-'Captura Septiembre'!AN11</f>
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="BA9" s="82">
         <f>'Captura Septiembre'!AQ11</f>
-        <v>0.74520000000000008</v>
+        <v>0.81770000000000009</v>
       </c>
       <c r="BB9" s="58"/>
       <c r="BC9" s="58"/>
@@ -19878,24 +19879,24 @@
         <v>0.06</v>
       </c>
       <c r="U10" s="85">
-        <v>0</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="V10" s="86">
         <f>U10*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="W10" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W10)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Y10" s="87">
         <v>0</v>
       </c>
       <c r="Z10" s="87">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA10" s="89">
         <f>IF(Y10&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -19903,11 +19904,11 @@
       </c>
       <c r="AB10" s="89">
         <f>IF(Z10&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC10" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AD10" s="87">
         <v>0</v>
@@ -19949,11 +19950,11 @@
       </c>
       <c r="AP10" s="86">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="AQ10" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10-AN10-IF(AO10="SI",Parametros!$E$33,0)))</f>
-        <v>0.75</v>
+        <v>0.97300000000000009</v>
       </c>
       <c r="AR10" s="58"/>
       <c r="AS10" s="71" t="str">
@@ -19966,15 +19967,15 @@
       </c>
       <c r="AU10" s="72">
         <f>'Captura Septiembre'!T12</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AV10" s="72">
         <f>'Captura Septiembre'!V12</f>
-        <v>0</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="AW10" s="72">
         <f>'Captura Septiembre'!G12</f>
-        <v>0.11364000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" s="72">
         <f>'Captura Septiembre'!X12</f>
@@ -19982,7 +19983,7 @@
       </c>
       <c r="AY10" s="72">
         <f>'Captura Septiembre'!AC12</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AZ10" s="73">
         <f>-'Captura Septiembre'!AN12</f>
@@ -19990,7 +19991,7 @@
       </c>
       <c r="BA10" s="74">
         <f>'Captura Septiembre'!AQ12</f>
-        <v>0.59564000000000006</v>
+        <v>1</v>
       </c>
       <c r="BB10" s="58"/>
       <c r="BC10" s="58"/>
@@ -20064,24 +20065,24 @@
         <v>0.06</v>
       </c>
       <c r="U11" s="85">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="V11" s="86">
         <f>U11*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="W11" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X11" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W11)</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="Y11" s="87">
         <v>0</v>
       </c>
       <c r="Z11" s="87">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA11" s="89">
         <f>IF(Y11&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -20089,11 +20090,11 @@
       </c>
       <c r="AB11" s="89">
         <f>IF(Z11&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC11" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AD11" s="87">
         <v>0</v>
@@ -20102,7 +20103,7 @@
         <v>222</v>
       </c>
       <c r="AF11" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" s="88" t="s">
         <v>222</v>
@@ -20127,7 +20128,7 @@
       </c>
       <c r="AN11" s="89">
         <f>AD11*Parametros!$E$28+AF11*Parametros!$E$29+AH11*Parametros!$E$30+AJ11*Parametros!$E$31+AL11*Parametros!$E$32</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AO11" s="12" t="str">
         <f t="shared" si="2"/>
@@ -20135,11 +20136,11 @@
       </c>
       <c r="AP11" s="86">
         <f t="shared" si="3"/>
-        <v>0.74520000000000008</v>
+        <v>0.87770000000000004</v>
       </c>
       <c r="AQ11" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11-AN11-IF(AO11="SI",Parametros!$E$33,0)))</f>
-        <v>0.74520000000000008</v>
+        <v>0.81770000000000009</v>
       </c>
       <c r="AR11" s="58"/>
       <c r="AS11" s="79" t="str">
@@ -20156,19 +20157,19 @@
       </c>
       <c r="AV11" s="80">
         <f>'Captura Septiembre'!V13</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="AW11" s="80">
         <f>'Captura Septiembre'!G13</f>
-        <v>0.184</v>
+        <v>0.18409</v>
       </c>
       <c r="AX11" s="80">
         <f>'Captura Septiembre'!X13</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AY11" s="80">
         <f>'Captura Septiembre'!AC13</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ11" s="81">
         <f>-'Captura Septiembre'!AN13</f>
@@ -20176,7 +20177,7 @@
       </c>
       <c r="BA11" s="82">
         <f>'Captura Septiembre'!AQ13</f>
-        <v>0.66439999999999999</v>
+        <v>0.69623999999999997</v>
       </c>
       <c r="BB11" s="58"/>
       <c r="BC11" s="58"/>
@@ -20196,15 +20197,15 @@
         <v>1</v>
       </c>
       <c r="E12" s="85">
-        <v>0.13639999999999999</v>
+        <v>1</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="0"/>
-        <v>0.56820000000000004</v>
+        <v>1</v>
       </c>
       <c r="G12" s="86">
         <f>F12*Parametros!$E$6</f>
-        <v>0.11364000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="87">
         <v>38</v>
@@ -20240,21 +20241,21 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="R12" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T12" s="86">
         <f>IF(S12="NO",0,R12*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U12" s="85">
-        <v>0</v>
+        <v>0.94799999999999995</v>
       </c>
       <c r="V12" s="86">
         <f>U12*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="W12" s="87">
         <v>0</v>
@@ -20264,22 +20265,22 @@
         <v>0.25</v>
       </c>
       <c r="Y12" s="87">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z12" s="87">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA12" s="89">
         <f>IF(Y12&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AB12" s="89">
         <f>IF(Z12&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC12" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AD12" s="87">
         <v>0</v>
@@ -20321,11 +20322,11 @@
       </c>
       <c r="AP12" s="86">
         <f t="shared" si="3"/>
-        <v>0.59564000000000006</v>
+        <v>0.97900000000000009</v>
       </c>
       <c r="AQ12" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12-AN12-IF(AO12="SI",Parametros!$E$33,0)))</f>
-        <v>0.59564000000000006</v>
+        <v>1</v>
       </c>
       <c r="AR12" s="58"/>
       <c r="AS12" s="71" t="str">
@@ -20342,15 +20343,15 @@
       </c>
       <c r="AV12" s="72">
         <f>'Captura Septiembre'!V14</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="AW12" s="72">
         <f>'Captura Septiembre'!G14</f>
-        <v>0.192</v>
+        <v>0.19286</v>
       </c>
       <c r="AX12" s="72">
         <f>'Captura Septiembre'!X14</f>
-        <v>0.25</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="AY12" s="72">
         <f>'Captura Septiembre'!AC14</f>
@@ -20362,7 +20363,7 @@
       </c>
       <c r="BA12" s="74">
         <f>'Captura Septiembre'!AQ14</f>
-        <v>0.6724</v>
+        <v>0.76500999999999997</v>
       </c>
       <c r="BB12" s="58"/>
       <c r="BC12" s="58"/>
@@ -20382,15 +20383,15 @@
         <v>1</v>
       </c>
       <c r="E13" s="85">
-        <v>0.84</v>
+        <v>0.84089999999999998</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="0"/>
-        <v>0.91999999999999993</v>
+        <v>0.92044999999999999</v>
       </c>
       <c r="G13" s="86">
         <f>F13*Parametros!$E$6</f>
-        <v>0.184</v>
+        <v>0.18409</v>
       </c>
       <c r="H13" s="87">
         <v>38</v>
@@ -20436,24 +20437,24 @@
         <v>0</v>
       </c>
       <c r="U13" s="85">
-        <v>0</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="V13" s="86">
         <f>U13*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="W13" s="87">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X13" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W13)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z13" s="87">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA13" s="89">
         <f>IF(Y13&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -20461,11 +20462,11 @@
       </c>
       <c r="AB13" s="89">
         <f>IF(Z13&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC13" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AD13" s="87">
         <v>0</v>
@@ -20507,11 +20508,11 @@
       </c>
       <c r="AP13" s="86">
         <f t="shared" si="3"/>
-        <v>0.66439999999999999</v>
+        <v>0.65623999999999993</v>
       </c>
       <c r="AQ13" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13-AN13-IF(AO13="SI",Parametros!$E$33,0)))</f>
-        <v>0.66439999999999999</v>
+        <v>0.69623999999999997</v>
       </c>
       <c r="AR13" s="58"/>
       <c r="AS13" s="79" t="str">
@@ -20524,23 +20525,23 @@
       </c>
       <c r="AU13" s="80">
         <f>'Captura Septiembre'!T15</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AV13" s="80">
         <f>'Captura Septiembre'!V15</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="AW13" s="80">
         <f>'Captura Septiembre'!G15</f>
-        <v>0.17700000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="AX13" s="80">
         <f>'Captura Septiembre'!X15</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AY13" s="80">
         <f>'Captura Septiembre'!AC15</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ13" s="81">
         <f>-'Captura Septiembre'!AN15</f>
@@ -20548,7 +20549,7 @@
       </c>
       <c r="BA13" s="82">
         <f>'Captura Septiembre'!AQ15</f>
-        <v>0.66379999999999995</v>
+        <v>0.77855000000000008</v>
       </c>
       <c r="BB13" s="58"/>
       <c r="BC13" s="58"/>
@@ -20568,15 +20569,15 @@
         <v>1</v>
       </c>
       <c r="E14" s="85">
-        <v>0.92</v>
+        <v>0.92859999999999998</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" si="0"/>
-        <v>0.96</v>
+        <v>0.96429999999999993</v>
       </c>
       <c r="G14" s="86">
         <f>F14*Parametros!$E$6</f>
-        <v>0.192</v>
+        <v>0.19286</v>
       </c>
       <c r="H14" s="87">
         <v>38</v>
@@ -20622,24 +20623,24 @@
         <v>0</v>
       </c>
       <c r="U14" s="85">
-        <v>0</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="V14" s="86">
         <f>U14*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="W14" s="87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W14)</f>
-        <v>0.25</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="Y14" s="87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z14" s="87">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA14" s="89">
         <f>IF(Y14&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -20693,11 +20694,11 @@
       </c>
       <c r="AP14" s="86">
         <f t="shared" si="3"/>
-        <v>0.6724</v>
+        <v>0.76500999999999997</v>
       </c>
       <c r="AQ14" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14-AN14-IF(AO14="SI",Parametros!$E$33,0)))</f>
-        <v>0.6724</v>
+        <v>0.76500999999999997</v>
       </c>
       <c r="AR14" s="58"/>
       <c r="AS14" s="71" t="str">
@@ -20710,23 +20711,23 @@
       </c>
       <c r="AU14" s="72">
         <f>'Captura Septiembre'!T16</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AV14" s="72">
         <f>'Captura Septiembre'!V16</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="AW14" s="72">
         <f>'Captura Septiembre'!G16</f>
-        <v>0.18600000000000003</v>
+        <v>0.19300000000000003</v>
       </c>
       <c r="AX14" s="72">
         <f>'Captura Septiembre'!X16</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AY14" s="72">
         <f>'Captura Septiembre'!AC16</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ14" s="73">
         <f>-'Captura Septiembre'!AN16</f>
@@ -20734,7 +20735,7 @@
       </c>
       <c r="BA14" s="74">
         <f>'Captura Septiembre'!AQ16</f>
-        <v>0.66959999999999997</v>
+        <v>0.91835</v>
       </c>
       <c r="BB14" s="58"/>
       <c r="BC14" s="58"/>
@@ -20754,15 +20755,15 @@
         <v>1</v>
       </c>
       <c r="E15" s="85">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
-        <v>0.88500000000000001</v>
+        <v>1</v>
       </c>
       <c r="G15" s="86">
         <f>F15*Parametros!$E$6</f>
-        <v>0.17700000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="H15" s="87">
         <v>38</v>
@@ -20798,34 +20799,34 @@
         <v>7.6799999999999993E-2</v>
       </c>
       <c r="R15" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T15" s="86">
         <f>IF(S15="NO",0,R15*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U15" s="85">
-        <v>0</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="V15" s="86">
         <f>U15*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="W15" s="87">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X15" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W15)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="87">
         <v>0</v>
       </c>
       <c r="Z15" s="87">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA15" s="89">
         <f>IF(Y15&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -20833,11 +20834,11 @@
       </c>
       <c r="AB15" s="89">
         <f>IF(Z15&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC15" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AD15" s="87">
         <v>0</v>
@@ -20879,11 +20880,11 @@
       </c>
       <c r="AP15" s="86">
         <f t="shared" si="3"/>
-        <v>0.66379999999999995</v>
+        <v>0.73855000000000004</v>
       </c>
       <c r="AQ15" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15-AN15-IF(AO15="SI",Parametros!$E$33,0)))</f>
-        <v>0.66379999999999995</v>
+        <v>0.77855000000000008</v>
       </c>
       <c r="AR15" s="58"/>
       <c r="AS15" s="79" t="str">
@@ -20900,7 +20901,7 @@
       </c>
       <c r="AV15" s="80">
         <f>'Captura Septiembre'!V17</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="AW15" s="80">
         <f>'Captura Septiembre'!G17</f>
@@ -20908,7 +20909,7 @@
       </c>
       <c r="AX15" s="80">
         <f>'Captura Septiembre'!X17</f>
-        <v>0.25</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="AY15" s="80">
         <f>'Captura Septiembre'!AC17</f>
@@ -20920,7 +20921,7 @@
       </c>
       <c r="BA15" s="82">
         <f>'Captura Septiembre'!AQ17</f>
-        <v>0.52639999999999998</v>
+        <v>0.61814999999999998</v>
       </c>
       <c r="BB15" s="58"/>
       <c r="BC15" s="58"/>
@@ -20940,15 +20941,15 @@
         <v>0.93</v>
       </c>
       <c r="E16" s="85">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
-        <v>0.93</v>
+        <v>0.96500000000000008</v>
       </c>
       <c r="G16" s="86">
         <f>F16*Parametros!$E$6</f>
-        <v>0.18600000000000003</v>
+        <v>0.19300000000000003</v>
       </c>
       <c r="H16" s="87">
         <v>38</v>
@@ -20984,34 +20985,34 @@
         <v>7.6799999999999993E-2</v>
       </c>
       <c r="R16" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T16" s="86">
         <f>IF(S16="NO",0,R16*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U16" s="85">
-        <v>0</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="V16" s="86">
         <f>U16*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="W16" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X16" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W16)</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="Y16" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z16" s="87">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA16" s="89">
         <f>IF(Y16&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -21019,11 +21020,11 @@
       </c>
       <c r="AB16" s="89">
         <f>IF(Z16&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC16" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AD16" s="87">
         <v>0</v>
@@ -21065,11 +21066,11 @@
       </c>
       <c r="AP16" s="86">
         <f t="shared" si="3"/>
-        <v>0.66959999999999997</v>
+        <v>0.87834999999999996</v>
       </c>
       <c r="AQ16" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16-AN16-IF(AO16="SI",Parametros!$E$33,0)))</f>
-        <v>0.66959999999999997</v>
+        <v>0.91835</v>
       </c>
       <c r="AR16" s="58"/>
       <c r="AS16" s="71" t="str">
@@ -21086,11 +21087,11 @@
       </c>
       <c r="AV16" s="72">
         <f>'Captura Septiembre'!V18</f>
-        <v>0</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="AW16" s="72">
         <f>'Captura Septiembre'!G18</f>
-        <v>0.18100000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="AX16" s="72">
         <f>'Captura Septiembre'!X18</f>
@@ -21106,7 +21107,7 @@
       </c>
       <c r="BA16" s="74">
         <f>'Captura Septiembre'!AQ18</f>
-        <v>0.66139999999999999</v>
+        <v>0.91290000000000004</v>
       </c>
       <c r="BB16" s="58"/>
       <c r="BC16" s="58"/>
@@ -21180,24 +21181,24 @@
         <v>0</v>
       </c>
       <c r="U17" s="85">
-        <v>0</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="V17" s="86">
         <f>U17*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.24174999999999999</v>
       </c>
       <c r="W17" s="87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X17" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W17)</f>
-        <v>0.25</v>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="Y17" s="87">
         <v>0</v>
       </c>
       <c r="Z17" s="87">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA17" s="89">
         <f>IF(Y17&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -21251,11 +21252,11 @@
       </c>
       <c r="AP17" s="86">
         <f t="shared" si="3"/>
-        <v>0.6764</v>
+        <v>0.76815</v>
       </c>
       <c r="AQ17" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17-AN17-IF(AO17="SI",Parametros!$E$33,0)))</f>
-        <v>0.52639999999999998</v>
+        <v>0.61814999999999998</v>
       </c>
       <c r="AR17" s="58"/>
       <c r="AS17" s="79" t="str">
@@ -21272,7 +21273,7 @@
       </c>
       <c r="AV17" s="80">
         <f>'Captura Septiembre'!V19</f>
-        <v>0</v>
+        <v>0.23125000000000001</v>
       </c>
       <c r="AW17" s="80">
         <f>'Captura Septiembre'!G19</f>
@@ -21280,11 +21281,11 @@
       </c>
       <c r="AX17" s="80">
         <f>'Captura Septiembre'!X19</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AY17" s="80">
         <f>'Captura Septiembre'!AC19</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ17" s="81">
         <f>-'Captura Septiembre'!AN19</f>
@@ -21292,7 +21293,7 @@
       </c>
       <c r="BA17" s="82">
         <f>'Captura Septiembre'!AQ19</f>
-        <v>0.69000000000000006</v>
+        <v>0.86125000000000018</v>
       </c>
       <c r="BB17" s="58"/>
       <c r="BC17" s="58"/>
@@ -21312,15 +21313,15 @@
         <v>1</v>
       </c>
       <c r="E18" s="85">
-        <v>0.81</v>
+        <v>1</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="0"/>
-        <v>0.90500000000000003</v>
+        <v>1</v>
       </c>
       <c r="G18" s="86">
         <f>F18*Parametros!$E$6</f>
-        <v>0.18100000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="H18" s="87">
         <v>38</v>
@@ -21366,11 +21367,11 @@
         <v>0</v>
       </c>
       <c r="U18" s="85">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="V18" s="86">
         <f>U18*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="W18" s="87">
         <v>0</v>
@@ -21380,10 +21381,10 @@
         <v>0.25</v>
       </c>
       <c r="Y18" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z18" s="87">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" s="89">
         <f>IF(Y18&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -21437,11 +21438,11 @@
       </c>
       <c r="AP18" s="86">
         <f t="shared" si="3"/>
-        <v>0.66139999999999999</v>
+        <v>0.91290000000000004</v>
       </c>
       <c r="AQ18" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18-AN18-IF(AO18="SI",Parametros!$E$33,0)))</f>
-        <v>0.66139999999999999</v>
+        <v>0.91290000000000004</v>
       </c>
       <c r="AR18" s="58"/>
       <c r="AS18" s="71" t="str">
@@ -21454,19 +21455,19 @@
       </c>
       <c r="AU18" s="72">
         <f>'Captura Septiembre'!T20</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AV18" s="72">
         <f>'Captura Septiembre'!V20</f>
-        <v>0</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="AW18" s="72">
         <f>'Captura Septiembre'!G20</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AX18" s="72">
         <f>'Captura Septiembre'!X20</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AY18" s="72">
         <f>'Captura Septiembre'!AC20</f>
@@ -21478,7 +21479,7 @@
       </c>
       <c r="BA18" s="74">
         <f>'Captura Septiembre'!AQ20</f>
-        <v>0.5835999999999999</v>
+        <v>0.93059999999999987</v>
       </c>
       <c r="BB18" s="58"/>
       <c r="BC18" s="58"/>
@@ -21552,24 +21553,24 @@
         <v>0</v>
       </c>
       <c r="U19" s="85">
-        <v>0</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="V19" s="86">
         <f>U19*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23125000000000001</v>
       </c>
       <c r="W19" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W19)</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="Y19" s="87">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z19" s="87">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA19" s="89">
         <f>IF(Y19&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -21577,11 +21578,11 @@
       </c>
       <c r="AB19" s="89">
         <f>IF(Z19&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC19" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AD19" s="87">
         <v>0</v>
@@ -21623,26 +21624,26 @@
       </c>
       <c r="AP19" s="86">
         <f t="shared" si="3"/>
-        <v>0.69000000000000006</v>
+        <v>0.82125000000000015</v>
       </c>
       <c r="AQ19" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19-AN19-IF(AO19="SI",Parametros!$E$33,0)))</f>
-        <v>0.69000000000000006</v>
+        <v>0.86125000000000018</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.6546373333333334</v>
+        <v>0.83891666666666675</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -21662,15 +21663,15 @@
         <v>1</v>
       </c>
       <c r="E20" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G20" s="86">
         <f>F20*Parametros!$E$6</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H20" s="87">
         <v>38</v>
@@ -21706,34 +21707,34 @@
         <v>7.6799999999999993E-2</v>
       </c>
       <c r="R20" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T20" s="86">
         <f>IF(S20="NO",0,R20*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U20" s="85">
-        <v>0</v>
+        <v>0.94799999999999995</v>
       </c>
       <c r="V20" s="86">
         <f>U20*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="W20" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W20)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Y20" s="87">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z20" s="87">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" s="89">
         <f>IF(Y20&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -21787,11 +21788,11 @@
       </c>
       <c r="AP20" s="86">
         <f t="shared" si="3"/>
-        <v>0.5835999999999999</v>
+        <v>0.93059999999999987</v>
       </c>
       <c r="AQ20" s="109">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20-AN20-IF(AO20="SI",Parametros!$E$33,0)))</f>
-        <v>0.5835999999999999</v>
+        <v>0.93059999999999987</v>
       </c>
       <c r="AR20" s="58"/>
       <c r="AS20" s="58"/>
@@ -21806,9 +21807,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21835,11 +21836,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21881,7 +21882,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="94">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.6546373333333334</v>
+        <v>0.83891666666666675</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -21897,6 +21898,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
+    <mergeCell ref="G2:M2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21911,13 +21919,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
-    <mergeCell ref="G2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21959,7 +21960,7 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="decimal" showErrorMessage="1" errorTitle="Valor invalido" error="Ingrese un porcentaje entre 0% y 100%" sqref="U6:U20 L6:L20 O6:O20 R6:R20 D6:E20" xr:uid="{00000000-0002-0000-0D00-000001000000}">
+    <dataValidation type="decimal" showErrorMessage="1" errorTitle="Valor invalido" error="Ingrese un porcentaje entre 0% y 100%" sqref="D6:E20 L6:L20 O6:O20 R6:R20 U6:U20" xr:uid="{00000000-0002-0000-0D00-000001000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -21999,62 +22000,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -22063,20 +22064,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -22124,66 +22125,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22395,10 +22396,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24965,16 +24966,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -25141,9 +25142,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -25170,11 +25171,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -25232,6 +25233,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -25246,12 +25253,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25333,62 +25334,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25397,20 +25398,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25458,66 +25459,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25729,10 +25730,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28299,16 +28300,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28475,9 +28476,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28504,11 +28505,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28566,6 +28567,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28580,12 +28587,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28667,62 +28668,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28731,20 +28732,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28792,66 +28793,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -29063,10 +29064,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31633,16 +31634,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31809,9 +31810,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31838,11 +31839,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31900,6 +31901,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31914,12 +31921,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31993,11 +31994,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="150" t="s">
@@ -32130,11 +32131,11 @@
       </c>
       <c r="B14" s="97">
         <f>IF(AVERAGE('Captura Septiembre'!D6:D20)=0,"",'Captura Septiembre'!AQ23)</f>
-        <v>0.6546373333333334</v>
+        <v>0.83891666666666675</v>
       </c>
       <c r="C14" s="12" t="str">
         <f>IF(B14="","",IF(B14&gt;=Parametros!$C$37,"Verde",IF(B14&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
-        <v>Rojo</v>
+        <v>Amarillo</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32314,7 +32315,7 @@
       </c>
       <c r="J4" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
-        <v>0.68375000000000008</v>
+        <v>1</v>
       </c>
       <c r="K4" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
@@ -32330,7 +32331,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.96211111111111114</v>
+        <v>0.99724999999999986</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32371,7 +32372,7 @@
       </c>
       <c r="J5" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
-        <v>0.67</v>
+        <v>0.89475000000000016</v>
       </c>
       <c r="K5" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
@@ -32387,7 +32388,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.92888333333333328</v>
+        <v>0.95385555555555557</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32428,7 +32429,7 @@
       </c>
       <c r="J6" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
-        <v>0.66959999999999997</v>
+        <v>0.91835</v>
       </c>
       <c r="K6" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
@@ -32444,7 +32445,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.93820952380952372</v>
+        <v>0.96584841269841271</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32485,7 +32486,7 @@
       </c>
       <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v>0.52639999999999998</v>
+        <v>0.61814999999999998</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -32501,7 +32502,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.81234536019536019</v>
+        <v>0.82253980463980469</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32542,7 +32543,7 @@
       </c>
       <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
-        <v>0.6724</v>
+        <v>0.76500999999999997</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
@@ -32558,7 +32559,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.87562888888888901</v>
+        <v>0.88591888888888903</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32599,7 +32600,7 @@
       </c>
       <c r="J9" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
-        <v>0.74520000000000008</v>
+        <v>0.81770000000000009</v>
       </c>
       <c r="K9" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
@@ -32615,7 +32616,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.90446666666666664</v>
+        <v>0.91252222222222223</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32656,7 +32657,7 @@
       </c>
       <c r="J10" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
-        <v>0.66439999999999999</v>
+        <v>0.69623999999999997</v>
       </c>
       <c r="K10" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D13=0,"",'Captura Octubre'!AQ13),"")</f>
@@ -32672,7 +32673,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.80467555555555537</v>
+        <v>0.80821333333333323</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32713,7 +32714,7 @@
       </c>
       <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v>0.75</v>
+        <v>0.97300000000000009</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -32729,7 +32730,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.93388888888888899</v>
+        <v>0.95866666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32770,7 +32771,7 @@
       </c>
       <c r="J12" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v>0.68737000000000004</v>
+        <v>0.86675000000000013</v>
       </c>
       <c r="K12" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
@@ -32786,7 +32787,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.95297999999999994</v>
+        <v>0.97291111111111106</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32827,7 +32828,7 @@
       </c>
       <c r="J13" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
-        <v>0.59564000000000006</v>
+        <v>1</v>
       </c>
       <c r="K13" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
@@ -32843,7 +32844,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.82932714975845423</v>
+        <v>0.87425603864734314</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32884,7 +32885,7 @@
       </c>
       <c r="J14" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
-        <v>0.66379999999999995</v>
+        <v>0.77855000000000008</v>
       </c>
       <c r="K14" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
@@ -32900,7 +32901,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.81519236517218985</v>
+        <v>0.82794236517218989</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32941,7 +32942,7 @@
       </c>
       <c r="J15" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
-        <v>0.55600000000000005</v>
+        <v>0.55049999999999999</v>
       </c>
       <c r="K15" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D7=0,"",'Captura Octubre'!AQ7),"")</f>
@@ -32957,7 +32958,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.75783333333333336</v>
+        <v>0.75722222222222213</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32998,7 +32999,7 @@
       </c>
       <c r="J16" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
-        <v>0.5835999999999999</v>
+        <v>0.93059999999999987</v>
       </c>
       <c r="K16" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
@@ -33014,7 +33015,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.90340000000000009</v>
+        <v>0.94195555555555566</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33055,7 +33056,7 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
-        <v>0.66139999999999999</v>
+        <v>0.91290000000000004</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
@@ -33071,7 +33072,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.91041721132897591</v>
+        <v>0.93836165577342046</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33112,7 +33113,7 @@
       </c>
       <c r="J18" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
-        <v>0.69000000000000006</v>
+        <v>0.86125000000000018</v>
       </c>
       <c r="K18" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
@@ -33128,7 +33129,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.88375000000000004</v>
+        <v>0.90277777777777779</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -33169,7 +33170,7 @@
       </c>
       <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v>0.6546373333333334</v>
+        <v>0.83891666666666675</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -33228,16 +33229,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -33279,11 +33280,11 @@
       </c>
       <c r="C5" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G20"))</f>
-        <v>0.17138400000000004</v>
+        <v>0.18731333333333339</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" ref="D5:D11" ca="1" si="0">IFERROR(C5/B5,0)</f>
-        <v>0.85692000000000013</v>
+        <v>0.93656666666666688</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33347,11 +33348,11 @@
       </c>
       <c r="C9" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T20"))</f>
-        <v>8.0000000000000002E-3</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.13333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33364,11 +33365,11 @@
       </c>
       <c r="C10" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"V6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"V20"))</f>
-        <v>0</v>
+        <v>0.23820000000000002</v>
       </c>
       <c r="D10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>0.95280000000000009</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33381,11 +33382,11 @@
       </c>
       <c r="C11" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"))</f>
-        <v>0.25</v>
+        <v>0.14333333333333337</v>
       </c>
       <c r="D11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0.57333333333333347</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33400,7 +33401,7 @@
       </c>
       <c r="B14" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"))</f>
-        <v>0.25</v>
+        <v>0.14333333333333337</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33409,7 +33410,7 @@
       </c>
       <c r="B15" s="12">
         <f ca="1">COUNTIF(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"),"&gt;=0.04")</f>
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33418,7 +33419,7 @@
       </c>
       <c r="B16" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AN6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AN20"))</f>
-        <v>0.01</v>
+        <v>1.6666666666666666E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33479,7 +33480,7 @@
       </c>
       <c r="B23" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,1),$E$23:$E$37,0))</f>
-        <v>ETEI</v>
+        <v>Calidad</v>
       </c>
       <c r="C23" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),1)</f>
@@ -33500,7 +33501,7 @@
       </c>
       <c r="B24" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,2),$E$23:$E$37,0))</f>
-        <v>Equipos Auxiliares</v>
+        <v>Jarabes</v>
       </c>
       <c r="C24" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),2)</f>
@@ -33512,7 +33513,7 @@
       </c>
       <c r="E24" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ7")*100000-7</f>
-        <v>55593.000000000007</v>
+        <v>55043</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33521,7 +33522,7 @@
       </c>
       <c r="B25" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,3),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>ETEI</v>
       </c>
       <c r="C25" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),3)</f>
@@ -33533,7 +33534,7 @@
       </c>
       <c r="E25" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ8")*100000-8</f>
-        <v>68367.000000000015</v>
+        <v>99992</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33542,7 +33543,7 @@
       </c>
       <c r="B26" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,4),$E$23:$E$37,0))</f>
-        <v>Centro de Distribucion</v>
+        <v>Linea 4</v>
       </c>
       <c r="C26" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),4)</f>
@@ -33554,7 +33555,7 @@
       </c>
       <c r="E26" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ9")*100000-9</f>
-        <v>68728</v>
+        <v>86666.000000000015</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33563,7 +33564,7 @@
       </c>
       <c r="B27" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,5),$E$23:$E$37,0))</f>
-        <v>Calidad</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C27" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),5)</f>
@@ -33575,7 +33576,7 @@
       </c>
       <c r="E27" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ10")*100000-10</f>
-        <v>74990</v>
+        <v>97290.000000000015</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33584,7 +33585,7 @@
       </c>
       <c r="B28" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,6),$E$23:$E$37,0))</f>
-        <v>Linea 2</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C28" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),6)</f>
@@ -33596,7 +33597,7 @@
       </c>
       <c r="E28" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ11")*100000-11</f>
-        <v>74509.000000000015</v>
+        <v>81759.000000000015</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33605,7 +33606,7 @@
       </c>
       <c r="B29" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,7),$E$23:$E$37,0))</f>
-        <v>Linea 4</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C29" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),7)</f>
@@ -33617,7 +33618,7 @@
       </c>
       <c r="E29" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ12")*100000-12</f>
-        <v>59552.000000000007</v>
+        <v>99988</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33626,7 +33627,7 @@
       </c>
       <c r="B30" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,8),$E$23:$E$37,0))</f>
-        <v>Linea 1</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C30" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),8)</f>
@@ -33638,7 +33639,7 @@
       </c>
       <c r="E30" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ13")*100000-13</f>
-        <v>66427</v>
+        <v>69611</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33659,7 +33660,7 @@
       </c>
       <c r="E31" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ14")*100000-14</f>
-        <v>67226</v>
+        <v>76487</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33668,7 +33669,7 @@
       </c>
       <c r="B32" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,10),$E$23:$E$37,0))</f>
-        <v>Mantenimiento</v>
+        <v>Linea 2</v>
       </c>
       <c r="C32" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),10)</f>
@@ -33680,7 +33681,7 @@
       </c>
       <c r="E32" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ15")*100000-15</f>
-        <v>66365</v>
+        <v>77840.000000000015</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33689,7 +33690,7 @@
       </c>
       <c r="B33" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,11),$E$23:$E$37,0))</f>
-        <v>Jarabes</v>
+        <v>Linea 1</v>
       </c>
       <c r="C33" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),11)</f>
@@ -33701,7 +33702,7 @@
       </c>
       <c r="E33" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ16")*100000-16</f>
-        <v>66944</v>
+        <v>91819</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33710,7 +33711,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>Alrededores</v>
+        <v>Linea 5</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33722,7 +33723,7 @@
       </c>
       <c r="E34" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ17")*100000-17</f>
-        <v>52623</v>
+        <v>61798</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33731,7 +33732,7 @@
       </c>
       <c r="B35" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,13),$E$23:$E$37,0))</f>
-        <v>Linea 5</v>
+        <v>Alrededores</v>
       </c>
       <c r="C35" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),13)</f>
@@ -33743,7 +33744,7 @@
       </c>
       <c r="E35" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ18")*100000-18</f>
-        <v>66122</v>
+        <v>91272</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33764,7 +33765,7 @@
       </c>
       <c r="E36" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ19")*100000-19</f>
-        <v>68981</v>
+        <v>86106.000000000015</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33827,7 +33828,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.6546373333333334</v>
+        <v>0.83891666666666675</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33836,7 +33837,7 @@
       </c>
       <c r="B45" s="18" t="str">
         <f ca="1">IF(B44&gt;=Parametros!$C$37,"Verde",IF(B44&gt;=Parametros!$C$38,"Amarillo","Rojo"))</f>
-        <v>Rojo</v>
+        <v>Amarillo</v>
       </c>
     </row>
   </sheetData>
@@ -33982,7 +33983,7 @@
       </c>
       <c r="J4" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
-        <v>0.68375000000000008</v>
+        <v>1</v>
       </c>
       <c r="K4" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
@@ -33998,7 +33999,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.96211111111111114</v>
+        <v>0.99724999999999986</v>
       </c>
       <c r="O4" s="106"/>
     </row>
@@ -34040,7 +34041,7 @@
       </c>
       <c r="J5" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v>0.68737000000000004</v>
+        <v>0.86675000000000013</v>
       </c>
       <c r="K5" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
@@ -34056,7 +34057,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.95297999999999994</v>
+        <v>0.97291111111111106</v>
       </c>
       <c r="O5" s="106"/>
     </row>
@@ -34098,7 +34099,7 @@
       </c>
       <c r="J6" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
-        <v>0.66959999999999997</v>
+        <v>0.91835</v>
       </c>
       <c r="K6" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
@@ -34114,7 +34115,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.93820952380952372</v>
+        <v>0.96584841269841271</v>
       </c>
       <c r="O6" s="106"/>
     </row>
@@ -34156,7 +34157,7 @@
       </c>
       <c r="J7" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
-        <v>0.67</v>
+        <v>0.89475000000000016</v>
       </c>
       <c r="K7" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
@@ -34172,7 +34173,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.92888333333333328</v>
+        <v>0.95385555555555557</v>
       </c>
       <c r="O7" s="106"/>
     </row>
@@ -34214,7 +34215,7 @@
       </c>
       <c r="J8" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
-        <v>0.75</v>
+        <v>0.97300000000000009</v>
       </c>
       <c r="K8" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
@@ -34230,7 +34231,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.93388888888888899</v>
+        <v>0.95866666666666667</v>
       </c>
       <c r="O8" s="106"/>
     </row>
@@ -34272,7 +34273,7 @@
       </c>
       <c r="J9" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
-        <v>0.5835999999999999</v>
+        <v>0.93059999999999987</v>
       </c>
       <c r="K9" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
@@ -34288,7 +34289,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.90340000000000009</v>
+        <v>0.94195555555555566</v>
       </c>
       <c r="O9" s="106"/>
     </row>
@@ -34330,7 +34331,7 @@
       </c>
       <c r="J10" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
-        <v>0.66139999999999999</v>
+        <v>0.91290000000000004</v>
       </c>
       <c r="K10" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
@@ -34346,7 +34347,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.91041721132897591</v>
+        <v>0.93836165577342046</v>
       </c>
       <c r="O10" s="106"/>
     </row>
@@ -34388,7 +34389,7 @@
       </c>
       <c r="J11" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
-        <v>0.74520000000000008</v>
+        <v>0.81770000000000009</v>
       </c>
       <c r="K11" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
@@ -34404,7 +34405,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.90446666666666664</v>
+        <v>0.91252222222222223</v>
       </c>
       <c r="O11" s="106"/>
     </row>
@@ -34446,7 +34447,7 @@
       </c>
       <c r="J12" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
-        <v>0.69000000000000006</v>
+        <v>0.86125000000000018</v>
       </c>
       <c r="K12" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
@@ -34462,7 +34463,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.88375000000000004</v>
+        <v>0.90277777777777779</v>
       </c>
       <c r="O12" s="106"/>
     </row>
@@ -34504,7 +34505,7 @@
       </c>
       <c r="J13" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
-        <v>0.6724</v>
+        <v>0.76500999999999997</v>
       </c>
       <c r="K13" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
@@ -34520,7 +34521,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.87562888888888901</v>
+        <v>0.88591888888888903</v>
       </c>
       <c r="O13" s="106"/>
     </row>
@@ -34562,7 +34563,7 @@
       </c>
       <c r="J14" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
-        <v>0.59564000000000006</v>
+        <v>1</v>
       </c>
       <c r="K14" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
@@ -34578,7 +34579,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.82932714975845423</v>
+        <v>0.87425603864734314</v>
       </c>
       <c r="O14" s="106"/>
     </row>
@@ -34620,7 +34621,7 @@
       </c>
       <c r="J15" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
-        <v>0.52639999999999998</v>
+        <v>0.61814999999999998</v>
       </c>
       <c r="K15" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
@@ -34636,7 +34637,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.81234536019536019</v>
+        <v>0.82253980463980469</v>
       </c>
       <c r="O15" s="106"/>
     </row>
@@ -34678,7 +34679,7 @@
       </c>
       <c r="J16" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
-        <v>0.66379999999999995</v>
+        <v>0.77855000000000008</v>
       </c>
       <c r="K16" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
@@ -34694,7 +34695,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.81519236517218985</v>
+        <v>0.82794236517218989</v>
       </c>
       <c r="O16" s="106"/>
     </row>
@@ -34736,7 +34737,7 @@
       </c>
       <c r="J17" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
-        <v>0.66439999999999999</v>
+        <v>0.69623999999999997</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D13=0,"",'Captura Octubre'!AQ13),"")</f>
@@ -34752,7 +34753,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.80467555555555537</v>
+        <v>0.80821333333333323</v>
       </c>
       <c r="O17" s="106"/>
     </row>
@@ -34794,7 +34795,7 @@
       </c>
       <c r="J18" s="10">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
-        <v>0.55600000000000005</v>
+        <v>0.55049999999999999</v>
       </c>
       <c r="K18" s="10" t="str">
         <f>IFERROR(IF('Captura Octubre'!D7=0,"",'Captura Octubre'!AQ7),"")</f>
@@ -34810,7 +34811,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.75783333333333336</v>
+        <v>0.75722222222222213</v>
       </c>
       <c r="O18" s="106"/>
     </row>
@@ -34852,7 +34853,7 @@
       </c>
       <c r="J19" s="104">
         <f t="shared" si="1"/>
-        <v>0.65463733333333329</v>
+        <v>0.83891666666666653</v>
       </c>
       <c r="K19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -34904,44 +34905,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="130"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="133"/>
+      <c r="Q2" s="133"/>
+      <c r="R2" s="133"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="130"/>
-      <c r="R3" s="130"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="133"/>
+      <c r="Q3" s="133"/>
+      <c r="R3" s="133"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34951,141 +34952,141 @@
         <f>Calculos!$B$2</f>
         <v>Septiembre</v>
       </c>
-      <c r="F4" s="131" t="s">
+      <c r="F4" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="131"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="131"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="131"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="134"/>
+      <c r="O4" s="134"/>
+      <c r="P4" s="134"/>
+      <c r="Q4" s="134"/>
+      <c r="R4" s="134"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="132" t="s">
+      <c r="B6" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132" t="s">
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="132"/>
-      <c r="H6" s="132"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132" t="s">
+      <c r="G6" s="135"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="132"/>
-      <c r="L6" s="132"/>
-      <c r="M6" s="132" t="s">
+      <c r="K6" s="135"/>
+      <c r="L6" s="135"/>
+      <c r="M6" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="132"/>
-      <c r="O6" s="132"/>
-      <c r="P6" s="132" t="s">
+      <c r="N6" s="135"/>
+      <c r="O6" s="135"/>
+      <c r="P6" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="132"/>
-      <c r="R6" s="132"/>
+      <c r="Q6" s="135"/>
+      <c r="R6" s="135"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="132"/>
-      <c r="N7" s="132"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="132"/>
-      <c r="R7" s="132"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
+      <c r="M7" s="135"/>
+      <c r="N7" s="135"/>
+      <c r="O7" s="135"/>
+      <c r="P7" s="135"/>
+      <c r="Q7" s="135"/>
+      <c r="R7" s="135"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="133">
+      <c r="B8" s="128">
         <f ca="1">Calculos!B44</f>
-        <v>0.6546373333333334</v>
-      </c>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="134" t="str">
+        <v>0.83891666666666675</v>
+      </c>
+      <c r="C8" s="128"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="129" t="str">
         <f ca="1">Calculos!B45</f>
-        <v>Rojo</v>
-      </c>
-      <c r="G8" s="134"/>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
-      <c r="J8" s="135">
+        <v>Amarillo</v>
+      </c>
+      <c r="G8" s="129"/>
+      <c r="H8" s="129"/>
+      <c r="I8" s="129"/>
+      <c r="J8" s="130">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="135"/>
-      <c r="L8" s="135"/>
-      <c r="M8" s="128">
+      <c r="K8" s="130"/>
+      <c r="L8" s="130"/>
+      <c r="M8" s="131">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="128"/>
-      <c r="O8" s="128"/>
-      <c r="P8" s="129">
+      <c r="N8" s="131"/>
+      <c r="O8" s="131"/>
+      <c r="P8" s="132">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="129"/>
-      <c r="R8" s="129"/>
+      <c r="Q8" s="132"/>
+      <c r="R8" s="132"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="134"/>
-      <c r="I9" s="134"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="135"/>
-      <c r="L9" s="135"/>
-      <c r="M9" s="128"/>
-      <c r="N9" s="128"/>
-      <c r="O9" s="128"/>
-      <c r="P9" s="129"/>
-      <c r="Q9" s="129"/>
-      <c r="R9" s="129"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="131"/>
+      <c r="N9" s="131"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="132"/>
+      <c r="R9" s="132"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="135"/>
-      <c r="K10" s="135"/>
-      <c r="L10" s="135"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
-      <c r="P10" s="129"/>
-      <c r="Q10" s="129"/>
-      <c r="R10" s="129"/>
+      <c r="B10" s="128"/>
+      <c r="C10" s="128"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="130"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="130"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
+      <c r="R10" s="132"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="127" t="s">
@@ -35116,7 +35117,7 @@
     <row r="14" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="str">
         <f ca="1">Calculos!B23</f>
-        <v>ETEI</v>
+        <v>Calidad</v>
       </c>
       <c r="C14" s="21">
         <f ca="1">Calculos!C23</f>
@@ -35128,13 +35129,13 @@
       </c>
       <c r="H14" s="22">
         <f ca="1">Calculos!D5</f>
-        <v>0.85692000000000013</v>
+        <v>0.93656666666666688</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="str">
         <f ca="1">Calculos!B24</f>
-        <v>Equipos Auxiliares</v>
+        <v>Jarabes</v>
       </c>
       <c r="C15" s="21">
         <f ca="1">Calculos!C24</f>
@@ -35152,7 +35153,7 @@
     <row r="16" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="str">
         <f ca="1">Calculos!B25</f>
-        <v>Materias Primas</v>
+        <v>ETEI</v>
       </c>
       <c r="C16" s="21">
         <f ca="1">Calculos!C25</f>
@@ -35170,7 +35171,7 @@
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="str">
         <f ca="1">Calculos!B26</f>
-        <v>Centro de Distribucion</v>
+        <v>Linea 4</v>
       </c>
       <c r="C17" s="21">
         <f ca="1">Calculos!C26</f>
@@ -35188,7 +35189,7 @@
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="str">
         <f ca="1">Calculos!B27</f>
-        <v>Calidad</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C18" s="21">
         <f ca="1">Calculos!C27</f>
@@ -35200,13 +35201,13 @@
       </c>
       <c r="H18" s="22">
         <f ca="1">Calculos!D9</f>
-        <v>0.13333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="str">
         <f ca="1">Calculos!B28</f>
-        <v>Linea 2</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C19" s="21">
         <f ca="1">Calculos!C28</f>
@@ -35218,13 +35219,13 @@
       </c>
       <c r="H19" s="22">
         <f ca="1">Calculos!D10</f>
-        <v>0</v>
+        <v>0.95280000000000009</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="str">
         <f ca="1">Calculos!B29</f>
-        <v>Linea 4</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C20" s="21">
         <f ca="1">Calculos!C29</f>
@@ -35236,13 +35237,13 @@
       </c>
       <c r="H20" s="22">
         <f ca="1">Calculos!D11</f>
-        <v>1</v>
+        <v>0.57333333333333347</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="str">
         <f ca="1">Calculos!B30</f>
-        <v>Linea 1</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C21" s="21">
         <f ca="1">Calculos!C30</f>
@@ -35262,7 +35263,7 @@
     <row r="23" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="str">
         <f ca="1">Calculos!B32</f>
-        <v>Mantenimiento</v>
+        <v>Linea 2</v>
       </c>
       <c r="C23" s="21">
         <f ca="1">Calculos!C32</f>
@@ -35272,7 +35273,7 @@
     <row r="24" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="str">
         <f ca="1">Calculos!B33</f>
-        <v>Jarabes</v>
+        <v>Linea 1</v>
       </c>
       <c r="C24" s="21">
         <f ca="1">Calculos!C33</f>
@@ -35282,7 +35283,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>Alrededores</v>
+        <v>Linea 5</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -35292,7 +35293,7 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="str">
         <f ca="1">Calculos!B35</f>
-        <v>Linea 5</v>
+        <v>Alrededores</v>
       </c>
       <c r="C26" s="21">
         <f ca="1">Calculos!C35</f>
@@ -35348,11 +35349,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35362,6 +35358,11 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35391,61 +35392,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="138" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="147" t="s">
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="139" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="148" t="s">
+      <c r="B4" s="140" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="148"/>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="148"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="148"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="148"/>
-      <c r="K4" s="148"/>
-      <c r="L4" s="148"/>
-      <c r="M4" s="148"/>
-      <c r="N4" s="148"/>
-      <c r="O4" s="148"/>
-      <c r="P4" s="148"/>
-      <c r="Q4" s="148"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="140"/>
+      <c r="J4" s="140"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
+      <c r="N4" s="140"/>
+      <c r="O4" s="140"/>
+      <c r="P4" s="140"/>
+      <c r="Q4" s="140"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="149" t="str">
+      <c r="B5" s="141" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  SEPTIEMBRE 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="149"/>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="149"/>
-      <c r="G5" s="149"/>
-      <c r="H5" s="149"/>
-      <c r="I5" s="149"/>
-      <c r="J5" s="149"/>
-      <c r="K5" s="149"/>
-      <c r="L5" s="149"/>
-      <c r="M5" s="149"/>
-      <c r="N5" s="149"/>
-      <c r="O5" s="149"/>
-      <c r="P5" s="149"/>
-      <c r="Q5" s="149"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="141"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
+      <c r="N5" s="141"/>
+      <c r="O5" s="141"/>
+      <c r="P5" s="141"/>
+      <c r="Q5" s="141"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35456,7 +35457,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="136" t="str">
+      <c r="A7" s="142" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>SEPTIEMBRE</v>
       </c>
@@ -35473,13 +35474,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="136"/>
-      <c r="G8" s="137">
+      <c r="A8" s="142"/>
+      <c r="G8" s="143">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35489,15 +35490,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="136"/>
-      <c r="F9" s="138">
+      <c r="A9" s="142"/>
+      <c r="F9" s="144">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-      <c r="J9" s="138"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="144"/>
+      <c r="J9" s="144"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35507,17 +35508,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="136"/>
-      <c r="E10" s="139">
+      <c r="A10" s="142"/>
+      <c r="E10" s="145">
         <f ca="1">X33</f>
         <v>1</v>
       </c>
-      <c r="F10" s="139"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="139"/>
-      <c r="K10" s="139"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="145"/>
+      <c r="K10" s="145"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35527,43 +35528,43 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="136"/>
-      <c r="D11" s="140">
+      <c r="A11" s="142"/>
+      <c r="D11" s="146">
         <f ca="1">X34</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
+        <v>1</v>
+      </c>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
       <c r="Q11" s="32">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="136"/>
-      <c r="C12" s="141">
+      <c r="A12" s="142"/>
+      <c r="C12" s="147">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="141"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="141"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="141"/>
-      <c r="M12" s="141"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="147"/>
+      <c r="H12" s="147"/>
+      <c r="I12" s="147"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="147"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35573,75 +35574,75 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="136"/>
-      <c r="B13" s="142">
+      <c r="A13" s="142"/>
+      <c r="B13" s="148">
         <f ca="1">X36</f>
-        <v>24</v>
-      </c>
-      <c r="C13" s="142"/>
-      <c r="D13" s="142"/>
-      <c r="E13" s="142"/>
-      <c r="F13" s="142"/>
-      <c r="G13" s="142"/>
-      <c r="H13" s="142"/>
-      <c r="I13" s="142"/>
-      <c r="J13" s="142"/>
-      <c r="K13" s="142"/>
-      <c r="L13" s="142"/>
-      <c r="M13" s="142"/>
-      <c r="N13" s="142"/>
+        <v>50</v>
+      </c>
+      <c r="C13" s="148"/>
+      <c r="D13" s="148"/>
+      <c r="E13" s="148"/>
+      <c r="F13" s="148"/>
+      <c r="G13" s="148"/>
+      <c r="H13" s="148"/>
+      <c r="I13" s="148"/>
+      <c r="J13" s="148"/>
+      <c r="K13" s="148"/>
+      <c r="L13" s="148"/>
+      <c r="M13" s="148"/>
+      <c r="N13" s="148"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
       <c r="Q13" s="34">
         <f>Y36</f>
-        <v>487</v>
+        <v>513</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="136"/>
-      <c r="B14" s="143">
+      <c r="A14" s="142"/>
+      <c r="B14" s="149">
         <f ca="1">X37</f>
-        <v>153</v>
-      </c>
-      <c r="C14" s="143"/>
-      <c r="D14" s="143"/>
-      <c r="E14" s="143"/>
-      <c r="F14" s="143"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="143"/>
-      <c r="I14" s="143"/>
-      <c r="J14" s="143"/>
-      <c r="K14" s="143"/>
-      <c r="L14" s="143"/>
-      <c r="M14" s="143"/>
-      <c r="N14" s="143"/>
+        <v>247</v>
+      </c>
+      <c r="C14" s="149"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="149"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="149"/>
+      <c r="J14" s="149"/>
+      <c r="K14" s="149"/>
+      <c r="L14" s="149"/>
+      <c r="M14" s="149"/>
+      <c r="N14" s="149"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
       <c r="Q14" s="34">
         <f t="shared" si="0"/>
-        <v>2077</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="144" t="s">
+      <c r="S16" s="136" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="144"/>
-      <c r="U16" s="144"/>
-      <c r="V16" s="144"/>
+      <c r="T16" s="136"/>
+      <c r="U16" s="136"/>
+      <c r="V16" s="136"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S18" s="35">
         <f ca="1">IF(T20="","—",INT(TODAY()-T20))</f>
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="U18" s="35">
         <f ca="1">IF(V20="","—",INT(TODAY()-V20))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35670,11 +35671,11 @@
     <row r="22" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S22" s="35">
         <f ca="1">IF(T24="","—",INT(TODAY()-T24))</f>
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U22" s="35">
         <f ca="1">IF(V24="","—",INT(TODAY()-V24))</f>
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35696,48 +35697,48 @@
         <v>84</v>
       </c>
       <c r="V24" s="38">
-        <v>46258</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="145" t="s">
+      <c r="B27" s="137" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="145"/>
-      <c r="D27" s="145"/>
-      <c r="E27" s="145"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="145"/>
-      <c r="H27" s="145"/>
-      <c r="I27" s="145"/>
-      <c r="J27" s="145"/>
-      <c r="K27" s="145"/>
-      <c r="L27" s="145"/>
-      <c r="M27" s="145"/>
-      <c r="N27" s="145"/>
-      <c r="O27" s="145"/>
-      <c r="P27" s="145"/>
-      <c r="Q27" s="145"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="137"/>
+      <c r="I27" s="137"/>
+      <c r="J27" s="137"/>
+      <c r="K27" s="137"/>
+      <c r="L27" s="137"/>
+      <c r="M27" s="137"/>
+      <c r="N27" s="137"/>
+      <c r="O27" s="137"/>
+      <c r="P27" s="137"/>
+      <c r="Q27" s="137"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="145"/>
-      <c r="C28" s="145"/>
-      <c r="D28" s="145"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="145"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="145"/>
-      <c r="J28" s="145"/>
-      <c r="K28" s="145"/>
-      <c r="L28" s="145"/>
-      <c r="M28" s="145"/>
-      <c r="N28" s="145"/>
-      <c r="O28" s="145"/>
-      <c r="P28" s="145"/>
-      <c r="Q28" s="145"/>
+      <c r="B28" s="137"/>
+      <c r="C28" s="137"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="137"/>
+      <c r="H28" s="137"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="137"/>
+      <c r="K28" s="137"/>
+      <c r="L28" s="137"/>
+      <c r="M28" s="137"/>
+      <c r="N28" s="137"/>
+      <c r="O28" s="137"/>
+      <c r="P28" s="137"/>
+      <c r="Q28" s="137"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35795,11 +35796,11 @@
       </c>
       <c r="X34" s="41">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF6")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF7")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF8")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF9")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF10")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF11")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF12")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF13")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF14")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF15")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF16")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF17")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF18")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF19")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF20"),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="41">
         <f>SUM('Captura Enero'!AF6:AF20)+SUM('Captura Febrero'!AF6:AF20)+SUM('Captura Marzo'!AF6:AF20)+SUM('Captura Abril'!AF6:AF20)+SUM('Captura Mayo'!AF6:AF20)+SUM('Captura Junio'!AF6:AF20)+SUM('Captura Julio'!AF6:AF20)+SUM('Captura Agosto'!AF6:AF20)+SUM('Captura Septiembre'!AF6:AF20)+SUM('Captura Octubre'!AF6:AF20)+SUM('Captura Noviembre'!AF6:AF20)+SUM('Captura Diciembre'!AF6:AF20)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="23:25" x14ac:dyDescent="0.35">
@@ -35821,11 +35822,11 @@
       </c>
       <c r="X36" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC3"),0)</f>
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="Y36" s="41">
         <f>'Captura Enero'!BC3+'Captura Febrero'!BC3+'Captura Marzo'!BC3+'Captura Abril'!BC3+'Captura Mayo'!BC3+'Captura Junio'!BC3+'Captura Julio'!BC3+'Captura Agosto'!BC3+'Captura Septiembre'!BC3+'Captura Octubre'!BC3+'Captura Noviembre'!BC3+'Captura Diciembre'!BC3</f>
-        <v>487</v>
+        <v>513</v>
       </c>
     </row>
     <row r="37" spans="23:25" x14ac:dyDescent="0.35">
@@ -35834,21 +35835,15 @@
       </c>
       <c r="X37" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC4"),0)</f>
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="Y37" s="41">
         <f>'Captura Enero'!BC4+'Captura Febrero'!BC4+'Captura Marzo'!BC4+'Captura Abril'!BC4+'Captura Mayo'!BC4+'Captura Junio'!BC4+'Captura Julio'!BC4+'Captura Agosto'!BC4+'Captura Septiembre'!BC4+'Captura Octubre'!BC4+'Captura Noviembre'!BC4+'Captura Diciembre'!BC4</f>
-        <v>2077</v>
+        <v>2171</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35857,6 +35852,12 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -35891,13 +35892,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="127" t="s">
@@ -36491,62 +36492,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36555,20 +36556,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36616,66 +36617,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36887,10 +36888,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39457,16 +39458,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93297435897435899</v>
@@ -39638,9 +39639,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39667,11 +39668,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39729,6 +39730,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39743,12 +39750,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39830,62 +39831,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39894,20 +39895,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39955,66 +39956,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -40226,10 +40227,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42796,16 +42797,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42972,9 +42973,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -43001,11 +43002,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -43063,6 +43064,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -43077,12 +43084,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -43164,62 +43165,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -43228,20 +43229,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -43289,66 +43290,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43560,10 +43561,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -46130,16 +46131,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46306,9 +46307,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46335,11 +46336,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46397,6 +46398,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46411,12 +46418,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46498,62 +46499,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="117" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="110"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="111" t="s">
+      <c r="AS1" s="118" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="111"/>
-      <c r="AU1" s="111"/>
-      <c r="AV1" s="111"/>
-      <c r="AW1" s="111"/>
-      <c r="AX1" s="111"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="111"/>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112" t="s">
+      <c r="AT1" s="118"/>
+      <c r="AU1" s="118"/>
+      <c r="AV1" s="118"/>
+      <c r="AW1" s="118"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="118"/>
+      <c r="BA1" s="118"/>
+      <c r="BB1" s="119" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="112"/>
+      <c r="BC1" s="119"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="120" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46562,20 +46563,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="114" t="s">
+      <c r="AT2" s="121" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="114"/>
-      <c r="AV2" s="114"/>
+      <c r="AU2" s="121"/>
+      <c r="AV2" s="121"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="115" t="s">
+      <c r="AX2" s="122" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="115"/>
-      <c r="AZ2" s="115"/>
-      <c r="BA2" s="115"/>
+      <c r="AY2" s="122"/>
+      <c r="AZ2" s="122"/>
+      <c r="BA2" s="122"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46623,66 +46624,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="121" t="s">
+      <c r="D4" s="114" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121" t="s">
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121" t="s">
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121" t="s">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121" t="s">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="121"/>
-      <c r="W4" s="122" t="s">
+      <c r="V4" s="114"/>
+      <c r="W4" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="121" t="s">
+      <c r="X4" s="115"/>
+      <c r="Y4" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="121"/>
-      <c r="AA4" s="121"/>
-      <c r="AB4" s="121"/>
-      <c r="AC4" s="121"/>
-      <c r="AD4" s="122" t="s">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="122"/>
-      <c r="AL4" s="122"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="123" t="s">
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="115"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="123"/>
+      <c r="AQ4" s="116"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46894,10 +46895,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="117" t="s">
+      <c r="BB5" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="117"/>
+      <c r="BC5" s="110"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49464,16 +49465,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="118" t="s">
+      <c r="AS19" s="111" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="118"/>
+      <c r="AT19" s="111"/>
+      <c r="AU19" s="111"/>
+      <c r="AV19" s="111"/>
+      <c r="AW19" s="111"/>
+      <c r="AX19" s="111"/>
+      <c r="AY19" s="111"/>
+      <c r="AZ19" s="111"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49640,9 +49641,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="119"/>
-      <c r="B22" s="119"/>
-      <c r="C22" s="119"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49669,11 +49670,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="113" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49731,6 +49732,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49745,12 +49752,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49811,15 +49812,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -50066,6 +50058,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -50078,14 +50079,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76AB9A25-5769-416B-8E9A-2215F01CC611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50100,6 +50093,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
